--- a/ROSALES/Noviembre/expensas rosales Noviembre.xlsx
+++ b/ROSALES/Noviembre/expensas rosales Noviembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Octubre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\ROSALES\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BAACF8B-066A-4F59-A567-DBA2E3E26408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E54E42-B564-4C6B-B87B-B344374D11FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Edesur" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$68</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$N$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$L$37</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="126">
   <si>
     <t>TOTAL</t>
   </si>
@@ -397,13 +397,16 @@
     <t>PUNITORIOS MAL COBRADOS</t>
   </si>
   <si>
-    <t>Vto. 14/11</t>
-  </si>
-  <si>
-    <t>LIQUIDACIÓN EXPENSAS OCTUBRE 2025</t>
-  </si>
-  <si>
-    <t>EGRESOS DEL MES DE OCTUBRE</t>
+    <t>Vto. 15/12</t>
+  </si>
+  <si>
+    <t>LIQUIDACIÓN EXPENSAS NOVIEMBRE 2025</t>
+  </si>
+  <si>
+    <t>EGRESOS DEL MES DE NOVIEMBRE</t>
+  </si>
+  <si>
+    <t>Arreglo Sr. Leo - Mano de obra y materiales</t>
   </si>
 </sst>
 </file>
@@ -1033,7 +1036,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="245">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1363,47 +1366,6 @@
     <xf numFmtId="44" fontId="20" fillId="11" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="32" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1427,6 +1389,52 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1844,17 +1852,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F68"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:F69"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -1862,22 +1870,22 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="15"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
@@ -1888,73 +1896,73 @@
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="35" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="36"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="28"/>
       <c r="B17" s="37"/>
       <c r="C17" s="33"/>
       <c r="D17" s="4"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="28" t="s">
         <v>105</v>
       </c>
       <c r="B18" s="38"/>
-      <c r="C18" s="33">
+      <c r="C18" s="246">
         <v>76654</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="206">
-        <v>320979.07</v>
+      <c r="C19" s="247">
+        <v>316973.44</v>
       </c>
       <c r="D19" s="20"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="28" t="s">
         <v>119</v>
       </c>
@@ -1965,18 +1973,18 @@
       <c r="D20" s="20"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="28" t="s">
         <v>25</v>
       </c>
       <c r="B21" s="39"/>
-      <c r="C21" s="33">
-        <v>75000</v>
+      <c r="C21" s="246">
+        <v>80000</v>
       </c>
       <c r="D21" s="20"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="28" t="s">
         <v>118</v>
       </c>
@@ -1990,7 +1998,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="28" t="s">
         <v>11</v>
       </c>
@@ -2001,15 +2009,15 @@
         <v>83400</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="40"/>
       <c r="B24" s="41"/>
       <c r="C24" s="23">
         <f>SUM(C17:C23)</f>
-        <v>1181978.07</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1182972.44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="35" t="s">
         <v>12</v>
       </c>
@@ -2018,7 +2026,7 @@
       <c r="D25" s="45"/>
       <c r="F25" s="12"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="28" t="s">
         <v>97</v>
       </c>
@@ -2030,7 +2038,7 @@
       <c r="D26" s="45"/>
       <c r="F26" s="12"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="28" t="s">
         <v>98</v>
       </c>
@@ -2041,305 +2049,316 @@
       <c r="D27" s="45"/>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="174" t="s">
+    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="245" t="s">
+        <v>125</v>
+      </c>
+      <c r="B28" s="138"/>
+      <c r="C28" s="246">
+        <v>610000</v>
+      </c>
+      <c r="D28" s="45"/>
+      <c r="F28" s="12"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="174" t="s">
         <v>107</v>
       </c>
-      <c r="B28" s="138"/>
-      <c r="C28" s="33">
+      <c r="B29" s="138"/>
+      <c r="C29" s="33">
         <v>41110</v>
       </c>
-      <c r="F28" s="12"/>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
+      <c r="F29" s="12"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="42"/>
-      <c r="C29" s="33">
+      <c r="B30" s="42"/>
+      <c r="C30" s="33">
         <v>55000</v>
       </c>
-      <c r="F29" s="12"/>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="28" t="s">
+      <c r="F30" s="12"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="B30" s="39"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="12"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="40"/>
-      <c r="B31" s="41"/>
-      <c r="C31" s="23">
-        <f>SUM(C25:C30)</f>
-        <v>485861.05699999997</v>
-      </c>
+      <c r="B31" s="39"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="6"/>
       <c r="F31" s="12"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="30" t="s">
+    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="40"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="23">
+        <f>SUM(C25:C31)</f>
+        <v>1095861.057</v>
+      </c>
+      <c r="F32" s="12"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="43">
-        <f>+C31+C24</f>
-        <v>1667839.1270000001</v>
-      </c>
-      <c r="F32" s="12"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C33" s="24"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="43">
+        <f>+C32+C24</f>
+        <v>2278833.497</v>
+      </c>
       <c r="F33" s="12"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="13" t="s">
-        <v>17</v>
-      </c>
+    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C34" s="24"/>
       <c r="F34" s="12"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="28"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="33"/>
+    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="24"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="28"/>
       <c r="B36" s="28"/>
-      <c r="C36" s="34"/>
+      <c r="C36" s="33"/>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="28"/>
       <c r="B37" s="28"/>
       <c r="C37" s="34"/>
       <c r="F37" s="12"/>
     </row>
-    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C38" s="25"/>
+    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="28"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="34"/>
       <c r="F38" s="12"/>
     </row>
-    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="177" t="s">
+    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C39" s="25"/>
+      <c r="F39" s="12"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="177" t="s">
         <v>111</v>
       </c>
-      <c r="B39" s="177"/>
-      <c r="C39" s="178">
+      <c r="B40" s="177"/>
+      <c r="C40" s="178">
         <v>400000</v>
       </c>
-      <c r="F39" s="12"/>
-    </row>
-    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C40" s="25"/>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="13" t="s">
+    <row r="41" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C41" s="25"/>
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="14">
-        <f>+C35+C36+C37+C40</f>
-        <v>0</v>
-      </c>
-      <c r="E41" s="6"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="18" t="s">
+      <c r="B42" s="13"/>
+      <c r="C42" s="14">
+        <f>+C36+C37+C38+C41</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="6"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B43" s="18"/>
-      <c r="C43" s="19">
-        <f>+C41+C32</f>
-        <v>1667839.1270000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="219" t="s">
+      <c r="B44" s="18"/>
+      <c r="C44" s="19">
+        <f>+C42+C33</f>
+        <v>2278833.497</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="234" t="s">
         <v>110</v>
       </c>
-      <c r="B45" s="220"/>
-      <c r="C45" s="220"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="220"/>
-      <c r="B46" s="220"/>
-      <c r="C46" s="220"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="220"/>
-      <c r="B47" s="220"/>
-      <c r="C47" s="220"/>
-    </row>
-    <row r="48" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="220"/>
-      <c r="B48" s="220"/>
-      <c r="C48" s="220"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-    </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="4"/>
-      <c r="C49" s="155"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="208" t="s">
-        <v>100</v>
-      </c>
-      <c r="B50" s="28"/>
-      <c r="C50" s="209">
-        <v>149754.72</v>
-      </c>
+      <c r="B46" s="235"/>
+      <c r="C46" s="235"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="235"/>
+      <c r="B47" s="235"/>
+      <c r="C47" s="235"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="235"/>
+      <c r="B48" s="235"/>
+      <c r="C48" s="235"/>
+    </row>
+    <row r="49" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="235"/>
+      <c r="B49" s="235"/>
+      <c r="C49" s="235"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+    </row>
+    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="4"/>
+      <c r="C50" s="155"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="208" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="B51" s="28"/>
-      <c r="C51" s="31">
-        <f>-(C32-C30)</f>
-        <v>-1667839.1270000001</v>
+      <c r="C51" s="209">
+        <v>149754.72</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="208" t="s">
+        <v>124</v>
+      </c>
+      <c r="B52" s="28"/>
+      <c r="C52" s="31">
+        <f>-(C33-C31)</f>
+        <v>-2278833.497</v>
+      </c>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="208" t="s">
         <v>96</v>
       </c>
-      <c r="B52" s="28"/>
-      <c r="C52" s="210">
+      <c r="B53" s="28"/>
+      <c r="C53" s="210">
         <f>'prorrateo '!F31</f>
         <v>2872567.6936899996</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="208" t="s">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="208" t="s">
         <v>121</v>
       </c>
-      <c r="B53" s="28"/>
-      <c r="C53" s="232">
+      <c r="B54" s="28"/>
+      <c r="C54" s="217">
         <v>-4346.7907999999998</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="208" t="s">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="208" t="s">
         <v>120</v>
       </c>
-      <c r="B54" s="28"/>
-      <c r="C54" s="210">
+      <c r="B55" s="28"/>
+      <c r="C55" s="210">
         <v>107386.2</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="208" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="208" t="s">
         <v>114</v>
       </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="211">
+      <c r="B56" s="28"/>
+      <c r="C56" s="211">
         <v>-376000</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="208" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="208" t="s">
         <v>8</v>
       </c>
-      <c r="B56" s="28"/>
-      <c r="C56" s="209">
-        <f>SUM(C48:C55)</f>
-        <v>1081522.6958899994</v>
-      </c>
-      <c r="D56" s="5"/>
-    </row>
-    <row r="57" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="9"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="10"/>
-    </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="215"/>
-      <c r="B58" s="215"/>
-      <c r="C58" s="215"/>
-      <c r="F58" s="44"/>
-    </row>
-    <row r="59" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="216"/>
-      <c r="B59" s="216"/>
-      <c r="C59" s="216"/>
-    </row>
-    <row r="60" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="26" t="s">
+      <c r="B57" s="28"/>
+      <c r="C57" s="209">
+        <f>SUM(C49:C56)</f>
+        <v>470528.32588999986</v>
+      </c>
+      <c r="D57" s="5"/>
+    </row>
+    <row r="58" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="9"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="10"/>
+    </row>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="230"/>
+      <c r="B59" s="230"/>
+      <c r="C59" s="230"/>
+      <c r="F59" s="44"/>
+    </row>
+    <row r="60" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="231"/>
+      <c r="B60" s="231"/>
+      <c r="C60" s="231"/>
+    </row>
+    <row r="61" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B60" s="27"/>
-      <c r="C60" s="29"/>
-    </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="28" t="s">
+      <c r="B61" s="27"/>
+      <c r="C61" s="29"/>
+    </row>
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B61" s="28"/>
-      <c r="C61" s="31">
-        <f>-C41</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="28"/>
       <c r="B62" s="28"/>
-      <c r="C62" s="31"/>
-    </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C62" s="31">
+        <f>-C42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="28"/>
       <c r="B63" s="28"/>
-      <c r="C63" s="32"/>
-    </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="156" t="s">
-        <v>0</v>
-      </c>
-      <c r="B64" s="157"/>
-      <c r="C64" s="158">
-        <f>SUM(C60:C63)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="217" t="s">
+      <c r="C63" s="31"/>
+    </row>
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="28"/>
+      <c r="B64" s="28"/>
+      <c r="C64" s="32"/>
+    </row>
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="156" t="s">
+        <v>0</v>
+      </c>
+      <c r="B65" s="157"/>
+      <c r="C65" s="158">
+        <f>SUM(C61:C64)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="B65" s="218"/>
-      <c r="C65" s="218"/>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="218"/>
-      <c r="B66" s="218"/>
-      <c r="C66" s="218"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="218"/>
-      <c r="B67" s="218"/>
-      <c r="C67" s="218"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="8"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
+      <c r="B66" s="233"/>
+      <c r="C66" s="233"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="233"/>
+      <c r="B67" s="233"/>
+      <c r="C67" s="233"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="233"/>
+      <c r="B68" s="233"/>
+      <c r="C68" s="233"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="8"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A58:C59"/>
-    <mergeCell ref="A65:C67"/>
-    <mergeCell ref="A45:C48"/>
+    <mergeCell ref="A59:C60"/>
+    <mergeCell ref="A66:C68"/>
+    <mergeCell ref="A46:C49"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <hyperlinks>
@@ -2358,58 +2377,58 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="11"/>
+    <col min="1" max="1" width="19.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" customWidth="1"/>
+    <col min="11" max="11" width="11.5546875" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.44140625" style="11"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="221">
+      <c r="B1" s="236">
         <f>D1-K1</f>
         <v>1057642.1270000001</v>
       </c>
-      <c r="C1" s="221"/>
+      <c r="C1" s="236"/>
       <c r="D1" s="139">
         <v>1667839.1270000001</v>
       </c>
       <c r="E1" t="s">
         <v>102</v>
       </c>
-      <c r="G1" s="223">
+      <c r="G1" s="238">
         <v>400000</v>
       </c>
-      <c r="H1" s="223"/>
-      <c r="I1" s="224" t="s">
+      <c r="H1" s="238"/>
+      <c r="I1" s="239" t="s">
         <v>116</v>
       </c>
-      <c r="J1" s="224"/>
-      <c r="K1" s="221">
+      <c r="J1" s="239"/>
+      <c r="K1" s="236">
         <f>M1</f>
         <v>610197</v>
       </c>
-      <c r="L1" s="221"/>
+      <c r="L1" s="236"/>
       <c r="M1">
         <v>610197</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="46" t="s">
         <v>26</v>
       </c>
@@ -2447,7 +2466,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="52" t="s">
         <v>31</v>
       </c>
@@ -2493,7 +2512,7 @@
       </c>
       <c r="M3" s="44"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="58" t="s">
         <v>33</v>
       </c>
@@ -2539,7 +2558,7 @@
       </c>
       <c r="M4" s="44"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>35</v>
       </c>
@@ -2580,7 +2599,7 @@
       </c>
       <c r="M5" s="44"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="58" t="s">
         <v>37</v>
       </c>
@@ -2624,7 +2643,7 @@
       </c>
       <c r="O6" s="180"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>35</v>
       </c>
@@ -2670,7 +2689,7 @@
       </c>
       <c r="O7" s="180"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="58" t="s">
         <v>40</v>
       </c>
@@ -2713,7 +2732,7 @@
         <v>105253.0115643</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>42</v>
       </c>
@@ -2757,7 +2776,7 @@
       </c>
       <c r="O9" s="180"/>
     </row>
-    <row r="10" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="183" t="s">
         <v>44</v>
       </c>
@@ -2799,7 +2818,7 @@
         <v>105253.0115643</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>95</v>
       </c>
@@ -2842,7 +2861,7 @@
         <v>104219.09200080001</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="58" t="s">
         <v>47</v>
       </c>
@@ -2857,7 +2876,7 @@
         <v>149035.48339000001</v>
       </c>
       <c r="F12" s="175">
-        <f t="shared" ref="F4:F12" si="7">E12</f>
+        <f t="shared" ref="F12" si="7">E12</f>
         <v>149035.48339000001</v>
       </c>
       <c r="G12" s="56">
@@ -2885,7 +2904,7 @@
         <v>107734.41851670001</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>49</v>
       </c>
@@ -2931,7 +2950,7 @@
       </c>
       <c r="M13" s="44"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="62" t="s">
         <v>49</v>
       </c>
@@ -2973,7 +2992,7 @@
         <v>371509.96055870003</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>53</v>
       </c>
@@ -3018,7 +3037,7 @@
         <v>104219.09188079997</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="58" t="s">
         <v>56</v>
       </c>
@@ -3035,7 +3054,7 @@
         <v>149035.48339000001</v>
       </c>
       <c r="F16" s="175">
-        <f>E16</f>
+        <f t="shared" ref="F16:F21" si="8">E16</f>
         <v>149035.48339000001</v>
       </c>
       <c r="G16" s="56">
@@ -3064,7 +3083,7 @@
       </c>
       <c r="M16" s="44"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>59</v>
       </c>
@@ -3079,7 +3098,7 @@
         <v>253501.39815999998</v>
       </c>
       <c r="F17" s="175">
-        <f>E17</f>
+        <f t="shared" si="8"/>
         <v>253501.39815999998</v>
       </c>
       <c r="G17" s="56">
@@ -3107,11 +3126,11 @@
         <v>104219.09200080001</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="230" t="s">
+    <row r="18" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="215" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="231"/>
+      <c r="B18" s="216"/>
       <c r="C18" s="63" t="s">
         <v>62</v>
       </c>
@@ -3122,7 +3141,7 @@
         <v>262052.04419000002</v>
       </c>
       <c r="F18" s="175">
-        <f>E18</f>
+        <f t="shared" si="8"/>
         <v>262052.04419000002</v>
       </c>
       <c r="G18" s="64">
@@ -3149,12 +3168,12 @@
         <f t="shared" si="5"/>
         <v>107734.41851670001</v>
       </c>
-      <c r="M18" s="235"/>
-      <c r="N18" s="234"/>
-      <c r="O18" s="233"/>
+      <c r="M18" s="220"/>
+      <c r="N18" s="219"/>
+      <c r="O18" s="218"/>
       <c r="P18" s="214"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="62" t="s">
         <v>63</v>
       </c>
@@ -3169,7 +3188,7 @@
         <v>211681.87660000002</v>
       </c>
       <c r="F19" s="175">
-        <f>E19</f>
+        <f t="shared" si="8"/>
         <v>211681.87660000002</v>
       </c>
       <c r="G19" s="64">
@@ -3197,7 +3216,7 @@
         <v>153020.095398</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="24" x14ac:dyDescent="0.3">
       <c r="A20" s="190"/>
       <c r="B20" s="184" t="s">
         <v>99</v>
@@ -3212,7 +3231,7 @@
         <v>30894.111720000001</v>
       </c>
       <c r="F20" s="212">
-        <f>E20</f>
+        <f t="shared" si="8"/>
         <v>30894.111720000001</v>
       </c>
       <c r="G20" s="188">
@@ -3237,7 +3256,7 @@
         <v>22332.662571600002</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="62"/>
       <c r="B21" s="59" t="s">
         <v>57</v>
@@ -3252,7 +3271,7 @@
         <v>30894.111720000001</v>
       </c>
       <c r="F21" s="175">
-        <f>E21</f>
+        <f t="shared" si="8"/>
         <v>30894.111720000001</v>
       </c>
       <c r="G21" s="56">
@@ -3280,7 +3299,7 @@
         <v>22332.662571600002</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="140"/>
       <c r="B22" s="141"/>
       <c r="C22" s="142" t="s">
@@ -3320,7 +3339,7 @@
         <v>262598.51501640002</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="58"/>
       <c r="B23" s="59"/>
       <c r="C23" s="60" t="s">
@@ -3358,7 +3377,7 @@
         <v>54462.538760400006</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="58" t="s">
         <v>49</v>
       </c>
@@ -3375,7 +3394,7 @@
         <v>30894.111720000001</v>
       </c>
       <c r="F24" s="175">
-        <f t="shared" ref="F24" si="8">E24</f>
+        <f t="shared" ref="F24" si="9">E24</f>
         <v>30894.111720000001</v>
       </c>
       <c r="G24" s="56">
@@ -3403,7 +3422,7 @@
         <v>22332.662571600002</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
@@ -3445,7 +3464,7 @@
         <v>78827.255240400002</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="58" t="s">
         <v>63</v>
       </c>
@@ -3460,7 +3479,7 @@
         <v>30894.111720000001</v>
       </c>
       <c r="F26" s="175">
-        <f t="shared" ref="F26:F28" si="9">E26</f>
+        <f t="shared" ref="F26:F28" si="10">E26</f>
         <v>30894.111720000001</v>
       </c>
       <c r="G26" s="56">
@@ -3488,7 +3507,7 @@
         <v>22332.662571600002</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="58" t="s">
         <v>63</v>
       </c>
@@ -3503,7 +3522,7 @@
         <v>30894.111720000001</v>
       </c>
       <c r="F27" s="175">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>30894.111720000001</v>
       </c>
       <c r="G27" s="56">
@@ -3535,7 +3554,7 @@
         <v>273470.10004000005</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="66"/>
       <c r="B28" s="65" t="str">
         <f>B7</f>
@@ -3551,7 +3570,7 @@
         <v>30894.111720000001</v>
       </c>
       <c r="F28" s="175">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>30894.111720000001</v>
       </c>
       <c r="G28" s="56">
@@ -3579,7 +3598,7 @@
         <v>22332.662571600002</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="66" t="s">
         <v>53</v>
       </c>
@@ -3624,7 +3643,7 @@
         <v>22332.662571600002</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="67"/>
       <c r="B30" s="67"/>
       <c r="C30" s="68"/>
@@ -3638,7 +3657,7 @@
       <c r="K30" s="71"/>
       <c r="L30" s="71"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="72"/>
       <c r="B31" s="73"/>
       <c r="C31" s="74" t="s">
@@ -3669,68 +3688,68 @@
         <v>2965528.3114872011</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="J32" s="22"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="222" t="s">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="237" t="s">
         <v>112</v>
       </c>
-      <c r="B33" s="222"/>
-      <c r="C33" s="222"/>
-      <c r="D33" s="222"/>
-      <c r="E33" s="222"/>
-      <c r="F33" s="222"/>
-      <c r="G33" s="222"/>
-      <c r="H33" s="222"/>
-      <c r="I33" s="222"/>
-      <c r="J33" s="222"/>
-      <c r="K33" s="222"/>
-      <c r="L33" s="222"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="222"/>
-      <c r="B34" s="222"/>
-      <c r="C34" s="222"/>
-      <c r="D34" s="222"/>
-      <c r="E34" s="222"/>
-      <c r="F34" s="222"/>
-      <c r="G34" s="222"/>
-      <c r="H34" s="222"/>
-      <c r="I34" s="222"/>
-      <c r="J34" s="222"/>
-      <c r="K34" s="222"/>
-      <c r="L34" s="222"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="222"/>
-      <c r="B35" s="222"/>
-      <c r="C35" s="222"/>
-      <c r="D35" s="222"/>
-      <c r="E35" s="222"/>
-      <c r="F35" s="222"/>
-      <c r="G35" s="222"/>
-      <c r="H35" s="222"/>
-      <c r="I35" s="222"/>
-      <c r="J35" s="222"/>
-      <c r="K35" s="222"/>
-      <c r="L35" s="222"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="222"/>
-      <c r="B36" s="222"/>
-      <c r="C36" s="222"/>
-      <c r="D36" s="222"/>
-      <c r="E36" s="222"/>
-      <c r="F36" s="222"/>
-      <c r="G36" s="222"/>
-      <c r="H36" s="222"/>
-      <c r="I36" s="222"/>
-      <c r="J36" s="222"/>
-      <c r="K36" s="222"/>
-      <c r="L36" s="222"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B33" s="237"/>
+      <c r="C33" s="237"/>
+      <c r="D33" s="237"/>
+      <c r="E33" s="237"/>
+      <c r="F33" s="237"/>
+      <c r="G33" s="237"/>
+      <c r="H33" s="237"/>
+      <c r="I33" s="237"/>
+      <c r="J33" s="237"/>
+      <c r="K33" s="237"/>
+      <c r="L33" s="237"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="237"/>
+      <c r="B34" s="237"/>
+      <c r="C34" s="237"/>
+      <c r="D34" s="237"/>
+      <c r="E34" s="237"/>
+      <c r="F34" s="237"/>
+      <c r="G34" s="237"/>
+      <c r="H34" s="237"/>
+      <c r="I34" s="237"/>
+      <c r="J34" s="237"/>
+      <c r="K34" s="237"/>
+      <c r="L34" s="237"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="237"/>
+      <c r="B35" s="237"/>
+      <c r="C35" s="237"/>
+      <c r="D35" s="237"/>
+      <c r="E35" s="237"/>
+      <c r="F35" s="237"/>
+      <c r="G35" s="237"/>
+      <c r="H35" s="237"/>
+      <c r="I35" s="237"/>
+      <c r="J35" s="237"/>
+      <c r="K35" s="237"/>
+      <c r="L35" s="237"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="237"/>
+      <c r="B36" s="237"/>
+      <c r="C36" s="237"/>
+      <c r="D36" s="237"/>
+      <c r="E36" s="237"/>
+      <c r="F36" s="237"/>
+      <c r="G36" s="237"/>
+      <c r="H36" s="237"/>
+      <c r="I36" s="237"/>
+      <c r="J36" s="237"/>
+      <c r="K36" s="237"/>
+      <c r="L36" s="237"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E40" s="21"/>
     </row>
   </sheetData>
@@ -3750,45 +3769,45 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="11.109375" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="13" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.109375" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="10.6640625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="225" t="s">
+    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="240" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="226"/>
-      <c r="C1" s="226"/>
-      <c r="D1" s="226"/>
-      <c r="E1" s="226"/>
-      <c r="F1" s="226"/>
-      <c r="G1" s="226"/>
-      <c r="H1" s="226"/>
-      <c r="I1" s="226"/>
-      <c r="J1" s="226"/>
-      <c r="K1" s="226"/>
-      <c r="L1" s="226"/>
-      <c r="M1" s="226"/>
-      <c r="N1" s="227"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="241"/>
+      <c r="H1" s="241"/>
+      <c r="I1" s="241"/>
+      <c r="J1" s="241"/>
+      <c r="K1" s="241"/>
+      <c r="L1" s="241"/>
+      <c r="M1" s="241"/>
+      <c r="N1" s="242"/>
       <c r="O1" s="76"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="77"/>
       <c r="B2" s="77"/>
       <c r="C2" s="162"/>
@@ -3806,7 +3825,7 @@
       <c r="O2" s="78"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="80"/>
       <c r="B3" s="80"/>
       <c r="C3" s="164"/>
@@ -3824,7 +3843,7 @@
       <c r="O3" s="78"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="80"/>
       <c r="B4" s="80"/>
       <c r="C4" s="164"/>
@@ -3844,7 +3863,7 @@
       <c r="O4" s="78"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="80"/>
       <c r="B5" s="80"/>
       <c r="C5" s="164"/>
@@ -3862,12 +3881,12 @@
       <c r="O5" s="78"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="80"/>
       <c r="B6" s="80"/>
-      <c r="C6" s="244" t="str">
+      <c r="C6" s="229" t="str">
         <f>'detalle y gastos'!C7</f>
-        <v>Vto. 14/11</v>
+        <v>Vto. 15/12</v>
       </c>
       <c r="D6" s="28"/>
       <c r="E6" s="162"/>
@@ -3883,13 +3902,13 @@
       <c r="O6" s="78"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="81"/>
       <c r="B7" s="81" t="s">
         <v>77</v>
       </c>
       <c r="C7" s="213">
-        <v>696052.93</v>
+        <v>551870.81000000006</v>
       </c>
       <c r="D7" s="28"/>
       <c r="E7" s="162"/>
@@ -3901,7 +3920,7 @@
       <c r="I7" s="162"/>
       <c r="J7" s="162" t="str">
         <f>'detalle y gastos'!C7</f>
-        <v>Vto. 14/11</v>
+        <v>Vto. 15/12</v>
       </c>
       <c r="K7" s="162"/>
       <c r="L7" s="162"/>
@@ -3910,7 +3929,7 @@
       <c r="O7" s="78"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="81"/>
       <c r="B8" s="80" t="s">
         <v>77</v>
@@ -3926,16 +3945,16 @@
         <f>C8-J38</f>
         <v>-329579.71031000023</v>
       </c>
-      <c r="L8" s="229">
+      <c r="L8" s="244">
         <f>C7-J38</f>
-        <v>366473.21968999982</v>
-      </c>
-      <c r="M8" s="229"/>
+        <v>222291.09968999983</v>
+      </c>
+      <c r="M8" s="244"/>
       <c r="N8" s="84"/>
       <c r="O8" s="78"/>
       <c r="P8" s="11"/>
     </row>
-    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="87" t="s">
         <v>78</v>
       </c>
@@ -3980,7 +3999,7 @@
       </c>
       <c r="P9" s="11"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="98">
         <v>1</v>
       </c>
@@ -4020,7 +4039,7 @@
       </c>
       <c r="L10" s="127">
         <f>L$8*E10/S$12</f>
-        <v>18726.781526158993</v>
+        <v>11359.075194158992</v>
       </c>
       <c r="M10" s="107">
         <f>G10-F10</f>
@@ -4028,15 +4047,15 @@
       </c>
       <c r="N10" s="104">
         <f>J10+L10</f>
-        <v>40094.273736158983</v>
+        <v>32726.567404158985</v>
       </c>
       <c r="O10" s="97">
         <f>N10+'prorrateo '!L3</f>
-        <v>145599.85312585899</v>
+        <v>138232.14679385899</v>
       </c>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="99">
         <v>2</v>
       </c>
@@ -4076,7 +4095,7 @@
       </c>
       <c r="L11" s="127">
         <f t="shared" ref="L11:L36" si="3">L$8*E11/S$12</f>
-        <v>18653.48688222099</v>
+        <v>11314.616974220991</v>
       </c>
       <c r="M11" s="107">
         <f t="shared" ref="M11:M26" si="4">G11-F11</f>
@@ -4084,15 +4103,15 @@
       </c>
       <c r="N11" s="104">
         <f t="shared" ref="N11:N25" si="5">J11+L11</f>
-        <v>40562.130082220981</v>
+        <v>33223.260174220981</v>
       </c>
       <c r="O11" s="97">
         <f>N11+'prorrateo '!L4</f>
-        <v>145081.14164652099</v>
+        <v>137742.271738521</v>
       </c>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="98">
         <v>3</v>
       </c>
@@ -4132,7 +4151,7 @@
       </c>
       <c r="L12" s="127">
         <f t="shared" si="3"/>
-        <v>18470.25027237599</v>
+        <v>11203.471424375992</v>
       </c>
       <c r="M12" s="107">
         <f>G12-F12</f>
@@ -4140,18 +4159,18 @@
       </c>
       <c r="N12" s="104">
         <f t="shared" si="5"/>
-        <v>31093.980472376003</v>
+        <v>23827.201624376008</v>
       </c>
       <c r="O12" s="97">
         <f>N12+'prorrateo '!L5</f>
-        <v>438749.98678357602</v>
+        <v>431483.20793557604</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="98">
         <v>4</v>
       </c>
@@ -4170,7 +4189,7 @@
       <c r="F13" s="103">
         <v>1058.9000000000001</v>
       </c>
-      <c r="G13" s="236">
+      <c r="G13" s="221">
         <v>1204.5999999999999</v>
       </c>
       <c r="H13" s="104">
@@ -4191,7 +4210,7 @@
       </c>
       <c r="L13" s="127">
         <f t="shared" si="3"/>
-        <v>19093.25474584899</v>
+        <v>11581.366293848991</v>
       </c>
       <c r="M13" s="169">
         <f t="shared" si="4"/>
@@ -4199,15 +4218,15 @@
       </c>
       <c r="N13" s="104">
         <f t="shared" si="5"/>
-        <v>32758.020645848974</v>
+        <v>25246.132193848975</v>
       </c>
       <c r="O13" s="97">
         <f>N13+'prorrateo '!L6</f>
-        <v>140492.43916254898</v>
+        <v>132980.550710549</v>
       </c>
       <c r="P13" s="11"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="98">
         <v>6</v>
       </c>
@@ -4226,7 +4245,7 @@
       <c r="F14" s="103">
         <v>1645.5</v>
       </c>
-      <c r="G14" s="236">
+      <c r="G14" s="221">
         <v>1814</v>
       </c>
       <c r="H14" s="104">
@@ -4247,7 +4266,7 @@
       </c>
       <c r="L14" s="127">
         <f t="shared" si="3"/>
-        <v>18726.781526158993</v>
+        <v>11359.075194158992</v>
       </c>
       <c r="M14" s="107">
         <f t="shared" si="4"/>
@@ -4255,15 +4274,15 @@
       </c>
       <c r="N14" s="104">
         <f t="shared" si="5"/>
-        <v>34529.891026158992</v>
+        <v>27162.18469415899</v>
       </c>
       <c r="O14" s="97">
         <f>N14+'prorrateo '!L7</f>
-        <v>140196.47041585902</v>
+        <v>132828.76408385899</v>
       </c>
       <c r="P14" s="11"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="98">
         <v>7</v>
       </c>
@@ -4303,7 +4322,7 @@
       </c>
       <c r="L15" s="127">
         <f t="shared" si="3"/>
-        <v>18653.48688222099</v>
+        <v>11314.616974220991</v>
       </c>
       <c r="M15" s="107">
         <f t="shared" si="4"/>
@@ -4311,14 +4330,14 @@
       </c>
       <c r="N15" s="104">
         <f t="shared" si="5"/>
-        <v>35638.312582220984</v>
+        <v>28299.442674220983</v>
       </c>
       <c r="O15" s="97">
         <f>N15+'prorrateo '!L8</f>
-        <v>140891.32414652099</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+        <v>133552.45423852099</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="98">
         <v>8</v>
       </c>
@@ -4358,7 +4377,7 @@
       </c>
       <c r="L16" s="127">
         <f t="shared" si="3"/>
-        <v>18726.781526158993</v>
+        <v>11359.075194158992</v>
       </c>
       <c r="M16" s="107">
         <f t="shared" si="4"/>
@@ -4366,14 +4385,14 @@
       </c>
       <c r="N16" s="104">
         <f t="shared" si="5"/>
-        <v>36452.524526158995</v>
+        <v>29084.818194158994</v>
       </c>
       <c r="O16" s="97">
         <f>N16+'prorrateo '!L9</f>
-        <v>142119.10391585901</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+        <v>134751.39758385901</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="98">
         <v>9</v>
       </c>
@@ -4413,7 +4432,7 @@
       </c>
       <c r="L17" s="200">
         <f t="shared" si="3"/>
-        <v>18653.48688222099</v>
+        <v>11314.616974220991</v>
       </c>
       <c r="M17" s="201">
         <f t="shared" si="4"/>
@@ -4421,14 +4440,14 @@
       </c>
       <c r="N17" s="196">
         <f t="shared" si="5"/>
-        <v>24383.872582221025</v>
+        <v>17045.002674221025</v>
       </c>
       <c r="O17" s="97">
         <f>N17+'prorrateo '!L10</f>
-        <v>129636.88414652103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+        <v>122298.01423852102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="98">
         <v>10</v>
       </c>
@@ -4468,7 +4487,7 @@
       </c>
       <c r="L18" s="127">
         <f t="shared" si="3"/>
-        <v>18470.25027237599</v>
+        <v>11203.471424375992</v>
       </c>
       <c r="M18" s="107">
         <f t="shared" si="4"/>
@@ -4476,14 +4495,14 @@
       </c>
       <c r="N18" s="104">
         <f t="shared" si="5"/>
-        <v>36289.780272375996</v>
+        <v>29023.001424375994</v>
       </c>
       <c r="O18" s="97">
         <f>N18+'prorrateo '!L11</f>
-        <v>140508.87227317601</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133242.09342517599</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="98">
         <v>11</v>
       </c>
@@ -4523,7 +4542,7 @@
       </c>
       <c r="L19" s="127">
         <f t="shared" si="3"/>
-        <v>19093.25474584899</v>
+        <v>11581.366293848991</v>
       </c>
       <c r="M19" s="107">
         <f>G19-F19</f>
@@ -4531,14 +4550,14 @@
       </c>
       <c r="N19" s="104">
         <f t="shared" si="5"/>
-        <v>69025.453545849043</v>
+        <v>61513.565093849043</v>
       </c>
       <c r="O19" s="97">
         <f>N19+'prorrateo '!L12</f>
-        <v>176759.87206254905</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>169247.98361054907</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="98">
         <v>12</v>
       </c>
@@ -4578,7 +4597,7 @@
       </c>
       <c r="L20" s="127">
         <f t="shared" si="3"/>
-        <v>18726.781526158993</v>
+        <v>11359.075194158992</v>
       </c>
       <c r="M20" s="107">
         <f t="shared" si="4"/>
@@ -4586,44 +4605,44 @@
       </c>
       <c r="N20" s="104">
         <f t="shared" si="5"/>
-        <v>28930.807126159008</v>
+        <v>21563.100794159007</v>
       </c>
       <c r="O20" s="97">
         <f>N20+'prorrateo '!L13</f>
-        <v>134597.38651585902</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+        <v>127229.68018385902</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="98">
         <v>13</v>
       </c>
       <c r="B21" s="89">
         <v>13</v>
       </c>
-      <c r="C21" s="237" t="s">
+      <c r="C21" s="222" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="238" t="s">
+      <c r="D21" s="223" t="s">
         <v>49</v>
       </c>
-      <c r="E21" s="239">
+      <c r="E21" s="224">
         <v>5.09</v>
       </c>
-      <c r="F21" s="240">
+      <c r="F21" s="225">
         <v>3851</v>
       </c>
-      <c r="G21" s="240">
+      <c r="G21" s="225">
         <v>4112.1000000000004</v>
       </c>
       <c r="H21" s="148">
         <f t="shared" si="1"/>
         <v>261.10000000000036</v>
       </c>
-      <c r="I21" s="241">
+      <c r="I21" s="226">
         <f t="shared" si="0"/>
         <v>18.277000000000026</v>
       </c>
-      <c r="J21" s="242">
+      <c r="J21" s="227">
         <f t="shared" si="2"/>
         <v>24487.785700000037</v>
       </c>
@@ -4633,7 +4652,7 @@
       </c>
       <c r="L21" s="150">
         <f t="shared" si="3"/>
-        <v>18653.48688222099</v>
+        <v>11314.616974220991</v>
       </c>
       <c r="M21" s="151">
         <f t="shared" si="4"/>
@@ -4641,14 +4660,14 @@
       </c>
       <c r="N21" s="148">
         <f t="shared" si="5"/>
-        <v>43141.272582221027</v>
+        <v>35802.402674221026</v>
       </c>
       <c r="O21" s="97">
         <f>N21+'prorrateo '!L14</f>
-        <v>414651.23314092105</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+        <v>407312.36323292105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="98">
         <v>14</v>
       </c>
@@ -4688,7 +4707,7 @@
       </c>
       <c r="L22" s="127">
         <f t="shared" si="3"/>
-        <v>18470.25027237599</v>
+        <v>11203.471424375992</v>
       </c>
       <c r="M22" s="107">
         <f t="shared" si="4"/>
@@ -4696,14 +4715,14 @@
       </c>
       <c r="N22" s="104">
         <f t="shared" si="5"/>
-        <v>28646.139772375991</v>
+        <v>21379.360924375993</v>
       </c>
       <c r="O22" s="97">
         <f>N22+'prorrateo '!L15</f>
-        <v>132865.23165317596</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+        <v>125598.45280517597</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="98">
         <v>15</v>
       </c>
@@ -4743,7 +4762,7 @@
       </c>
       <c r="L23" s="127">
         <f t="shared" si="3"/>
-        <v>19093.25474584899</v>
+        <v>11581.366293848991</v>
       </c>
       <c r="M23" s="107">
         <f t="shared" si="4"/>
@@ -4751,14 +4770,14 @@
       </c>
       <c r="N23" s="104">
         <f t="shared" si="5"/>
-        <v>43102.726745848995</v>
+        <v>35590.838293848996</v>
       </c>
       <c r="O23" s="97">
         <f>N23+'prorrateo '!L16</f>
-        <v>150837.14526254899</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+        <v>143325.25681054901</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="98">
         <v>16</v>
       </c>
@@ -4798,7 +4817,7 @@
       </c>
       <c r="L24" s="127">
         <f t="shared" si="3"/>
-        <v>18470.25027237599</v>
+        <v>11203.471424375992</v>
       </c>
       <c r="M24" s="107">
         <f t="shared" si="4"/>
@@ -4806,14 +4825,14 @@
       </c>
       <c r="N24" s="104">
         <f t="shared" si="5"/>
-        <v>27933.358572375997</v>
+        <v>20666.579724376003</v>
       </c>
       <c r="O24" s="97">
         <f>N24+'prorrateo '!L17</f>
-        <v>132152.450573176</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+        <v>124885.67172517601</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="98">
         <v>17</v>
       </c>
@@ -4853,7 +4872,7 @@
       </c>
       <c r="L25" s="127">
         <f t="shared" si="3"/>
-        <v>19093.25474584899</v>
+        <v>11581.366293848991</v>
       </c>
       <c r="M25" s="107">
         <f t="shared" si="4"/>
@@ -4861,14 +4880,14 @@
       </c>
       <c r="N25" s="104">
         <f t="shared" si="5"/>
-        <v>36003.050845848986</v>
+        <v>28491.162393848987</v>
       </c>
       <c r="O25" s="97">
         <f>N25+'prorrateo '!L18</f>
-        <v>143737.46936254899</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+        <v>136225.580910549</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="98">
         <v>18</v>
       </c>
@@ -4908,7 +4927,7 @@
       </c>
       <c r="L26" s="127">
         <f t="shared" si="3"/>
-        <v>27119.01825705999</v>
+        <v>16449.541377059988</v>
       </c>
       <c r="M26" s="107">
         <f t="shared" si="4"/>
@@ -4916,14 +4935,14 @@
       </c>
       <c r="N26" s="104">
         <f>J26+L26</f>
-        <v>67888.227157060057</v>
+        <v>57218.750277060055</v>
       </c>
       <c r="O26" s="97">
         <f>N26+'prorrateo '!L19</f>
-        <v>220908.32255506006</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>210238.84567506006</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="98">
         <v>19</v>
       </c>
@@ -4951,21 +4970,21 @@
       <c r="K27" s="199"/>
       <c r="L27" s="200">
         <f t="shared" si="3"/>
-        <v>3957.9107726519987</v>
+        <v>2400.7438766519986</v>
       </c>
       <c r="M27" s="201">
         <v>0</v>
       </c>
       <c r="N27" s="196">
         <f t="shared" ref="N27:N37" si="6">J27+L27</f>
-        <v>3957.9107726519987</v>
+        <v>2400.7438766519986</v>
       </c>
       <c r="O27" s="97">
         <f>N27+'prorrateo '!L20</f>
-        <v>26290.573344252</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+        <v>24733.406448252001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="98">
         <v>20</v>
       </c>
@@ -4990,21 +5009,21 @@
       <c r="K28" s="106"/>
       <c r="L28" s="127">
         <f t="shared" si="3"/>
-        <v>3957.9107726519987</v>
+        <v>2400.7438766519986</v>
       </c>
       <c r="M28" s="107">
         <v>0</v>
       </c>
       <c r="N28" s="104">
         <f t="shared" si="6"/>
-        <v>3957.9107726519987</v>
+        <v>2400.7438766519986</v>
       </c>
       <c r="O28" s="97">
         <f>N28+'prorrateo '!L21</f>
-        <v>26290.573344252</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+        <v>24733.406448252001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="98"/>
       <c r="B29" s="90"/>
       <c r="C29" s="159" t="s">
@@ -5022,21 +5041,21 @@
       <c r="K29" s="149"/>
       <c r="L29" s="150">
         <f t="shared" si="3"/>
-        <v>3957.9107726519987</v>
+        <v>2400.7438766519986</v>
       </c>
       <c r="M29" s="151">
         <v>0</v>
       </c>
       <c r="N29" s="148">
         <f t="shared" si="6"/>
-        <v>3957.9107726519987</v>
+        <v>2400.7438766519986</v>
       </c>
       <c r="O29" s="97">
         <f>N29+'prorrateo '!L22</f>
-        <v>266556.42578905204</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+        <v>264999.258893052</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="98"/>
       <c r="B30" s="90"/>
       <c r="C30" s="170" t="s">
@@ -5054,21 +5073,21 @@
       <c r="K30" s="106"/>
       <c r="L30" s="127">
         <f t="shared" si="3"/>
-        <v>3957.9107726519987</v>
+        <v>2400.7438766519986</v>
       </c>
       <c r="M30" s="107">
         <v>0</v>
       </c>
       <c r="N30" s="104">
         <f t="shared" si="6"/>
-        <v>3957.9107726519987</v>
+        <v>2400.7438766519986</v>
       </c>
       <c r="O30" s="97">
         <f>N30+'prorrateo '!L23</f>
-        <v>58420.449533052008</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+        <v>56863.282637052005</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="98"/>
       <c r="B31" s="90"/>
       <c r="C31" s="170" t="s">
@@ -5088,23 +5107,23 @@
       <c r="K31" s="106"/>
       <c r="L31" s="127">
         <f t="shared" si="3"/>
-        <v>3957.9107726519987</v>
+        <v>2400.7438766519986</v>
       </c>
       <c r="M31" s="107">
         <v>0</v>
       </c>
       <c r="N31" s="104">
         <f t="shared" si="6"/>
-        <v>3957.9107726519987</v>
+        <v>2400.7438766519986</v>
       </c>
       <c r="O31" s="97">
         <f>N31+'prorrateo '!L24</f>
-        <v>26290.573344252</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+        <v>24733.406448252001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="99"/>
-      <c r="B32" s="243"/>
+      <c r="B32" s="228"/>
       <c r="C32" s="159" t="s">
         <v>70</v>
       </c>
@@ -5122,21 +5141,21 @@
       <c r="K32" s="149"/>
       <c r="L32" s="150">
         <f t="shared" si="3"/>
-        <v>3957.9107726519987</v>
+        <v>2400.7438766519986</v>
       </c>
       <c r="M32" s="151">
         <v>0</v>
       </c>
       <c r="N32" s="148">
         <f t="shared" si="6"/>
-        <v>3957.9107726519987</v>
+        <v>2400.7438766519986</v>
       </c>
       <c r="O32" s="97">
         <f>N32+'prorrateo '!L25</f>
-        <v>82785.166013052003</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+        <v>81227.999117051993</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="98"/>
       <c r="B33" s="90"/>
       <c r="C33" s="130" t="s">
@@ -5156,21 +5175,21 @@
       <c r="K33" s="113"/>
       <c r="L33" s="127">
         <f t="shared" si="3"/>
-        <v>3957.9107726519987</v>
+        <v>2400.7438766519986</v>
       </c>
       <c r="M33" s="107">
         <v>0</v>
       </c>
       <c r="N33" s="104">
         <f t="shared" si="6"/>
-        <v>3957.9107726519987</v>
+        <v>2400.7438766519986</v>
       </c>
       <c r="O33" s="97">
         <f>N33+'prorrateo '!L26</f>
-        <v>26290.573344252</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+        <v>24733.406448252001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="98"/>
       <c r="B34" s="90"/>
       <c r="C34" s="130" t="s">
@@ -5190,21 +5209,21 @@
       <c r="K34" s="113"/>
       <c r="L34" s="127">
         <f t="shared" si="3"/>
-        <v>3957.9107726519987</v>
+        <v>2400.7438766519986</v>
       </c>
       <c r="M34" s="107">
         <v>0</v>
       </c>
       <c r="N34" s="104">
         <f t="shared" si="6"/>
-        <v>3957.9107726519987</v>
+        <v>2400.7438766519986</v>
       </c>
       <c r="O34" s="97">
         <f>N34+'prorrateo '!L27</f>
-        <v>26290.573344252</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+        <v>24733.406448252001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="98">
         <v>21</v>
       </c>
@@ -5229,21 +5248,21 @@
       <c r="K35" s="106"/>
       <c r="L35" s="127">
         <f t="shared" si="3"/>
-        <v>3957.9107726519987</v>
+        <v>2400.7438766519986</v>
       </c>
       <c r="M35" s="107">
         <v>0</v>
       </c>
       <c r="N35" s="104">
         <f t="shared" si="6"/>
-        <v>3957.9107726519987</v>
+        <v>2400.7438766519986</v>
       </c>
       <c r="O35" s="97">
         <f>N35+'prorrateo '!L28</f>
-        <v>26290.573344252</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+        <v>24733.406448252001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="98">
         <v>22</v>
       </c>
@@ -5270,21 +5289,21 @@
       <c r="K36" s="106"/>
       <c r="L36" s="127">
         <f t="shared" si="3"/>
-        <v>3957.9107726519987</v>
+        <v>2400.7438766519986</v>
       </c>
       <c r="M36" s="107">
         <v>0</v>
       </c>
       <c r="N36" s="104">
         <f t="shared" si="6"/>
-        <v>3957.9107726519987</v>
+        <v>2400.7438766519986</v>
       </c>
       <c r="O36" s="97">
         <f>N36+'prorrateo '!L29</f>
-        <v>26290.573344252</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+        <v>24733.406448252001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="98">
         <v>23</v>
       </c>
@@ -5314,7 +5333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="98">
         <v>24</v>
       </c>
@@ -5333,16 +5352,16 @@
       <c r="K38" s="113"/>
       <c r="L38" s="113">
         <f>SUM(L10:L37)</f>
-        <v>366473.21969</v>
+        <v>222291.09968999989</v>
       </c>
       <c r="M38" s="114"/>
       <c r="N38" s="110">
         <f>SUM(N10:N37)</f>
-        <v>696052.93000000017</v>
+        <v>551870.80999999982</v>
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="78"/>
       <c r="C39" s="91"/>
       <c r="D39" s="92"/>
@@ -5361,47 +5380,47 @@
       <c r="K39" s="94"/>
       <c r="L39" s="133">
         <f>L38+J38</f>
-        <v>696052.93000000017</v>
+        <v>551870.81000000006</v>
       </c>
       <c r="M39" s="93"/>
       <c r="N39" s="93"/>
       <c r="O39" s="79"/>
     </row>
-    <row r="40" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="95" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="228"/>
-      <c r="D40" s="226"/>
-      <c r="E40" s="226"/>
-      <c r="F40" s="226"/>
-      <c r="G40" s="226"/>
-      <c r="H40" s="226"/>
-      <c r="I40" s="226"/>
-      <c r="J40" s="226"/>
-      <c r="K40" s="226"/>
-      <c r="L40" s="226"/>
-      <c r="M40" s="226"/>
-      <c r="N40" s="226"/>
+      <c r="C40" s="243"/>
+      <c r="D40" s="241"/>
+      <c r="E40" s="241"/>
+      <c r="F40" s="241"/>
+      <c r="G40" s="241"/>
+      <c r="H40" s="241"/>
+      <c r="I40" s="241"/>
+      <c r="J40" s="241"/>
+      <c r="K40" s="241"/>
+      <c r="L40" s="241"/>
+      <c r="M40" s="241"/>
+      <c r="N40" s="241"/>
       <c r="O40" s="95"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="H41" s="79"/>
       <c r="J41" s="96"/>
       <c r="K41" s="96"/>
       <c r="L41" s="96"/>
       <c r="N41" s="97"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="L44" s="152"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="L45" s="96"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E46" s="153"/>
       <c r="F46" s="153"/>
       <c r="G46" s="153"/>

--- a/ROSALES/Noviembre/expensas rosales Noviembre.xlsx
+++ b/ROSALES/Noviembre/expensas rosales Noviembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\ROSALES\Noviembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E54E42-B564-4C6B-B87B-B344374D11FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E196E9E5-C8BC-4115-8DAB-5BC82CB633CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Edesur" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$64</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$N$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$L$37</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="124">
   <si>
     <t>TOTAL</t>
   </si>
@@ -348,9 +348,6 @@
   </si>
   <si>
     <t>Anabella</t>
-  </si>
-  <si>
-    <t>Articulos de limpieza</t>
   </si>
   <si>
     <t xml:space="preserve">CAJA NO REAL, YA QUE DE ESTE FONDO SE PAGA EDESUR DE LAS UNIDADES
@@ -373,9 +370,6 @@
     <t>Fumigacion</t>
   </si>
   <si>
-    <t>ADELANTO PAGO 2 - TERRAZA</t>
-  </si>
-  <si>
     <t>EXTRAORD.</t>
   </si>
   <si>
@@ -385,15 +379,6 @@
     <t>Subidos en 0CT 2025</t>
   </si>
   <si>
-    <t>TSG MES 9</t>
-  </si>
-  <si>
-    <t>ARBA revaluo 2024 - Ultimo 2024, solo resta 2025</t>
-  </si>
-  <si>
-    <t>CUOTA PLAN DE PAGOS (3/6)</t>
-  </si>
-  <si>
     <t>PUNITORIOS MAL COBRADOS</t>
   </si>
   <si>
@@ -406,7 +391,16 @@
     <t>EGRESOS DEL MES DE NOVIEMBRE</t>
   </si>
   <si>
-    <t>Arreglo Sr. Leo - Mano de obra y materiales</t>
+    <t xml:space="preserve">Cuota 1 revaluo ARBA </t>
+  </si>
+  <si>
+    <t>Sr. Leonardo Balcazza - Mano de obra y materiales - Arreglo medianera</t>
+  </si>
+  <si>
+    <t>TSG MES 10</t>
+  </si>
+  <si>
+    <t>CUOTA PLAN DE PAGOS (4/6)</t>
   </si>
 </sst>
 </file>
@@ -428,7 +422,7 @@
     <numFmt numFmtId="173" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="174" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -649,12 +643,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1036,7 +1024,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="248">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1251,7 +1239,6 @@
     <xf numFmtId="2" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1307,14 +1294,8 @@
     <xf numFmtId="171" fontId="25" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="25" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="25" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="174" fontId="9" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="20" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1353,17 +1334,12 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="2" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="11" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="32" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1372,11 +1348,9 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1389,6 +1363,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="11" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1429,11 +1412,6 @@
     </xf>
     <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1852,17 +1830,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F69"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:F65"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -1870,495 +1848,462 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="15"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="36"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
       <c r="B17" s="37"/>
       <c r="C17" s="33"/>
       <c r="D17" s="4"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
         <v>105</v>
       </c>
       <c r="B18" s="38"/>
-      <c r="C18" s="246">
+      <c r="C18" s="223">
         <v>76654</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="247">
+      <c r="C19" s="224">
         <v>316973.44</v>
       </c>
       <c r="D19" s="20"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="B20" s="39"/>
-      <c r="C20" s="206">
-        <v>610197</v>
+      <c r="C20" s="223">
+        <v>80000</v>
       </c>
       <c r="D20" s="20"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="B21" s="39"/>
-      <c r="C21" s="246">
-        <v>80000</v>
-      </c>
-      <c r="D21" s="20"/>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C21" s="223">
+        <v>15748</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="6"/>
+      <c r="F21" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="33">
-        <v>15748</v>
-      </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="6"/>
-      <c r="F22" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="39" t="s">
+      <c r="B22" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="33">
+      <c r="C22" s="223">
         <v>83400</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="40"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="23">
-        <f>SUM(C17:C23)</f>
-        <v>1182972.44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="35" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="40"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="225">
+        <f>SUM(C17:C22)</f>
+        <v>572775.43999999994</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="176"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="45"/>
+      <c r="F24" s="12"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="42"/>
+      <c r="C25" s="223">
+        <f>349151.87+ (349151.87*10%)</f>
+        <v>384067.05699999997</v>
+      </c>
       <c r="D25" s="45"/>
       <c r="F25" s="12"/>
     </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B26" s="42"/>
-      <c r="C26" s="33">
-        <f>349151.87+ (349151.87*10%)</f>
-        <v>384067.05699999997</v>
+      <c r="C26" s="223">
+        <v>5684</v>
       </c>
       <c r="D26" s="45"/>
       <c r="F26" s="12"/>
     </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="28" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="B27" s="42"/>
-      <c r="C27" s="33">
-        <v>5684</v>
-      </c>
-      <c r="D27" s="45"/>
+      <c r="C27" s="223">
+        <v>55000</v>
+      </c>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="245" t="s">
-        <v>125</v>
-      </c>
-      <c r="B28" s="138"/>
-      <c r="C28" s="246">
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" s="39"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="12"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="40"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="23">
+        <f>SUM(C24:C28)</f>
+        <v>444751.05699999997</v>
+      </c>
+      <c r="F29" s="12"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="30"/>
+      <c r="C30" s="43">
+        <f>+C29+C23</f>
+        <v>1017526.497</v>
+      </c>
+      <c r="F30" s="12"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C31" s="24"/>
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="24"/>
+      <c r="F32" s="12"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="B33" s="28"/>
+      <c r="C33" s="223">
         <v>610000</v>
       </c>
-      <c r="D28" s="45"/>
-      <c r="F28" s="12"/>
-    </row>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="174" t="s">
+      <c r="F33" s="12"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="B34" s="28"/>
+      <c r="C34" s="226">
+        <v>1034026.5</v>
+      </c>
+      <c r="F34" s="12"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="28"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="34"/>
+      <c r="F35" s="12"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C36" s="25"/>
+      <c r="F36" s="12"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="173" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" s="173"/>
+      <c r="C37" s="174">
+        <v>0</v>
+      </c>
+      <c r="F37" s="12"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C38" s="25"/>
+      <c r="F38" s="12"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" s="13"/>
+      <c r="C39" s="14">
+        <f>+C33+C34+C35+C38</f>
+        <v>1644026.5</v>
+      </c>
+      <c r="E39" s="6"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" s="18"/>
+      <c r="C41" s="19">
+        <f>+C39+C30</f>
+        <v>2661552.997</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="231" t="s">
+        <v>109</v>
+      </c>
+      <c r="B43" s="232"/>
+      <c r="C43" s="232"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="232"/>
+      <c r="B44" s="232"/>
+      <c r="C44" s="232"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="232"/>
+      <c r="B45" s="232"/>
+      <c r="C45" s="232"/>
+    </row>
+    <row r="46" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="232"/>
+      <c r="B46" s="232"/>
+      <c r="C46" s="232"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+    </row>
+    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="4"/>
+      <c r="C47" s="154"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="202" t="s">
+        <v>100</v>
+      </c>
+      <c r="B48" s="28"/>
+      <c r="C48" s="203">
+        <v>1081522.6958899994</v>
+      </c>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="202" t="s">
+        <v>119</v>
+      </c>
+      <c r="B49" s="28"/>
+      <c r="C49" s="31">
+        <f>-(C41-C28)</f>
+        <v>-2661552.997</v>
+      </c>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="202" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" s="28"/>
+      <c r="C50" s="204">
+        <f>'prorrateo '!F31</f>
+        <v>2610074.1626310009</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="202" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" s="28"/>
+      <c r="C51" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="202" t="s">
+        <v>123</v>
+      </c>
+      <c r="B52" s="28"/>
+      <c r="C52" s="204">
+        <v>107386.2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="202" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" s="28"/>
+      <c r="C53" s="203">
+        <f>SUM(C48:C52)</f>
+        <v>1137430.0615210002</v>
+      </c>
+      <c r="D53" s="5"/>
+    </row>
+    <row r="54" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="9"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="10"/>
+    </row>
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="227"/>
+      <c r="B55" s="227"/>
+      <c r="C55" s="227"/>
+      <c r="F55" s="44"/>
+    </row>
+    <row r="56" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="228"/>
+      <c r="B56" s="228"/>
+      <c r="C56" s="228"/>
+    </row>
+    <row r="57" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B57" s="27"/>
+      <c r="C57" s="29"/>
+    </row>
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B58" s="28"/>
+      <c r="C58" s="31">
+        <f>-C39</f>
+        <v>-1644026.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="28"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="31"/>
+    </row>
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="28"/>
+      <c r="B60" s="28"/>
+      <c r="C60" s="32"/>
+    </row>
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="155" t="s">
+        <v>0</v>
+      </c>
+      <c r="B61" s="156"/>
+      <c r="C61" s="157">
+        <f>SUM(C57:C60)</f>
+        <v>-1644026.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="229" t="s">
         <v>107</v>
       </c>
-      <c r="B29" s="138"/>
-      <c r="C29" s="33">
-        <v>41110</v>
-      </c>
-      <c r="F29" s="12"/>
-    </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="B30" s="42"/>
-      <c r="C30" s="33">
-        <v>55000</v>
-      </c>
-      <c r="F30" s="12"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="B31" s="39"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="12"/>
-    </row>
-    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="40"/>
-      <c r="B32" s="41"/>
-      <c r="C32" s="23">
-        <f>SUM(C25:C31)</f>
-        <v>1095861.057</v>
-      </c>
-      <c r="F32" s="12"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="30"/>
-      <c r="C33" s="43">
-        <f>+C32+C24</f>
-        <v>2278833.497</v>
-      </c>
-      <c r="F33" s="12"/>
-    </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C34" s="24"/>
-      <c r="F34" s="12"/>
-    </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" s="24"/>
-      <c r="F35" s="12"/>
-    </row>
-    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="28"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="33"/>
-      <c r="F36" s="12"/>
-    </row>
-    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="28"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="34"/>
-      <c r="F37" s="12"/>
-    </row>
-    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="28"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="34"/>
-      <c r="F38" s="12"/>
-    </row>
-    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C39" s="25"/>
-      <c r="F39" s="12"/>
-    </row>
-    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="177" t="s">
-        <v>111</v>
-      </c>
-      <c r="B40" s="177"/>
-      <c r="C40" s="178">
-        <v>400000</v>
-      </c>
-      <c r="F40" s="12"/>
-    </row>
-    <row r="41" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C41" s="25"/>
-      <c r="F41" s="12"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="14">
-        <f>+C36+C37+C38+C41</f>
-        <v>0</v>
-      </c>
-      <c r="E42" s="6"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B44" s="18"/>
-      <c r="C44" s="19">
-        <f>+C42+C33</f>
-        <v>2278833.497</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="234" t="s">
-        <v>110</v>
-      </c>
-      <c r="B46" s="235"/>
-      <c r="C46" s="235"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="235"/>
-      <c r="B47" s="235"/>
-      <c r="C47" s="235"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="235"/>
-      <c r="B48" s="235"/>
-      <c r="C48" s="235"/>
-    </row>
-    <row r="49" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="235"/>
-      <c r="B49" s="235"/>
-      <c r="C49" s="235"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-    </row>
-    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="4"/>
-      <c r="C50" s="155"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="208" t="s">
-        <v>100</v>
-      </c>
-      <c r="B51" s="28"/>
-      <c r="C51" s="209">
-        <v>149754.72</v>
-      </c>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="208" t="s">
-        <v>124</v>
-      </c>
-      <c r="B52" s="28"/>
-      <c r="C52" s="31">
-        <f>-(C33-C31)</f>
-        <v>-2278833.497</v>
-      </c>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="208" t="s">
-        <v>96</v>
-      </c>
-      <c r="B53" s="28"/>
-      <c r="C53" s="210">
-        <f>'prorrateo '!F31</f>
-        <v>2872567.6936899996</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="208" t="s">
-        <v>121</v>
-      </c>
-      <c r="B54" s="28"/>
-      <c r="C54" s="217">
-        <v>-4346.7907999999998</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="208" t="s">
-        <v>120</v>
-      </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="210">
-        <v>107386.2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="208" t="s">
-        <v>114</v>
-      </c>
-      <c r="B56" s="28"/>
-      <c r="C56" s="211">
-        <v>-376000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="208" t="s">
-        <v>8</v>
-      </c>
-      <c r="B57" s="28"/>
-      <c r="C57" s="209">
-        <f>SUM(C49:C56)</f>
-        <v>470528.32588999986</v>
-      </c>
-      <c r="D57" s="5"/>
-    </row>
-    <row r="58" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="9"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="10"/>
-    </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="230"/>
-      <c r="B59" s="230"/>
-      <c r="C59" s="230"/>
-      <c r="F59" s="44"/>
-    </row>
-    <row r="60" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="231"/>
-      <c r="B60" s="231"/>
-      <c r="C60" s="231"/>
-    </row>
-    <row r="61" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B61" s="27"/>
-      <c r="C61" s="29"/>
-    </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B62" s="28"/>
-      <c r="C62" s="31">
-        <f>-C42</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="28"/>
-      <c r="B63" s="28"/>
-      <c r="C63" s="31"/>
-    </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="28"/>
-      <c r="B64" s="28"/>
-      <c r="C64" s="32"/>
-    </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="156" t="s">
-        <v>0</v>
-      </c>
-      <c r="B65" s="157"/>
-      <c r="C65" s="158">
-        <f>SUM(C61:C64)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="232" t="s">
-        <v>108</v>
-      </c>
-      <c r="B66" s="233"/>
-      <c r="C66" s="233"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="233"/>
-      <c r="B67" s="233"/>
-      <c r="C67" s="233"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="233"/>
-      <c r="B68" s="233"/>
-      <c r="C68" s="233"/>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="8"/>
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
+      <c r="B62" s="230"/>
+      <c r="C62" s="230"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="230"/>
+      <c r="B63" s="230"/>
+      <c r="C63" s="230"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="230"/>
+      <c r="B64" s="230"/>
+      <c r="C64" s="230"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A59:C60"/>
-    <mergeCell ref="A66:C68"/>
-    <mergeCell ref="A46:C49"/>
+    <mergeCell ref="A55:C56"/>
+    <mergeCell ref="A62:C64"/>
+    <mergeCell ref="A43:C46"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <hyperlinks>
@@ -2377,58 +2322,58 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="11.5546875" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="11"/>
+    <col min="1" max="1" width="19.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="11"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="236">
+      <c r="B1" s="233">
         <f>D1-K1</f>
         <v>1057642.1270000001</v>
       </c>
-      <c r="C1" s="236"/>
-      <c r="D1" s="139">
+      <c r="C1" s="233"/>
+      <c r="D1" s="138">
         <v>1667839.1270000001</v>
       </c>
       <c r="E1" t="s">
         <v>102</v>
       </c>
-      <c r="G1" s="238">
+      <c r="G1" s="235">
         <v>400000</v>
       </c>
-      <c r="H1" s="238"/>
-      <c r="I1" s="239" t="s">
-        <v>116</v>
-      </c>
-      <c r="J1" s="239"/>
-      <c r="K1" s="236">
+      <c r="H1" s="235"/>
+      <c r="I1" s="236" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1" s="236"/>
+      <c r="K1" s="233">
         <f>M1</f>
         <v>610197</v>
       </c>
-      <c r="L1" s="236"/>
+      <c r="L1" s="233"/>
       <c r="M1">
         <v>610197</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
         <v>26</v>
       </c>
@@ -2450,23 +2395,23 @@
       <c r="G2" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="207" t="s">
+      <c r="H2" s="201" t="s">
         <v>92</v>
       </c>
       <c r="I2" s="50" t="s">
         <v>104</v>
       </c>
       <c r="J2" s="50" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K2" s="50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L2" s="51" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
         <v>31</v>
       </c>
@@ -2480,15 +2425,15 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E3" s="129">
-        <v>146174.91749000002</v>
-      </c>
-      <c r="F3" s="175">
-        <f>E3+161</f>
-        <v>146335.91749000002</v>
+        <v>105505.57938970001</v>
+      </c>
+      <c r="F3" s="220">
+        <f>E3</f>
+        <v>105505.57938970001</v>
       </c>
       <c r="G3" s="56">
         <f>E3-F3</f>
-        <v>-161</v>
+        <v>0</v>
       </c>
       <c r="H3" s="56">
         <f>IF(G3&gt;0,G3*4%,0)</f>
@@ -2508,11 +2453,11 @@
       </c>
       <c r="L3" s="57">
         <f>I3+G3+K3+J3+H3</f>
-        <v>105505.57938970001</v>
+        <v>105666.57938970001</v>
       </c>
       <c r="M3" s="44"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="58" t="s">
         <v>33</v>
       </c>
@@ -2526,15 +2471,15 @@
         <v>5.09</v>
       </c>
       <c r="E4" s="129">
-        <v>145602.80430999998</v>
-      </c>
-      <c r="F4" s="175">
-        <f>E4+734</f>
-        <v>146336.80430999998</v>
+        <v>104519.0115643</v>
+      </c>
+      <c r="F4" s="220">
+        <f>E4</f>
+        <v>104519.0115643</v>
       </c>
       <c r="G4" s="56">
         <f t="shared" ref="G4:G29" si="0">E4-F4</f>
-        <v>-734</v>
+        <v>0</v>
       </c>
       <c r="H4" s="56">
         <f t="shared" ref="H4:H29" si="1">IF(G4&gt;0,G4*4%,0)</f>
@@ -2554,11 +2499,11 @@
       </c>
       <c r="L4" s="57">
         <f t="shared" ref="L4:L29" si="5">I4+G4+K4+J4+H4</f>
-        <v>104519.0115643</v>
+        <v>105253.0115643</v>
       </c>
       <c r="M4" s="44"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>35</v>
       </c>
@@ -2570,16 +2515,19 @@
         <v>5.04</v>
       </c>
       <c r="E5" s="129">
-        <v>291766.26376</v>
-      </c>
-      <c r="F5" s="175"/>
+        <v>407656.00631120004</v>
+      </c>
+      <c r="F5" s="220">
+        <f>497170.55-64957-F23</f>
+        <v>377751.01123959996</v>
+      </c>
       <c r="G5" s="56">
         <f t="shared" si="0"/>
-        <v>291766.26376</v>
+        <v>29904.995071600075</v>
       </c>
       <c r="H5" s="56">
         <f t="shared" si="1"/>
-        <v>11670.6505504</v>
+        <v>1196.199802864003</v>
       </c>
       <c r="I5" s="56">
         <f t="shared" si="2"/>
@@ -2595,11 +2543,11 @@
       </c>
       <c r="L5" s="57">
         <f t="shared" si="5"/>
-        <v>407656.00631120004</v>
+        <v>135320.28687526408</v>
       </c>
       <c r="M5" s="44"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="58" t="s">
         <v>37</v>
       </c>
@@ -2611,19 +2559,16 @@
         <v>5.21</v>
       </c>
       <c r="E6" s="129">
-        <v>149035.48339000001</v>
-      </c>
-      <c r="F6" s="175">
-        <f t="shared" ref="F6:F11" si="6">E6</f>
-        <v>149035.48339000001</v>
-      </c>
+        <v>107734.41851670001</v>
+      </c>
+      <c r="F6" s="220"/>
       <c r="G6" s="56">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>107734.41851670001</v>
       </c>
       <c r="H6" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4309.3767406680008</v>
       </c>
       <c r="I6" s="56">
         <f t="shared" si="2"/>
@@ -2639,11 +2584,11 @@
       </c>
       <c r="L6" s="57">
         <f t="shared" si="5"/>
-        <v>107734.41851670001</v>
-      </c>
-      <c r="O6" s="180"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+        <v>219778.21377406802</v>
+      </c>
+      <c r="O6" s="175"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>35</v>
       </c>
@@ -2657,11 +2602,11 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E7" s="129">
-        <v>146174.91749000002</v>
-      </c>
-      <c r="F7" s="175">
-        <f t="shared" si="6"/>
-        <v>146174.91749000002</v>
+        <v>105666.57938970001</v>
+      </c>
+      <c r="F7" s="220">
+        <f t="shared" ref="F7:F11" si="6">E7</f>
+        <v>105666.57938970001</v>
       </c>
       <c r="G7" s="56">
         <f t="shared" si="0"/>
@@ -2687,9 +2632,9 @@
         <f t="shared" si="5"/>
         <v>105666.57938970001</v>
       </c>
-      <c r="O7" s="180"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O7" s="175"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
         <v>40</v>
       </c>
@@ -2701,11 +2646,11 @@
         <v>5.09</v>
       </c>
       <c r="E8" s="129">
-        <v>145602.80430999998</v>
-      </c>
-      <c r="F8" s="175">
+        <v>105253.0115643</v>
+      </c>
+      <c r="F8" s="220">
         <f t="shared" si="6"/>
-        <v>145602.80430999998</v>
+        <v>105253.0115643</v>
       </c>
       <c r="G8" s="56">
         <f t="shared" si="0"/>
@@ -2732,7 +2677,7 @@
         <v>105253.0115643</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>42</v>
       </c>
@@ -2744,11 +2689,11 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E9" s="129">
-        <v>146174.91749000002</v>
-      </c>
-      <c r="F9" s="175">
+        <v>105666.57938970001</v>
+      </c>
+      <c r="F9" s="220">
         <f t="shared" si="6"/>
-        <v>146174.91749000002</v>
+        <v>105666.57938970001</v>
       </c>
       <c r="G9" s="56">
         <f t="shared" si="0"/>
@@ -2774,51 +2719,51 @@
         <f t="shared" si="5"/>
         <v>105666.57938970001</v>
       </c>
-      <c r="O9" s="180"/>
-    </row>
-    <row r="10" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="183" t="s">
+      <c r="O9" s="175"/>
+    </row>
+    <row r="10" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="178" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="184" t="s">
+      <c r="B10" s="179" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="185" t="s">
+      <c r="C10" s="180" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="186">
+      <c r="D10" s="181">
         <v>5.09</v>
       </c>
-      <c r="E10" s="187">
-        <v>145602.80430999998</v>
-      </c>
-      <c r="F10" s="212">
+      <c r="E10" s="182">
+        <v>105253.0115643</v>
+      </c>
+      <c r="F10" s="221">
         <f t="shared" si="6"/>
-        <v>145602.80430999998</v>
-      </c>
-      <c r="G10" s="188">
+        <v>105253.0115643</v>
+      </c>
+      <c r="G10" s="183">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="188"/>
-      <c r="I10" s="188">
+      <c r="H10" s="183"/>
+      <c r="I10" s="183">
         <f t="shared" si="2"/>
         <v>53833.984264300001</v>
       </c>
-      <c r="J10" s="188">
+      <c r="J10" s="183">
         <f t="shared" si="3"/>
         <v>20360</v>
       </c>
-      <c r="K10" s="188">
+      <c r="K10" s="183">
         <f t="shared" si="4"/>
         <v>31059.027300000002</v>
       </c>
-      <c r="L10" s="189">
+      <c r="L10" s="184">
         <f t="shared" si="5"/>
         <v>105253.0115643</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>95</v>
       </c>
@@ -2830,11 +2775,11 @@
         <v>5.04</v>
       </c>
       <c r="E11" s="129">
-        <v>144172.52136000001</v>
-      </c>
-      <c r="F11" s="175">
+        <v>104219.09200080001</v>
+      </c>
+      <c r="F11" s="220">
         <f t="shared" si="6"/>
-        <v>144172.52136000001</v>
+        <v>104219.09200080001</v>
       </c>
       <c r="G11" s="56">
         <f t="shared" si="0"/>
@@ -2861,7 +2806,7 @@
         <v>104219.09200080001</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="58" t="s">
         <v>47</v>
       </c>
@@ -2873,11 +2818,11 @@
         <v>5.21</v>
       </c>
       <c r="E12" s="129">
-        <v>149035.48339000001</v>
-      </c>
-      <c r="F12" s="175">
+        <v>107734.41851670001</v>
+      </c>
+      <c r="F12" s="220">
         <f t="shared" ref="F12" si="7">E12</f>
-        <v>149035.48339000001</v>
+        <v>107734.41851670001</v>
       </c>
       <c r="G12" s="56">
         <f t="shared" si="0"/>
@@ -2904,7 +2849,7 @@
         <v>107734.41851670001</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>49</v>
       </c>
@@ -2918,11 +2863,11 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E13" s="129">
-        <v>146174.91749000002</v>
-      </c>
-      <c r="F13" s="175">
+        <v>105666.57938970001</v>
+      </c>
+      <c r="F13" s="220">
         <f>E13</f>
-        <v>146174.91749000002</v>
+        <v>105666.57938970001</v>
       </c>
       <c r="G13" s="56">
         <f t="shared" si="0"/>
@@ -2950,30 +2895,33 @@
       </c>
       <c r="M13" s="44"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="205" t="s">
+      <c r="B14" s="200" t="s">
         <v>106</v>
       </c>
       <c r="C14" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="181">
+      <c r="D14" s="176">
         <v>5.09</v>
       </c>
       <c r="E14" s="129">
-        <v>256016.29710999998</v>
-      </c>
-      <c r="F14" s="175"/>
+        <v>371509.96055870003</v>
+      </c>
+      <c r="F14" s="220">
+        <f>580000-F25-84879</f>
+        <v>416293.74475960003</v>
+      </c>
       <c r="G14" s="64">
         <f t="shared" si="0"/>
-        <v>256016.29710999998</v>
+        <v>-44783.784200900001</v>
       </c>
       <c r="H14" s="64">
         <f t="shared" si="1"/>
-        <v>10240.6518844</v>
+        <v>0</v>
       </c>
       <c r="I14" s="64">
         <f t="shared" si="2"/>
@@ -2987,12 +2935,12 @@
         <f t="shared" si="4"/>
         <v>31059.027300000002</v>
       </c>
-      <c r="L14" s="182">
+      <c r="L14" s="177">
         <f t="shared" si="5"/>
-        <v>371509.96055870003</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+        <v>60469.227363400001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>53</v>
       </c>
@@ -3006,19 +2954,19 @@
         <v>5.04</v>
       </c>
       <c r="E15" s="129">
-        <v>315391.53816</v>
-      </c>
-      <c r="F15" s="175">
-        <f>346286-F29-0.35</f>
-        <v>315391.53828000004</v>
+        <v>104219.09188079997</v>
+      </c>
+      <c r="F15" s="220">
+        <f>104219-F29+22333.1-0.35</f>
+        <v>104219.0874284</v>
       </c>
       <c r="G15" s="56">
         <f t="shared" si="0"/>
-        <v>-1.200000406242907E-4</v>
+        <v>4.4523999677039683E-3</v>
       </c>
       <c r="H15" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.7809599870815873E-4</v>
       </c>
       <c r="I15" s="56">
         <f t="shared" si="2"/>
@@ -3034,10 +2982,10 @@
       </c>
       <c r="L15" s="57">
         <f t="shared" si="5"/>
-        <v>104219.09188079997</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+        <v>104219.09663129598</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="58" t="s">
         <v>56</v>
       </c>
@@ -3051,11 +2999,11 @@
         <v>5.21</v>
       </c>
       <c r="E16" s="129">
-        <v>149035.48339000001</v>
-      </c>
-      <c r="F16" s="175">
+        <v>107734.41851670001</v>
+      </c>
+      <c r="F16" s="220">
         <f t="shared" ref="F16:F21" si="8">E16</f>
-        <v>149035.48339000001</v>
+        <v>107734.41851670001</v>
       </c>
       <c r="G16" s="56">
         <f t="shared" si="0"/>
@@ -3083,7 +3031,7 @@
       </c>
       <c r="M16" s="44"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>59</v>
       </c>
@@ -3095,11 +3043,11 @@
         <v>5.04</v>
       </c>
       <c r="E17" s="129">
-        <v>253501.39815999998</v>
-      </c>
-      <c r="F17" s="175">
+        <v>104219.09200080001</v>
+      </c>
+      <c r="F17" s="220">
         <f t="shared" si="8"/>
-        <v>253501.39815999998</v>
+        <v>104219.09200080001</v>
       </c>
       <c r="G17" s="56">
         <f t="shared" si="0"/>
@@ -3126,23 +3074,23 @@
         <v>104219.09200080001</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="215" t="s">
+    <row r="18" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="207" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="216"/>
+      <c r="B18" s="208"/>
       <c r="C18" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="D18" s="181">
+      <c r="D18" s="176">
         <v>5.21</v>
       </c>
       <c r="E18" s="129">
-        <v>262052.04419000002</v>
-      </c>
-      <c r="F18" s="175">
+        <v>107734.41851670001</v>
+      </c>
+      <c r="F18" s="220">
         <f t="shared" si="8"/>
-        <v>262052.04419000002</v>
+        <v>107734.41851670001</v>
       </c>
       <c r="G18" s="64">
         <f t="shared" si="0"/>
@@ -3164,32 +3112,32 @@
         <f t="shared" si="4"/>
         <v>31791.2637</v>
       </c>
-      <c r="L18" s="182">
+      <c r="L18" s="177">
         <f t="shared" si="5"/>
         <v>107734.41851670001</v>
       </c>
-      <c r="M18" s="220"/>
-      <c r="N18" s="219"/>
-      <c r="O18" s="218"/>
-      <c r="P18" s="214"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M18" s="211"/>
+      <c r="N18" s="210"/>
+      <c r="O18" s="209"/>
+      <c r="P18" s="206"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="205"/>
+      <c r="B19" s="200"/>
       <c r="C19" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="181">
+      <c r="D19" s="176">
         <v>7.4</v>
       </c>
       <c r="E19" s="129">
-        <v>211681.87660000002</v>
-      </c>
-      <c r="F19" s="175">
+        <v>153020.095398</v>
+      </c>
+      <c r="F19" s="220">
         <f t="shared" si="8"/>
-        <v>211681.87660000002</v>
+        <v>153020.095398</v>
       </c>
       <c r="G19" s="64">
         <f t="shared" si="0"/>
@@ -3211,52 +3159,52 @@
         <f t="shared" si="4"/>
         <v>45154.578000000001</v>
       </c>
-      <c r="L19" s="182">
+      <c r="L19" s="177">
         <f t="shared" si="5"/>
         <v>153020.095398</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="24" x14ac:dyDescent="0.3">
-      <c r="A20" s="190"/>
-      <c r="B20" s="184" t="s">
+    <row r="20" spans="1:16" ht="24" x14ac:dyDescent="0.25">
+      <c r="A20" s="185"/>
+      <c r="B20" s="179" t="s">
         <v>99</v>
       </c>
-      <c r="C20" s="185" t="s">
+      <c r="C20" s="180" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="186">
+      <c r="D20" s="181">
         <v>1.08</v>
       </c>
-      <c r="E20" s="187">
-        <v>30894.111720000001</v>
-      </c>
-      <c r="F20" s="212">
+      <c r="E20" s="182">
+        <v>22332.662571600002</v>
+      </c>
+      <c r="F20" s="221">
         <f t="shared" si="8"/>
-        <v>30894.111720000001</v>
-      </c>
-      <c r="G20" s="188">
+        <v>22332.662571600002</v>
+      </c>
+      <c r="G20" s="183">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H20" s="188"/>
-      <c r="I20" s="188">
+      <c r="H20" s="183"/>
+      <c r="I20" s="183">
         <f t="shared" si="2"/>
         <v>11422.534971600002</v>
       </c>
-      <c r="J20" s="188">
+      <c r="J20" s="183">
         <f t="shared" si="3"/>
         <v>4320</v>
       </c>
-      <c r="K20" s="188">
+      <c r="K20" s="183">
         <f t="shared" si="4"/>
         <v>6590.1275999999998</v>
       </c>
-      <c r="L20" s="189">
+      <c r="L20" s="184">
         <f t="shared" si="5"/>
         <v>22332.662571600002</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="62"/>
       <c r="B21" s="59" t="s">
         <v>57</v>
@@ -3268,11 +3216,11 @@
         <v>1.08</v>
       </c>
       <c r="E21" s="129">
-        <v>30894.111720000001</v>
-      </c>
-      <c r="F21" s="175">
+        <v>22332.662571600002</v>
+      </c>
+      <c r="F21" s="220">
         <f t="shared" si="8"/>
-        <v>30894.111720000001</v>
+        <v>22332.662571600002</v>
       </c>
       <c r="G21" s="56">
         <f t="shared" si="0"/>
@@ -3299,48 +3247,50 @@
         <v>22332.662571600002</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A22" s="140"/>
-      <c r="B22" s="141"/>
-      <c r="C22" s="142" t="s">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="139"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="141" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="143">
+      <c r="D22" s="142">
         <v>1.08</v>
       </c>
-      <c r="E22" s="144">
-        <v>231024.85812000002</v>
-      </c>
-      <c r="F22" s="179">
-        <v>0</v>
-      </c>
-      <c r="G22" s="145">
+      <c r="E22" s="143">
+        <v>262598.51501640002</v>
+      </c>
+      <c r="F22" s="222">
+        <v>0</v>
+      </c>
+      <c r="G22" s="144">
         <f t="shared" si="0"/>
-        <v>231024.85812000002</v>
-      </c>
-      <c r="H22" s="145">
+        <v>262598.51501640002</v>
+      </c>
+      <c r="H22" s="144">
         <f t="shared" si="1"/>
-        <v>9240.9943248000018</v>
-      </c>
-      <c r="I22" s="145">
+        <v>10503.940600656</v>
+      </c>
+      <c r="I22" s="144">
         <f t="shared" si="2"/>
         <v>11422.534971600002</v>
       </c>
-      <c r="J22" s="145">
+      <c r="J22" s="144">
         <f t="shared" si="3"/>
         <v>4320</v>
       </c>
-      <c r="K22" s="145">
+      <c r="K22" s="144">
         <f t="shared" si="4"/>
         <v>6590.1275999999998</v>
       </c>
-      <c r="L22" s="146">
+      <c r="L22" s="145">
         <f t="shared" si="5"/>
-        <v>262598.51501640002</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" s="58"/>
+        <v>295435.11818865599</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="58" t="s">
+        <v>35</v>
+      </c>
       <c r="B23" s="59"/>
       <c r="C23" s="60" t="s">
         <v>68</v>
@@ -3349,16 +3299,19 @@
         <v>1.08</v>
       </c>
       <c r="E23" s="129">
-        <v>30894.111720000001</v>
-      </c>
-      <c r="F23" s="175"/>
+        <v>54462.538760400006</v>
+      </c>
+      <c r="F23" s="220">
+        <f>E23</f>
+        <v>54462.538760400006</v>
+      </c>
       <c r="G23" s="56">
         <f t="shared" si="0"/>
-        <v>30894.111720000001</v>
+        <v>0</v>
       </c>
       <c r="H23" s="56">
         <f t="shared" si="1"/>
-        <v>1235.7644688</v>
+        <v>0</v>
       </c>
       <c r="I23" s="56">
         <f t="shared" si="2"/>
@@ -3374,10 +3327,10 @@
       </c>
       <c r="L23" s="57">
         <f t="shared" si="5"/>
-        <v>54462.538760400006</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+        <v>22332.662571600002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
         <v>49</v>
       </c>
@@ -3391,11 +3344,11 @@
         <v>1.08</v>
       </c>
       <c r="E24" s="129">
-        <v>30894.111720000001</v>
-      </c>
-      <c r="F24" s="175">
+        <v>22332.662571600002</v>
+      </c>
+      <c r="F24" s="220">
         <f t="shared" ref="F24" si="9">E24</f>
-        <v>30894.111720000001</v>
+        <v>22332.662571600002</v>
       </c>
       <c r="G24" s="56">
         <f t="shared" si="0"/>
@@ -3422,11 +3375,11 @@
         <v>22332.662571600002</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="205" t="s">
+      <c r="B25" s="200" t="s">
         <v>106</v>
       </c>
       <c r="C25" s="60" t="s">
@@ -3436,16 +3389,19 @@
         <v>1.08</v>
       </c>
       <c r="E25" s="129">
-        <v>54321.723720000002</v>
-      </c>
-      <c r="F25" s="175"/>
+        <v>78827.255240400002</v>
+      </c>
+      <c r="F25" s="220">
+        <f>E25</f>
+        <v>78827.255240400002</v>
+      </c>
       <c r="G25" s="56">
         <f t="shared" si="0"/>
-        <v>54321.723720000002</v>
+        <v>0</v>
       </c>
       <c r="H25" s="56">
         <f t="shared" si="1"/>
-        <v>2172.8689488</v>
+        <v>0</v>
       </c>
       <c r="I25" s="56">
         <f t="shared" si="2"/>
@@ -3461,10 +3417,10 @@
       </c>
       <c r="L25" s="57">
         <f t="shared" si="5"/>
-        <v>78827.255240400002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+        <v>22332.662571600002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
         <v>63</v>
       </c>
@@ -3476,11 +3432,11 @@
         <v>1.08</v>
       </c>
       <c r="E26" s="129">
-        <v>30894.111720000001</v>
-      </c>
-      <c r="F26" s="175">
+        <v>22332.662571600002</v>
+      </c>
+      <c r="F26" s="220">
         <f t="shared" ref="F26:F28" si="10">E26</f>
-        <v>30894.111720000001</v>
+        <v>22332.662571600002</v>
       </c>
       <c r="G26" s="56">
         <f t="shared" si="0"/>
@@ -3507,7 +3463,7 @@
         <v>22332.662571600002</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
         <v>63</v>
       </c>
@@ -3519,11 +3475,11 @@
         <v>1.08</v>
       </c>
       <c r="E27" s="129">
-        <v>30894.111720000001</v>
-      </c>
-      <c r="F27" s="175">
+        <v>22332.662571600002</v>
+      </c>
+      <c r="F27" s="220">
         <f t="shared" si="10"/>
-        <v>30894.111720000001</v>
+        <v>22332.662571600002</v>
       </c>
       <c r="G27" s="56">
         <f t="shared" si="0"/>
@@ -3551,10 +3507,10 @@
       </c>
       <c r="O27" s="44">
         <f>F27+F26+F19</f>
-        <v>273470.10004000005</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+        <v>197685.4205412</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="66"/>
       <c r="B28" s="65" t="str">
         <f>B7</f>
@@ -3567,11 +3523,11 @@
         <v>1.08</v>
       </c>
       <c r="E28" s="129">
-        <v>30894.111720000001</v>
-      </c>
-      <c r="F28" s="175">
+        <v>22332.662571600002</v>
+      </c>
+      <c r="F28" s="220">
         <f t="shared" si="10"/>
-        <v>30894.111720000001</v>
+        <v>22332.662571600002</v>
       </c>
       <c r="G28" s="56">
         <f t="shared" si="0"/>
@@ -3598,7 +3554,7 @@
         <v>22332.662571600002</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="66" t="s">
         <v>53</v>
       </c>
@@ -3612,11 +3568,11 @@
         <v>1.08</v>
       </c>
       <c r="E29" s="129">
-        <v>30894.111720000001</v>
-      </c>
-      <c r="F29" s="175">
+        <v>22332.662571600002</v>
+      </c>
+      <c r="F29" s="220">
         <f>E29</f>
-        <v>30894.111720000001</v>
+        <v>22332.662571600002</v>
       </c>
       <c r="G29" s="56">
         <f t="shared" si="0"/>
@@ -3643,7 +3599,7 @@
         <v>22332.662571600002</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="67"/>
       <c r="B30" s="67"/>
       <c r="C30" s="68"/>
@@ -3657,7 +3613,7 @@
       <c r="K30" s="71"/>
       <c r="L30" s="71"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="72"/>
       <c r="B31" s="73"/>
       <c r="C31" s="74" t="s">
@@ -3670,7 +3626,7 @@
       <c r="E31" s="73"/>
       <c r="F31" s="135">
         <f>SUM(F3:F30)</f>
-        <v>2872567.6936899996</v>
+        <v>2610074.1626310009</v>
       </c>
       <c r="G31" s="75"/>
       <c r="H31" s="75"/>
@@ -3685,71 +3641,71 @@
       <c r="K31" s="135"/>
       <c r="L31" s="135">
         <f>SUM(L3:L29)</f>
-        <v>2965528.3114872011</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+        <v>2439302.7931784848</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="J32" s="22"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="237" t="s">
-        <v>112</v>
-      </c>
-      <c r="B33" s="237"/>
-      <c r="C33" s="237"/>
-      <c r="D33" s="237"/>
-      <c r="E33" s="237"/>
-      <c r="F33" s="237"/>
-      <c r="G33" s="237"/>
-      <c r="H33" s="237"/>
-      <c r="I33" s="237"/>
-      <c r="J33" s="237"/>
-      <c r="K33" s="237"/>
-      <c r="L33" s="237"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="237"/>
-      <c r="B34" s="237"/>
-      <c r="C34" s="237"/>
-      <c r="D34" s="237"/>
-      <c r="E34" s="237"/>
-      <c r="F34" s="237"/>
-      <c r="G34" s="237"/>
-      <c r="H34" s="237"/>
-      <c r="I34" s="237"/>
-      <c r="J34" s="237"/>
-      <c r="K34" s="237"/>
-      <c r="L34" s="237"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="237"/>
-      <c r="B35" s="237"/>
-      <c r="C35" s="237"/>
-      <c r="D35" s="237"/>
-      <c r="E35" s="237"/>
-      <c r="F35" s="237"/>
-      <c r="G35" s="237"/>
-      <c r="H35" s="237"/>
-      <c r="I35" s="237"/>
-      <c r="J35" s="237"/>
-      <c r="K35" s="237"/>
-      <c r="L35" s="237"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="237"/>
-      <c r="B36" s="237"/>
-      <c r="C36" s="237"/>
-      <c r="D36" s="237"/>
-      <c r="E36" s="237"/>
-      <c r="F36" s="237"/>
-      <c r="G36" s="237"/>
-      <c r="H36" s="237"/>
-      <c r="I36" s="237"/>
-      <c r="J36" s="237"/>
-      <c r="K36" s="237"/>
-      <c r="L36" s="237"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="234" t="s">
+        <v>111</v>
+      </c>
+      <c r="B33" s="234"/>
+      <c r="C33" s="234"/>
+      <c r="D33" s="234"/>
+      <c r="E33" s="234"/>
+      <c r="F33" s="234"/>
+      <c r="G33" s="234"/>
+      <c r="H33" s="234"/>
+      <c r="I33" s="234"/>
+      <c r="J33" s="234"/>
+      <c r="K33" s="234"/>
+      <c r="L33" s="234"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="234"/>
+      <c r="B34" s="234"/>
+      <c r="C34" s="234"/>
+      <c r="D34" s="234"/>
+      <c r="E34" s="234"/>
+      <c r="F34" s="234"/>
+      <c r="G34" s="234"/>
+      <c r="H34" s="234"/>
+      <c r="I34" s="234"/>
+      <c r="J34" s="234"/>
+      <c r="K34" s="234"/>
+      <c r="L34" s="234"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="234"/>
+      <c r="B35" s="234"/>
+      <c r="C35" s="234"/>
+      <c r="D35" s="234"/>
+      <c r="E35" s="234"/>
+      <c r="F35" s="234"/>
+      <c r="G35" s="234"/>
+      <c r="H35" s="234"/>
+      <c r="I35" s="234"/>
+      <c r="J35" s="234"/>
+      <c r="K35" s="234"/>
+      <c r="L35" s="234"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="234"/>
+      <c r="B36" s="234"/>
+      <c r="C36" s="234"/>
+      <c r="D36" s="234"/>
+      <c r="E36" s="234"/>
+      <c r="F36" s="234"/>
+      <c r="G36" s="234"/>
+      <c r="H36" s="234"/>
+      <c r="I36" s="234"/>
+      <c r="J36" s="234"/>
+      <c r="K36" s="234"/>
+      <c r="L36" s="234"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E40" s="21"/>
     </row>
   </sheetData>
@@ -3769,167 +3725,167 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5546875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="13" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="11.109375" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="10.6640625" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="240" t="s">
+    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="237" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="241"/>
-      <c r="C1" s="241"/>
-      <c r="D1" s="241"/>
-      <c r="E1" s="241"/>
-      <c r="F1" s="241"/>
-      <c r="G1" s="241"/>
-      <c r="H1" s="241"/>
-      <c r="I1" s="241"/>
-      <c r="J1" s="241"/>
-      <c r="K1" s="241"/>
-      <c r="L1" s="241"/>
-      <c r="M1" s="241"/>
-      <c r="N1" s="242"/>
+      <c r="B1" s="238"/>
+      <c r="C1" s="238"/>
+      <c r="D1" s="238"/>
+      <c r="E1" s="238"/>
+      <c r="F1" s="238"/>
+      <c r="G1" s="238"/>
+      <c r="H1" s="238"/>
+      <c r="I1" s="238"/>
+      <c r="J1" s="238"/>
+      <c r="K1" s="238"/>
+      <c r="L1" s="238"/>
+      <c r="M1" s="238"/>
+      <c r="N1" s="239"/>
       <c r="O1" s="76"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="77"/>
       <c r="B2" s="77"/>
-      <c r="C2" s="162"/>
-      <c r="D2" s="162"/>
-      <c r="E2" s="162"/>
-      <c r="F2" s="162"/>
-      <c r="G2" s="162"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="162"/>
-      <c r="J2" s="162"/>
-      <c r="K2" s="162"/>
-      <c r="L2" s="162"/>
-      <c r="M2" s="162"/>
-      <c r="N2" s="162"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="162"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="161"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="161"/>
       <c r="O2" s="78"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="80"/>
-      <c r="C3" s="164"/>
-      <c r="D3" s="164"/>
-      <c r="E3" s="164"/>
-      <c r="F3" s="164"/>
-      <c r="G3" s="164"/>
-      <c r="H3" s="163"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="162"/>
-      <c r="K3" s="162"/>
-      <c r="L3" s="162"/>
-      <c r="M3" s="162"/>
-      <c r="N3" s="162"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
+      <c r="F3" s="163"/>
+      <c r="G3" s="163"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="161"/>
+      <c r="K3" s="161"/>
+      <c r="L3" s="161"/>
+      <c r="M3" s="161"/>
+      <c r="N3" s="161"/>
       <c r="O3" s="78"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="80"/>
       <c r="B4" s="80"/>
-      <c r="C4" s="164"/>
-      <c r="D4" s="164"/>
-      <c r="E4" s="164"/>
-      <c r="F4" s="164"/>
-      <c r="G4" s="164"/>
-      <c r="H4" s="163"/>
-      <c r="I4" s="162" t="s">
+      <c r="C4" s="163"/>
+      <c r="D4" s="163"/>
+      <c r="E4" s="163"/>
+      <c r="F4" s="163"/>
+      <c r="G4" s="163"/>
+      <c r="H4" s="162"/>
+      <c r="I4" s="161" t="s">
         <v>76</v>
       </c>
-      <c r="J4" s="162"/>
-      <c r="K4" s="162"/>
-      <c r="L4" s="162"/>
-      <c r="M4" s="162"/>
-      <c r="N4" s="162"/>
+      <c r="J4" s="161"/>
+      <c r="K4" s="161"/>
+      <c r="L4" s="161"/>
+      <c r="M4" s="161"/>
+      <c r="N4" s="161"/>
       <c r="O4" s="78"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="80"/>
       <c r="B5" s="80"/>
-      <c r="C5" s="164"/>
-      <c r="D5" s="164"/>
-      <c r="E5" s="164"/>
-      <c r="F5" s="164"/>
-      <c r="G5" s="164"/>
-      <c r="H5" s="163"/>
-      <c r="I5" s="162"/>
-      <c r="J5" s="162"/>
-      <c r="K5" s="162"/>
-      <c r="L5" s="162"/>
-      <c r="M5" s="162"/>
-      <c r="N5" s="162"/>
+      <c r="C5" s="163"/>
+      <c r="D5" s="163"/>
+      <c r="E5" s="163"/>
+      <c r="F5" s="163"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="162"/>
+      <c r="I5" s="161"/>
+      <c r="J5" s="161"/>
+      <c r="K5" s="161"/>
+      <c r="L5" s="161"/>
+      <c r="M5" s="161"/>
+      <c r="N5" s="161"/>
       <c r="O5" s="78"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="80"/>
       <c r="B6" s="80"/>
-      <c r="C6" s="229" t="str">
+      <c r="C6" s="219" t="str">
         <f>'detalle y gastos'!C7</f>
         <v>Vto. 15/12</v>
       </c>
       <c r="D6" s="28"/>
-      <c r="E6" s="162"/>
-      <c r="F6" s="162"/>
-      <c r="G6" s="162"/>
-      <c r="H6" s="163"/>
-      <c r="I6" s="162"/>
-      <c r="J6" s="162"/>
-      <c r="K6" s="162"/>
-      <c r="L6" s="162"/>
-      <c r="M6" s="162"/>
-      <c r="N6" s="162"/>
+      <c r="E6" s="161"/>
+      <c r="F6" s="161"/>
+      <c r="G6" s="161"/>
+      <c r="H6" s="162"/>
+      <c r="I6" s="161"/>
+      <c r="J6" s="161"/>
+      <c r="K6" s="161"/>
+      <c r="L6" s="161"/>
+      <c r="M6" s="161"/>
+      <c r="N6" s="161"/>
       <c r="O6" s="78"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="81"/>
       <c r="B7" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="213">
+      <c r="C7" s="205">
         <v>551870.81000000006</v>
       </c>
       <c r="D7" s="28"/>
-      <c r="E7" s="162"/>
-      <c r="F7" s="162" t="s">
+      <c r="E7" s="161"/>
+      <c r="F7" s="161" t="s">
         <v>93</v>
       </c>
-      <c r="G7" s="162"/>
-      <c r="H7" s="163"/>
-      <c r="I7" s="162"/>
-      <c r="J7" s="162" t="str">
+      <c r="G7" s="161"/>
+      <c r="H7" s="162"/>
+      <c r="I7" s="161"/>
+      <c r="J7" s="161" t="str">
         <f>'detalle y gastos'!C7</f>
         <v>Vto. 15/12</v>
       </c>
-      <c r="K7" s="162"/>
-      <c r="L7" s="162"/>
-      <c r="M7" s="162"/>
-      <c r="N7" s="162"/>
+      <c r="K7" s="161"/>
+      <c r="L7" s="161"/>
+      <c r="M7" s="161"/>
+      <c r="N7" s="161"/>
       <c r="O7" s="78"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="81"/>
       <c r="B8" s="80" t="s">
         <v>77</v>
@@ -3943,18 +3899,18 @@
       <c r="J8" s="78"/>
       <c r="K8" s="86">
         <f>C8-J38</f>
-        <v>-329579.71031000023</v>
-      </c>
-      <c r="L8" s="244">
+        <v>-199922.9342899998</v>
+      </c>
+      <c r="L8" s="241">
         <f>C7-J38</f>
-        <v>222291.09968999983</v>
-      </c>
-      <c r="M8" s="244"/>
+        <v>351947.87571000028</v>
+      </c>
+      <c r="M8" s="241"/>
       <c r="N8" s="84"/>
       <c r="O8" s="78"/>
       <c r="P8" s="11"/>
     </row>
-    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="87" t="s">
         <v>78</v>
       </c>
@@ -3999,7 +3955,7 @@
       </c>
       <c r="P9" s="11"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="98">
         <v>1</v>
       </c>
@@ -4016,46 +3972,46 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F10" s="103">
-        <v>4075</v>
+        <v>4302.83</v>
       </c>
       <c r="G10" s="103">
-        <v>4302.83</v>
+        <v>4441.7</v>
       </c>
       <c r="H10" s="104">
         <f>G10-F10</f>
-        <v>227.82999999999993</v>
+        <v>138.86999999999989</v>
       </c>
       <c r="I10" s="105">
         <f t="shared" ref="I10:I37" si="0">H10*7%</f>
-        <v>15.948099999999997</v>
+        <v>9.7208999999999932</v>
       </c>
       <c r="J10" s="116">
         <f>M10*93.787</f>
-        <v>21367.492209999993</v>
+        <v>13024.200689999991</v>
       </c>
       <c r="K10" s="106">
         <f>K8*E10%</f>
-        <v>-16841.523196841015</v>
+        <v>-10216.061942218992</v>
       </c>
       <c r="L10" s="127">
         <f>L$8*E10/S$12</f>
-        <v>11359.075194158992</v>
+        <v>17984.536448781015</v>
       </c>
       <c r="M10" s="107">
         <f>G10-F10</f>
-        <v>227.82999999999993</v>
+        <v>138.86999999999989</v>
       </c>
       <c r="N10" s="104">
         <f>J10+L10</f>
-        <v>32726.567404158985</v>
+        <v>31008.737138781005</v>
       </c>
       <c r="O10" s="97">
         <f>N10+'prorrateo '!L3</f>
-        <v>138232.14679385899</v>
+        <v>136675.31652848102</v>
       </c>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="99">
         <v>2</v>
       </c>
@@ -4072,46 +4028,46 @@
         <v>5.09</v>
       </c>
       <c r="F11" s="103">
-        <v>3872.9</v>
+        <v>4106.5</v>
       </c>
       <c r="G11" s="103">
-        <v>4106.5</v>
+        <v>4207.8</v>
       </c>
       <c r="H11" s="104">
         <f t="shared" ref="H11:H27" si="1">G11-F11</f>
-        <v>233.59999999999991</v>
+        <v>101.30000000000018</v>
       </c>
       <c r="I11" s="105">
         <f t="shared" si="0"/>
-        <v>16.351999999999997</v>
+        <v>7.0910000000000135</v>
       </c>
       <c r="J11" s="116">
         <f t="shared" ref="J11:J26" si="2">M11*93.787</f>
-        <v>21908.643199999991</v>
+        <v>9500.6231000000171</v>
       </c>
       <c r="K11" s="106">
         <f>K8*E11%</f>
-        <v>-16775.607254779014</v>
+        <v>-10176.077355360991</v>
       </c>
       <c r="L11" s="127">
         <f t="shared" ref="L11:L36" si="3">L$8*E11/S$12</f>
-        <v>11314.616974220991</v>
+        <v>17914.146873639012</v>
       </c>
       <c r="M11" s="107">
         <f t="shared" ref="M11:M26" si="4">G11-F11</f>
-        <v>233.59999999999991</v>
+        <v>101.30000000000018</v>
       </c>
       <c r="N11" s="104">
         <f t="shared" ref="N11:N25" si="5">J11+L11</f>
-        <v>33223.260174220981</v>
+        <v>27414.769973639028</v>
       </c>
       <c r="O11" s="97">
         <f>N11+'prorrateo '!L4</f>
-        <v>137742.271738521</v>
+        <v>132667.78153793904</v>
       </c>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="98">
         <v>3</v>
       </c>
@@ -4128,105 +4084,105 @@
         <v>5.04</v>
       </c>
       <c r="F12" s="103">
-        <v>1424.1</v>
+        <v>1558.7</v>
       </c>
       <c r="G12" s="103">
-        <v>1558.7</v>
+        <v>1667.5</v>
       </c>
       <c r="H12" s="104">
         <f t="shared" si="1"/>
-        <v>134.60000000000014</v>
+        <v>108.79999999999995</v>
       </c>
       <c r="I12" s="105">
         <f t="shared" si="0"/>
-        <v>9.4220000000000113</v>
+        <v>7.6159999999999979</v>
       </c>
       <c r="J12" s="116">
         <f t="shared" si="2"/>
-        <v>12623.730200000015</v>
+        <v>10204.025599999997</v>
       </c>
       <c r="K12" s="106">
         <f>K8*E12%</f>
-        <v>-16610.817399624011</v>
+        <v>-10076.115888215991</v>
       </c>
       <c r="L12" s="127">
         <f t="shared" si="3"/>
-        <v>11203.471424375992</v>
+        <v>17738.172935784016</v>
       </c>
       <c r="M12" s="107">
         <f>G12-F12</f>
-        <v>134.60000000000014</v>
+        <v>108.79999999999995</v>
       </c>
       <c r="N12" s="104">
         <f t="shared" si="5"/>
-        <v>23827.201624376008</v>
+        <v>27942.198535784013</v>
       </c>
       <c r="O12" s="97">
         <f>N12+'prorrateo '!L5</f>
-        <v>431483.20793557604</v>
+        <v>163262.48541104808</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="98">
         <v>4</v>
       </c>
       <c r="B13" s="89" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="165" t="s">
+      <c r="C13" s="164" t="s">
         <v>38</v>
       </c>
       <c r="D13" s="100" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="166">
+      <c r="E13" s="165">
         <v>5.21</v>
       </c>
       <c r="F13" s="103">
-        <v>1058.9000000000001</v>
-      </c>
-      <c r="G13" s="221">
         <v>1204.5999999999999</v>
+      </c>
+      <c r="G13" s="103">
+        <v>1283.0999999999999</v>
       </c>
       <c r="H13" s="104">
         <f t="shared" si="1"/>
-        <v>145.69999999999982</v>
-      </c>
-      <c r="I13" s="167">
+        <v>78.5</v>
+      </c>
+      <c r="I13" s="166">
         <f t="shared" si="0"/>
-        <v>10.198999999999987</v>
+        <v>5.4950000000000001</v>
       </c>
       <c r="J13" s="116">
         <f t="shared" si="2"/>
-        <v>13664.765899999984</v>
-      </c>
-      <c r="K13" s="168">
+        <v>7362.2795000000006</v>
+      </c>
+      <c r="K13" s="167">
         <f>K8*E13%</f>
-        <v>-17171.102907151013</v>
+        <v>-10415.98487650899</v>
       </c>
       <c r="L13" s="127">
         <f t="shared" si="3"/>
-        <v>11581.366293848991</v>
-      </c>
-      <c r="M13" s="169">
+        <v>18336.484324491015</v>
+      </c>
+      <c r="M13" s="168">
         <f t="shared" si="4"/>
-        <v>145.69999999999982</v>
+        <v>78.5</v>
       </c>
       <c r="N13" s="104">
         <f t="shared" si="5"/>
-        <v>25246.132193848975</v>
+        <v>25698.763824491016</v>
       </c>
       <c r="O13" s="97">
         <f>N13+'prorrateo '!L6</f>
-        <v>132980.550710549</v>
+        <v>245476.97759855902</v>
       </c>
       <c r="P13" s="11"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="98">
         <v>6</v>
       </c>
@@ -4243,46 +4199,46 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F14" s="103">
-        <v>1645.5</v>
-      </c>
-      <c r="G14" s="221">
         <v>1814</v>
+      </c>
+      <c r="G14" s="103">
+        <v>1914.3</v>
       </c>
       <c r="H14" s="104">
         <f t="shared" si="1"/>
-        <v>168.5</v>
+        <v>100.29999999999995</v>
       </c>
       <c r="I14" s="105">
         <f t="shared" si="0"/>
-        <v>11.795000000000002</v>
+        <v>7.0209999999999972</v>
       </c>
       <c r="J14" s="116">
         <f t="shared" si="2"/>
-        <v>15803.1095</v>
+        <v>9406.8360999999968</v>
       </c>
       <c r="K14" s="106">
         <f>K8*E14%</f>
-        <v>-16841.523196841015</v>
+        <v>-10216.061942218992</v>
       </c>
       <c r="L14" s="127">
         <f t="shared" si="3"/>
-        <v>11359.075194158992</v>
+        <v>17984.536448781015</v>
       </c>
       <c r="M14" s="107">
         <f t="shared" si="4"/>
-        <v>168.5</v>
+        <v>100.29999999999995</v>
       </c>
       <c r="N14" s="104">
         <f t="shared" si="5"/>
-        <v>27162.18469415899</v>
+        <v>27391.372548781012</v>
       </c>
       <c r="O14" s="97">
         <f>N14+'prorrateo '!L7</f>
-        <v>132828.76408385899</v>
+        <v>133057.95193848101</v>
       </c>
       <c r="P14" s="11"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="98">
         <v>7</v>
       </c>
@@ -4299,45 +4255,45 @@
         <v>5.09</v>
       </c>
       <c r="F15" s="103">
-        <v>2836.9</v>
+        <v>3018</v>
       </c>
       <c r="G15" s="103">
-        <v>3018</v>
+        <v>3098.9</v>
       </c>
       <c r="H15" s="104">
         <f t="shared" si="1"/>
-        <v>181.09999999999991</v>
+        <v>80.900000000000091</v>
       </c>
       <c r="I15" s="105">
         <f t="shared" si="0"/>
-        <v>12.676999999999994</v>
+        <v>5.6630000000000065</v>
       </c>
       <c r="J15" s="116">
         <f t="shared" si="2"/>
-        <v>16984.825699999994</v>
+        <v>7587.3683000000092</v>
       </c>
       <c r="K15" s="106">
         <f>K8*E15%</f>
-        <v>-16775.607254779014</v>
+        <v>-10176.077355360991</v>
       </c>
       <c r="L15" s="127">
         <f t="shared" si="3"/>
-        <v>11314.616974220991</v>
+        <v>17914.146873639012</v>
       </c>
       <c r="M15" s="107">
         <f t="shared" si="4"/>
-        <v>181.09999999999991</v>
+        <v>80.900000000000091</v>
       </c>
       <c r="N15" s="104">
         <f t="shared" si="5"/>
-        <v>28299.442674220983</v>
+        <v>25501.515173639022</v>
       </c>
       <c r="O15" s="97">
         <f>N15+'prorrateo '!L8</f>
-        <v>133552.45423852099</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+        <v>130754.52673793903</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="98">
         <v>8</v>
       </c>
@@ -4354,100 +4310,100 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F16" s="103">
-        <v>2327.4</v>
+        <v>2516.4</v>
       </c>
       <c r="G16" s="103">
-        <v>2516.4</v>
+        <v>2607.6</v>
       </c>
       <c r="H16" s="104">
         <f t="shared" si="1"/>
-        <v>189</v>
+        <v>91.199999999999818</v>
       </c>
       <c r="I16" s="105">
         <f t="shared" si="0"/>
-        <v>13.23</v>
+        <v>6.3839999999999879</v>
       </c>
       <c r="J16" s="116">
         <f t="shared" si="2"/>
-        <v>17725.743000000002</v>
+        <v>8553.3743999999842</v>
       </c>
       <c r="K16" s="106">
         <f>K8*E16%</f>
-        <v>-16841.523196841015</v>
+        <v>-10216.061942218992</v>
       </c>
       <c r="L16" s="127">
         <f t="shared" si="3"/>
-        <v>11359.075194158992</v>
+        <v>17984.536448781015</v>
       </c>
       <c r="M16" s="107">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>91.199999999999818</v>
       </c>
       <c r="N16" s="104">
         <f t="shared" si="5"/>
-        <v>29084.818194158994</v>
+        <v>26537.910848781001</v>
       </c>
       <c r="O16" s="97">
         <f>N16+'prorrateo '!L9</f>
-        <v>134751.39758385901</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+        <v>132204.49023848103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="98">
         <v>9</v>
       </c>
       <c r="B17" s="89">
         <v>9</v>
       </c>
-      <c r="C17" s="191" t="s">
+      <c r="C17" s="186" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="192" t="s">
+      <c r="D17" s="187" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="193">
+      <c r="E17" s="188">
         <v>5.09</v>
       </c>
-      <c r="F17" s="195">
-        <v>3314.7</v>
-      </c>
-      <c r="G17" s="195">
+      <c r="F17" s="190">
         <v>3375.8</v>
       </c>
-      <c r="H17" s="196">
+      <c r="G17" s="190">
+        <v>3400.1</v>
+      </c>
+      <c r="H17" s="191">
         <f t="shared" si="1"/>
-        <v>61.100000000000364</v>
-      </c>
-      <c r="I17" s="197">
+        <v>24.299999999999727</v>
+      </c>
+      <c r="I17" s="192">
         <f t="shared" si="0"/>
-        <v>4.2770000000000259</v>
-      </c>
-      <c r="J17" s="198">
+        <v>1.700999999999981</v>
+      </c>
+      <c r="J17" s="193">
         <f t="shared" si="2"/>
-        <v>5730.3857000000344</v>
-      </c>
-      <c r="K17" s="199">
+        <v>2279.0240999999746</v>
+      </c>
+      <c r="K17" s="194">
         <f>K8*E17%</f>
-        <v>-16775.607254779014</v>
-      </c>
-      <c r="L17" s="200">
+        <v>-10176.077355360991</v>
+      </c>
+      <c r="L17" s="195">
         <f t="shared" si="3"/>
-        <v>11314.616974220991</v>
-      </c>
-      <c r="M17" s="201">
+        <v>17914.146873639012</v>
+      </c>
+      <c r="M17" s="196">
         <f t="shared" si="4"/>
-        <v>61.100000000000364</v>
-      </c>
-      <c r="N17" s="196">
+        <v>24.299999999999727</v>
+      </c>
+      <c r="N17" s="191">
         <f t="shared" si="5"/>
-        <v>17045.002674221025</v>
+        <v>20193.170973638986</v>
       </c>
       <c r="O17" s="97">
         <f>N17+'prorrateo '!L10</f>
-        <v>122298.01423852102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+        <v>125446.18253793899</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="98">
         <v>10</v>
       </c>
@@ -4464,45 +4420,45 @@
         <v>5.04</v>
       </c>
       <c r="F18" s="103">
-        <v>2080.5</v>
+        <v>2270.5</v>
       </c>
       <c r="G18" s="103">
-        <v>2270.5</v>
+        <v>2354.6999999999998</v>
       </c>
       <c r="H18" s="104">
         <f t="shared" si="1"/>
-        <v>190</v>
+        <v>84.199999999999818</v>
       </c>
       <c r="I18" s="105">
         <f t="shared" si="0"/>
-        <v>13.3</v>
+        <v>5.8939999999999877</v>
       </c>
       <c r="J18" s="116">
         <f t="shared" si="2"/>
-        <v>17819.530000000002</v>
+        <v>7896.8653999999833</v>
       </c>
       <c r="K18" s="106">
         <f>K8*E18%</f>
-        <v>-16610.817399624011</v>
+        <v>-10076.115888215991</v>
       </c>
       <c r="L18" s="127">
         <f t="shared" si="3"/>
-        <v>11203.471424375992</v>
+        <v>17738.172935784016</v>
       </c>
       <c r="M18" s="107">
         <f t="shared" si="4"/>
-        <v>190</v>
+        <v>84.199999999999818</v>
       </c>
       <c r="N18" s="104">
         <f t="shared" si="5"/>
-        <v>29023.001424375994</v>
+        <v>25635.038335784</v>
       </c>
       <c r="O18" s="97">
         <f>N18+'prorrateo '!L11</f>
-        <v>133242.09342517599</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>129854.13033658401</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="98">
         <v>11</v>
       </c>
@@ -4519,45 +4475,45 @@
         <v>5.21</v>
       </c>
       <c r="F19" s="103">
-        <v>3819.2</v>
+        <v>4351.6000000000004</v>
       </c>
       <c r="G19" s="103">
-        <v>4351.6000000000004</v>
+        <v>4574.8999999999996</v>
       </c>
       <c r="H19" s="104">
         <f t="shared" si="1"/>
-        <v>532.40000000000055</v>
+        <v>223.29999999999927</v>
       </c>
       <c r="I19" s="105">
         <f t="shared" si="0"/>
-        <v>37.268000000000043</v>
+        <v>15.63099999999995</v>
       </c>
       <c r="J19" s="116">
         <f t="shared" si="2"/>
-        <v>49932.198800000057</v>
+        <v>20942.637099999934</v>
       </c>
       <c r="K19" s="106">
         <f>K8*E19%</f>
-        <v>-17171.102907151013</v>
+        <v>-10415.98487650899</v>
       </c>
       <c r="L19" s="127">
         <f t="shared" si="3"/>
-        <v>11581.366293848991</v>
+        <v>18336.484324491015</v>
       </c>
       <c r="M19" s="107">
         <f>G19-F19</f>
-        <v>532.40000000000055</v>
+        <v>223.29999999999927</v>
       </c>
       <c r="N19" s="104">
         <f t="shared" si="5"/>
-        <v>61513.565093849043</v>
+        <v>39279.12142449095</v>
       </c>
       <c r="O19" s="97">
         <f>N19+'prorrateo '!L12</f>
-        <v>169247.98361054907</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>147013.53994119097</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="98">
         <v>12</v>
       </c>
@@ -4574,100 +4530,100 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F20" s="103">
-        <v>5380.5</v>
+        <v>5489.3</v>
       </c>
       <c r="G20" s="103">
-        <v>5489.3</v>
+        <v>6064.7</v>
       </c>
       <c r="H20" s="104">
         <f t="shared" si="1"/>
-        <v>108.80000000000018</v>
+        <v>575.39999999999964</v>
       </c>
       <c r="I20" s="105">
         <f t="shared" si="0"/>
-        <v>7.6160000000000139</v>
+        <v>40.277999999999977</v>
       </c>
       <c r="J20" s="116">
         <f t="shared" si="2"/>
-        <v>10204.025600000017</v>
+        <v>53965.03979999997</v>
       </c>
       <c r="K20" s="106">
         <f>K8*E20%</f>
-        <v>-16841.523196841015</v>
+        <v>-10216.061942218992</v>
       </c>
       <c r="L20" s="127">
         <f t="shared" si="3"/>
-        <v>11359.075194158992</v>
+        <v>17984.536448781015</v>
       </c>
       <c r="M20" s="107">
         <f t="shared" si="4"/>
-        <v>108.80000000000018</v>
+        <v>575.39999999999964</v>
       </c>
       <c r="N20" s="104">
         <f t="shared" si="5"/>
-        <v>21563.100794159007</v>
+        <v>71949.576248780984</v>
       </c>
       <c r="O20" s="97">
         <f>N20+'prorrateo '!L13</f>
-        <v>127229.68018385902</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+        <v>177616.155638481</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="98">
         <v>13</v>
       </c>
       <c r="B21" s="89">
         <v>13</v>
       </c>
-      <c r="C21" s="222" t="s">
+      <c r="C21" s="212" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="223" t="s">
+      <c r="D21" s="213" t="s">
         <v>49</v>
       </c>
-      <c r="E21" s="224">
+      <c r="E21" s="214">
         <v>5.09</v>
       </c>
-      <c r="F21" s="225">
-        <v>3851</v>
-      </c>
-      <c r="G21" s="225">
+      <c r="F21" s="215">
         <v>4112.1000000000004</v>
       </c>
-      <c r="H21" s="148">
+      <c r="G21" s="215">
+        <v>4199</v>
+      </c>
+      <c r="H21" s="147">
         <f t="shared" si="1"/>
-        <v>261.10000000000036</v>
-      </c>
-      <c r="I21" s="226">
+        <v>86.899999999999636</v>
+      </c>
+      <c r="I21" s="216">
         <f t="shared" si="0"/>
-        <v>18.277000000000026</v>
-      </c>
-      <c r="J21" s="227">
+        <v>6.0829999999999753</v>
+      </c>
+      <c r="J21" s="217">
         <f t="shared" si="2"/>
-        <v>24487.785700000037</v>
-      </c>
-      <c r="K21" s="149">
+        <v>8150.0902999999662</v>
+      </c>
+      <c r="K21" s="148">
         <f>K8*E21%</f>
-        <v>-16775.607254779014</v>
-      </c>
-      <c r="L21" s="150">
+        <v>-10176.077355360991</v>
+      </c>
+      <c r="L21" s="149">
         <f t="shared" si="3"/>
-        <v>11314.616974220991</v>
-      </c>
-      <c r="M21" s="151">
+        <v>17914.146873639012</v>
+      </c>
+      <c r="M21" s="150">
         <f t="shared" si="4"/>
-        <v>261.10000000000036</v>
-      </c>
-      <c r="N21" s="148">
+        <v>86.899999999999636</v>
+      </c>
+      <c r="N21" s="147">
         <f t="shared" si="5"/>
-        <v>35802.402674221026</v>
+        <v>26064.23717363898</v>
       </c>
       <c r="O21" s="97">
         <f>N21+'prorrateo '!L14</f>
-        <v>407312.36323292105</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+        <v>86533.464537038977</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="98">
         <v>14</v>
       </c>
@@ -4684,45 +4640,45 @@
         <v>5.04</v>
       </c>
       <c r="F22" s="103">
-        <v>2333</v>
+        <v>2441.5</v>
       </c>
       <c r="G22" s="103">
-        <v>2441.5</v>
+        <v>2497.1</v>
       </c>
       <c r="H22" s="104">
         <f t="shared" si="1"/>
-        <v>108.5</v>
+        <v>55.599999999999909</v>
       </c>
       <c r="I22" s="105">
         <f t="shared" si="0"/>
-        <v>7.5950000000000006</v>
+        <v>3.8919999999999941</v>
       </c>
       <c r="J22" s="116">
         <f t="shared" si="2"/>
-        <v>10175.889500000001</v>
+        <v>5214.557199999992</v>
       </c>
       <c r="K22" s="106">
         <f>K8*E22%</f>
-        <v>-16610.817399624011</v>
+        <v>-10076.115888215991</v>
       </c>
       <c r="L22" s="127">
         <f t="shared" si="3"/>
-        <v>11203.471424375992</v>
+        <v>17738.172935784016</v>
       </c>
       <c r="M22" s="107">
         <f t="shared" si="4"/>
-        <v>108.5</v>
+        <v>55.599999999999909</v>
       </c>
       <c r="N22" s="104">
         <f t="shared" si="5"/>
-        <v>21379.360924375993</v>
+        <v>22952.730135784008</v>
       </c>
       <c r="O22" s="97">
         <f>N22+'prorrateo '!L15</f>
-        <v>125598.45280517597</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+        <v>127171.82676707998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="98">
         <v>15</v>
       </c>
@@ -4739,45 +4695,45 @@
         <v>5.21</v>
       </c>
       <c r="F23" s="103">
-        <v>4630.6000000000004</v>
+        <v>4886.6000000000004</v>
       </c>
       <c r="G23" s="103">
-        <v>4886.6000000000004</v>
+        <v>5000</v>
       </c>
       <c r="H23" s="104">
         <f t="shared" si="1"/>
-        <v>256</v>
+        <v>113.39999999999964</v>
       </c>
       <c r="I23" s="105">
         <f t="shared" si="0"/>
-        <v>17.920000000000002</v>
+        <v>7.9379999999999749</v>
       </c>
       <c r="J23" s="116">
         <f t="shared" si="2"/>
-        <v>24009.472000000002</v>
+        <v>10635.445799999967</v>
       </c>
       <c r="K23" s="106">
         <f>K8*E23%</f>
-        <v>-17171.102907151013</v>
+        <v>-10415.98487650899</v>
       </c>
       <c r="L23" s="127">
         <f t="shared" si="3"/>
-        <v>11581.366293848991</v>
+        <v>18336.484324491015</v>
       </c>
       <c r="M23" s="107">
         <f t="shared" si="4"/>
-        <v>256</v>
+        <v>113.39999999999964</v>
       </c>
       <c r="N23" s="104">
         <f t="shared" si="5"/>
-        <v>35590.838293848996</v>
+        <v>28971.93012449098</v>
       </c>
       <c r="O23" s="97">
         <f>N23+'prorrateo '!L16</f>
-        <v>143325.25681054901</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+        <v>136706.348641191</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="98">
         <v>16</v>
       </c>
@@ -4794,45 +4750,45 @@
         <v>5.04</v>
       </c>
       <c r="F24" s="103">
-        <v>1675.8</v>
+        <v>1776.7</v>
       </c>
       <c r="G24" s="103">
-        <v>1776.7</v>
+        <v>1802.7</v>
       </c>
       <c r="H24" s="104">
         <f t="shared" si="1"/>
-        <v>100.90000000000009</v>
+        <v>26</v>
       </c>
       <c r="I24" s="105">
         <f t="shared" si="0"/>
-        <v>7.0630000000000068</v>
+        <v>1.8200000000000003</v>
       </c>
       <c r="J24" s="116">
         <f t="shared" si="2"/>
-        <v>9463.108300000009</v>
+        <v>2438.462</v>
       </c>
       <c r="K24" s="106">
         <f>K8*E24%</f>
-        <v>-16610.817399624011</v>
+        <v>-10076.115888215991</v>
       </c>
       <c r="L24" s="127">
         <f t="shared" si="3"/>
-        <v>11203.471424375992</v>
+        <v>17738.172935784016</v>
       </c>
       <c r="M24" s="107">
         <f t="shared" si="4"/>
-        <v>100.90000000000009</v>
+        <v>26</v>
       </c>
       <c r="N24" s="104">
         <f t="shared" si="5"/>
-        <v>20666.579724376003</v>
+        <v>20176.634935784015</v>
       </c>
       <c r="O24" s="97">
         <f>N24+'prorrateo '!L17</f>
-        <v>124885.67172517601</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+        <v>124395.72693658402</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="98">
         <v>17</v>
       </c>
@@ -4849,45 +4805,45 @@
         <v>5.21</v>
       </c>
       <c r="F25" s="103">
-        <v>1689</v>
+        <v>1869.3</v>
       </c>
       <c r="G25" s="103">
-        <v>1869.3</v>
+        <v>1949.4</v>
       </c>
       <c r="H25" s="104">
         <f t="shared" si="1"/>
-        <v>180.29999999999995</v>
+        <v>80.100000000000136</v>
       </c>
       <c r="I25" s="105">
         <f t="shared" si="0"/>
-        <v>12.620999999999999</v>
+        <v>5.60700000000001</v>
       </c>
       <c r="J25" s="116">
         <f t="shared" si="2"/>
-        <v>16909.796099999996</v>
+        <v>7512.338700000013</v>
       </c>
       <c r="K25" s="106">
         <f>K8*E25%</f>
-        <v>-17171.102907151013</v>
+        <v>-10415.98487650899</v>
       </c>
       <c r="L25" s="127">
         <f t="shared" si="3"/>
-        <v>11581.366293848991</v>
+        <v>18336.484324491015</v>
       </c>
       <c r="M25" s="107">
         <f t="shared" si="4"/>
-        <v>180.29999999999995</v>
+        <v>80.100000000000136</v>
       </c>
       <c r="N25" s="104">
         <f t="shared" si="5"/>
-        <v>28491.162393848987</v>
+        <v>25848.82302449103</v>
       </c>
       <c r="O25" s="97">
         <f>N25+'prorrateo '!L18</f>
-        <v>136225.580910549</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+        <v>133583.24154119103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="98">
         <v>18</v>
       </c>
@@ -4904,92 +4860,92 @@
         <v>7.4</v>
       </c>
       <c r="F26" s="103">
-        <v>8479.7999999999993</v>
+        <v>8914.5</v>
       </c>
       <c r="G26" s="103">
-        <v>8914.5</v>
+        <v>9077.1</v>
       </c>
       <c r="H26" s="104">
         <f t="shared" si="1"/>
-        <v>434.70000000000073</v>
+        <v>162.60000000000036</v>
       </c>
       <c r="I26" s="105">
         <f t="shared" si="0"/>
-        <v>30.429000000000055</v>
+        <v>11.382000000000026</v>
       </c>
       <c r="J26" s="116">
         <f t="shared" si="2"/>
-        <v>40769.208900000071</v>
+        <v>15249.766200000035</v>
       </c>
       <c r="K26" s="106">
         <f>K8*E26%</f>
-        <v>-24388.898562940019</v>
+        <v>-14794.297137459987</v>
       </c>
       <c r="L26" s="127">
         <f t="shared" si="3"/>
-        <v>16449.541377059988</v>
+        <v>26044.142802540024</v>
       </c>
       <c r="M26" s="107">
         <f t="shared" si="4"/>
-        <v>434.70000000000073</v>
+        <v>162.60000000000036</v>
       </c>
       <c r="N26" s="104">
         <f>J26+L26</f>
-        <v>57218.750277060055</v>
+        <v>41293.909002540058</v>
       </c>
       <c r="O26" s="97">
         <f>N26+'prorrateo '!L19</f>
-        <v>210238.84567506006</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>194314.00440054006</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="98">
         <v>19</v>
       </c>
       <c r="B27" s="90">
         <v>19</v>
       </c>
-      <c r="C27" s="202" t="s">
+      <c r="C27" s="197" t="s">
         <v>65</v>
       </c>
-      <c r="D27" s="203"/>
-      <c r="E27" s="204">
+      <c r="D27" s="198"/>
+      <c r="E27" s="199">
         <v>1.08</v>
       </c>
-      <c r="F27" s="194"/>
-      <c r="G27" s="195"/>
-      <c r="H27" s="196">
+      <c r="F27" s="189"/>
+      <c r="G27" s="190"/>
+      <c r="H27" s="191">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="197">
+      <c r="I27" s="192">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="198"/>
-      <c r="K27" s="199"/>
-      <c r="L27" s="200">
+      <c r="J27" s="193"/>
+      <c r="K27" s="194"/>
+      <c r="L27" s="195">
         <f t="shared" si="3"/>
-        <v>2400.7438766519986</v>
-      </c>
-      <c r="M27" s="201">
-        <v>0</v>
-      </c>
-      <c r="N27" s="196">
+        <v>3801.0370576680034</v>
+      </c>
+      <c r="M27" s="196">
+        <v>0</v>
+      </c>
+      <c r="N27" s="191">
         <f t="shared" ref="N27:N37" si="6">J27+L27</f>
-        <v>2400.7438766519986</v>
+        <v>3801.0370576680034</v>
       </c>
       <c r="O27" s="97">
         <f>N27+'prorrateo '!L20</f>
-        <v>24733.406448252001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+        <v>26133.699629268005</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="98">
         <v>20</v>
       </c>
       <c r="B28" s="90"/>
-      <c r="C28" s="170" t="s">
+      <c r="C28" s="169" t="s">
         <v>66</v>
       </c>
       <c r="D28" s="102"/>
@@ -5001,64 +4957,64 @@
       <c r="H28" s="104">
         <v>0</v>
       </c>
-      <c r="I28" s="171">
+      <c r="I28" s="170">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="172"/>
+      <c r="J28" s="171"/>
       <c r="K28" s="106"/>
       <c r="L28" s="127">
         <f t="shared" si="3"/>
-        <v>2400.7438766519986</v>
+        <v>3801.0370576680034</v>
       </c>
       <c r="M28" s="107">
         <v>0</v>
       </c>
       <c r="N28" s="104">
         <f t="shared" si="6"/>
-        <v>2400.7438766519986</v>
+        <v>3801.0370576680034</v>
       </c>
       <c r="O28" s="97">
         <f>N28+'prorrateo '!L21</f>
-        <v>24733.406448252001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+        <v>26133.699629268005</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="98"/>
       <c r="B29" s="90"/>
-      <c r="C29" s="159" t="s">
+      <c r="C29" s="158" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="147"/>
-      <c r="E29" s="147">
+      <c r="D29" s="146"/>
+      <c r="E29" s="146">
         <v>1.08</v>
       </c>
-      <c r="F29" s="147"/>
-      <c r="G29" s="147"/>
-      <c r="H29" s="148"/>
-      <c r="I29" s="160"/>
-      <c r="J29" s="161"/>
-      <c r="K29" s="149"/>
-      <c r="L29" s="150">
+      <c r="F29" s="146"/>
+      <c r="G29" s="146"/>
+      <c r="H29" s="147"/>
+      <c r="I29" s="159"/>
+      <c r="J29" s="160"/>
+      <c r="K29" s="148"/>
+      <c r="L29" s="149">
         <f t="shared" si="3"/>
-        <v>2400.7438766519986</v>
-      </c>
-      <c r="M29" s="151">
-        <v>0</v>
-      </c>
-      <c r="N29" s="148">
+        <v>3801.0370576680034</v>
+      </c>
+      <c r="M29" s="150">
+        <v>0</v>
+      </c>
+      <c r="N29" s="147">
         <f t="shared" si="6"/>
-        <v>2400.7438766519986</v>
+        <v>3801.0370576680034</v>
       </c>
       <c r="O29" s="97">
         <f>N29+'prorrateo '!L22</f>
-        <v>264999.258893052</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+        <v>299236.15524632402</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="98"/>
       <c r="B30" s="90"/>
-      <c r="C30" s="170" t="s">
+      <c r="C30" s="169" t="s">
         <v>68</v>
       </c>
       <c r="D30" s="102"/>
@@ -5068,29 +5024,29 @@
       <c r="F30" s="102"/>
       <c r="G30" s="102"/>
       <c r="H30" s="104"/>
-      <c r="I30" s="171"/>
-      <c r="J30" s="172"/>
+      <c r="I30" s="170"/>
+      <c r="J30" s="171"/>
       <c r="K30" s="106"/>
       <c r="L30" s="127">
         <f t="shared" si="3"/>
-        <v>2400.7438766519986</v>
+        <v>3801.0370576680034</v>
       </c>
       <c r="M30" s="107">
         <v>0</v>
       </c>
       <c r="N30" s="104">
         <f t="shared" si="6"/>
-        <v>2400.7438766519986</v>
+        <v>3801.0370576680034</v>
       </c>
       <c r="O30" s="97">
         <f>N30+'prorrateo '!L23</f>
-        <v>56863.282637052005</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+        <v>26133.699629268005</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="98"/>
       <c r="B31" s="90"/>
-      <c r="C31" s="170" t="s">
+      <c r="C31" s="169" t="s">
         <v>69</v>
       </c>
       <c r="D31" s="102" t="s">
@@ -5102,60 +5058,60 @@
       <c r="F31" s="102"/>
       <c r="G31" s="102"/>
       <c r="H31" s="104"/>
-      <c r="I31" s="171"/>
-      <c r="J31" s="172"/>
+      <c r="I31" s="170"/>
+      <c r="J31" s="171"/>
       <c r="K31" s="106"/>
       <c r="L31" s="127">
         <f t="shared" si="3"/>
-        <v>2400.7438766519986</v>
+        <v>3801.0370576680034</v>
       </c>
       <c r="M31" s="107">
         <v>0</v>
       </c>
       <c r="N31" s="104">
         <f t="shared" si="6"/>
-        <v>2400.7438766519986</v>
+        <v>3801.0370576680034</v>
       </c>
       <c r="O31" s="97">
         <f>N31+'prorrateo '!L24</f>
-        <v>24733.406448252001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+        <v>26133.699629268005</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="99"/>
-      <c r="B32" s="228"/>
-      <c r="C32" s="159" t="s">
+      <c r="B32" s="218"/>
+      <c r="C32" s="158" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="147" t="s">
+      <c r="D32" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="E32" s="147">
+      <c r="E32" s="146">
         <v>1.08</v>
       </c>
-      <c r="F32" s="147"/>
-      <c r="G32" s="147"/>
-      <c r="H32" s="148"/>
-      <c r="I32" s="160"/>
-      <c r="J32" s="161"/>
-      <c r="K32" s="149"/>
-      <c r="L32" s="150">
+      <c r="F32" s="146"/>
+      <c r="G32" s="146"/>
+      <c r="H32" s="147"/>
+      <c r="I32" s="159"/>
+      <c r="J32" s="160"/>
+      <c r="K32" s="148"/>
+      <c r="L32" s="149">
         <f t="shared" si="3"/>
-        <v>2400.7438766519986</v>
-      </c>
-      <c r="M32" s="151">
-        <v>0</v>
-      </c>
-      <c r="N32" s="148">
+        <v>3801.0370576680034</v>
+      </c>
+      <c r="M32" s="150">
+        <v>0</v>
+      </c>
+      <c r="N32" s="147">
         <f t="shared" si="6"/>
-        <v>2400.7438766519986</v>
+        <v>3801.0370576680034</v>
       </c>
       <c r="O32" s="97">
         <f>N32+'prorrateo '!L25</f>
-        <v>81227.999117051993</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+        <v>26133.699629268005</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="98"/>
       <c r="B33" s="90"/>
       <c r="C33" s="130" t="s">
@@ -5175,21 +5131,21 @@
       <c r="K33" s="113"/>
       <c r="L33" s="127">
         <f t="shared" si="3"/>
-        <v>2400.7438766519986</v>
+        <v>3801.0370576680034</v>
       </c>
       <c r="M33" s="107">
         <v>0</v>
       </c>
       <c r="N33" s="104">
         <f t="shared" si="6"/>
-        <v>2400.7438766519986</v>
+        <v>3801.0370576680034</v>
       </c>
       <c r="O33" s="97">
         <f>N33+'prorrateo '!L26</f>
-        <v>24733.406448252001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+        <v>26133.699629268005</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="98"/>
       <c r="B34" s="90"/>
       <c r="C34" s="130" t="s">
@@ -5209,26 +5165,26 @@
       <c r="K34" s="113"/>
       <c r="L34" s="127">
         <f t="shared" si="3"/>
-        <v>2400.7438766519986</v>
+        <v>3801.0370576680034</v>
       </c>
       <c r="M34" s="107">
         <v>0</v>
       </c>
       <c r="N34" s="104">
         <f t="shared" si="6"/>
-        <v>2400.7438766519986</v>
+        <v>3801.0370576680034</v>
       </c>
       <c r="O34" s="97">
         <f>N34+'prorrateo '!L27</f>
-        <v>24733.406448252001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+        <v>26133.699629268005</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="98">
         <v>21</v>
       </c>
       <c r="B35" s="90"/>
-      <c r="C35" s="170" t="s">
+      <c r="C35" s="169" t="s">
         <v>73</v>
       </c>
       <c r="D35" s="102"/>
@@ -5240,34 +5196,34 @@
       <c r="H35" s="104">
         <v>0</v>
       </c>
-      <c r="I35" s="171">
+      <c r="I35" s="170">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J35" s="173"/>
+      <c r="J35" s="172"/>
       <c r="K35" s="106"/>
       <c r="L35" s="127">
         <f t="shared" si="3"/>
-        <v>2400.7438766519986</v>
+        <v>3801.0370576680034</v>
       </c>
       <c r="M35" s="107">
         <v>0</v>
       </c>
       <c r="N35" s="104">
         <f t="shared" si="6"/>
-        <v>2400.7438766519986</v>
+        <v>3801.0370576680034</v>
       </c>
       <c r="O35" s="97">
         <f>N35+'prorrateo '!L28</f>
-        <v>24733.406448252001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+        <v>26133.699629268005</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="98">
         <v>22</v>
       </c>
       <c r="B36" s="90"/>
-      <c r="C36" s="170" t="s">
+      <c r="C36" s="169" t="s">
         <v>74</v>
       </c>
       <c r="D36" s="102" t="s">
@@ -5281,29 +5237,29 @@
       <c r="H36" s="104">
         <v>0</v>
       </c>
-      <c r="I36" s="171">
+      <c r="I36" s="170">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J36" s="173"/>
+      <c r="J36" s="172"/>
       <c r="K36" s="106"/>
       <c r="L36" s="127">
         <f t="shared" si="3"/>
-        <v>2400.7438766519986</v>
+        <v>3801.0370576680034</v>
       </c>
       <c r="M36" s="107">
         <v>0</v>
       </c>
       <c r="N36" s="104">
         <f t="shared" si="6"/>
-        <v>2400.7438766519986</v>
+        <v>3801.0370576680034</v>
       </c>
       <c r="O36" s="97">
         <f>N36+'prorrateo '!L29</f>
-        <v>24733.406448252001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+        <v>26133.699629268005</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="98">
         <v>23</v>
       </c>
@@ -5333,7 +5289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="98">
         <v>24</v>
       </c>
@@ -5347,21 +5303,21 @@
       <c r="I38" s="112"/>
       <c r="J38" s="117">
         <f>SUM(J10:J37)</f>
-        <v>329579.71031000023</v>
+        <v>199922.9342899998</v>
       </c>
       <c r="K38" s="113"/>
       <c r="L38" s="113">
         <f>SUM(L10:L37)</f>
-        <v>222291.09968999989</v>
+        <v>351947.87571000058</v>
       </c>
       <c r="M38" s="114"/>
       <c r="N38" s="110">
         <f>SUM(N10:N37)</f>
-        <v>551870.80999999982</v>
+        <v>551870.80999999994</v>
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="78"/>
       <c r="C39" s="91"/>
       <c r="D39" s="92"/>
@@ -5374,61 +5330,61 @@
       <c r="H39" s="93"/>
       <c r="I39" s="94">
         <f>SUM(I10:I38)</f>
-        <v>245.98910000000015</v>
+        <v>149.21689999999987</v>
       </c>
       <c r="J39" s="126"/>
       <c r="K39" s="94"/>
       <c r="L39" s="133">
         <f>L38+J38</f>
-        <v>551870.81000000006</v>
+        <v>551870.81000000041</v>
       </c>
       <c r="M39" s="93"/>
       <c r="N39" s="93"/>
       <c r="O39" s="79"/>
     </row>
-    <row r="40" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="95" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="243"/>
-      <c r="D40" s="241"/>
-      <c r="E40" s="241"/>
-      <c r="F40" s="241"/>
-      <c r="G40" s="241"/>
-      <c r="H40" s="241"/>
-      <c r="I40" s="241"/>
-      <c r="J40" s="241"/>
-      <c r="K40" s="241"/>
-      <c r="L40" s="241"/>
-      <c r="M40" s="241"/>
-      <c r="N40" s="241"/>
+      <c r="C40" s="240"/>
+      <c r="D40" s="238"/>
+      <c r="E40" s="238"/>
+      <c r="F40" s="238"/>
+      <c r="G40" s="238"/>
+      <c r="H40" s="238"/>
+      <c r="I40" s="238"/>
+      <c r="J40" s="238"/>
+      <c r="K40" s="238"/>
+      <c r="L40" s="238"/>
+      <c r="M40" s="238"/>
+      <c r="N40" s="238"/>
       <c r="O40" s="95"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H41" s="79"/>
       <c r="J41" s="96"/>
       <c r="K41" s="96"/>
       <c r="L41" s="96"/>
       <c r="N41" s="97"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="L44" s="152"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L44" s="151"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L45" s="96"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="E46" s="153"/>
-      <c r="F46" s="153"/>
-      <c r="G46" s="153"/>
-      <c r="H46" s="153"/>
-      <c r="I46" s="153"/>
-      <c r="J46" s="153"/>
-      <c r="K46" s="153"/>
-      <c r="L46" s="154"/>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E46" s="152"/>
+      <c r="F46" s="152"/>
+      <c r="G46" s="152"/>
+      <c r="H46" s="152"/>
+      <c r="I46" s="152"/>
+      <c r="J46" s="152"/>
+      <c r="K46" s="152"/>
+      <c r="L46" s="153"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/ROSALES/Noviembre/expensas rosales Noviembre.xlsx
+++ b/ROSALES/Noviembre/expensas rosales Noviembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Noviembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\ROSALES\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E196E9E5-C8BC-4115-8DAB-5BC82CB633CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC4D5A4-710B-4D06-9F65-F645C3AFACD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -20,14 +20,14 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$64</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$N$40</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$L$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$37</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="125">
   <si>
     <t>TOTAL</t>
   </si>
@@ -401,6 +401,9 @@
   </si>
   <si>
     <t>CUOTA PLAN DE PAGOS (4/6)</t>
+  </si>
+  <si>
+    <t>EDESUR</t>
   </si>
 </sst>
 </file>
@@ -1024,7 +1027,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1298,7 +1301,6 @@
     <xf numFmtId="174" fontId="9" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1831,16 +1833,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:F65"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -1848,22 +1850,22 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="15"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
@@ -1874,89 +1876,89 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="35" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="36"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="28"/>
       <c r="B17" s="37"/>
       <c r="C17" s="33"/>
       <c r="D17" s="4"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="28" t="s">
         <v>105</v>
       </c>
       <c r="B18" s="38"/>
-      <c r="C18" s="223">
+      <c r="C18" s="222">
         <v>76654</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="224">
+      <c r="C19" s="223">
         <v>316973.44</v>
       </c>
       <c r="D19" s="20"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="28" t="s">
         <v>25</v>
       </c>
       <c r="B20" s="39"/>
-      <c r="C20" s="223">
+      <c r="C20" s="222">
         <v>80000</v>
       </c>
       <c r="D20" s="20"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="28" t="s">
         <v>122</v>
       </c>
       <c r="B21" s="39"/>
-      <c r="C21" s="223">
+      <c r="C21" s="222">
         <v>15748</v>
       </c>
       <c r="D21" s="4"/>
@@ -1965,26 +1967,26 @@
         <v>115</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="28" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="223">
+      <c r="C22" s="222">
         <v>83400</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="40"/>
       <c r="B23" s="41"/>
-      <c r="C23" s="225">
+      <c r="C23" s="224">
         <f>SUM(C17:C22)</f>
         <v>572775.43999999994</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="35" t="s">
         <v>12</v>
       </c>
@@ -1993,40 +1995,40 @@
       <c r="D24" s="45"/>
       <c r="F24" s="12"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="28" t="s">
         <v>97</v>
       </c>
       <c r="B25" s="42"/>
-      <c r="C25" s="223">
+      <c r="C25" s="222">
         <f>349151.87+ (349151.87*10%)</f>
         <v>384067.05699999997</v>
       </c>
       <c r="D25" s="45"/>
       <c r="F25" s="12"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="28" t="s">
         <v>98</v>
       </c>
       <c r="B26" s="42"/>
-      <c r="C26" s="223">
+      <c r="C26" s="222">
         <v>5684</v>
       </c>
       <c r="D26" s="45"/>
       <c r="F26" s="12"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="28" t="s">
         <v>112</v>
       </c>
       <c r="B27" s="42"/>
-      <c r="C27" s="223">
+      <c r="C27" s="222">
         <v>55000</v>
       </c>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="28" t="s">
         <v>91</v>
       </c>
@@ -2036,7 +2038,7 @@
       <c r="E28" s="6"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="40"/>
       <c r="B29" s="41"/>
       <c r="C29" s="23">
@@ -2045,7 +2047,7 @@
       </c>
       <c r="F29" s="12"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="30" t="s">
         <v>6</v>
       </c>
@@ -2056,48 +2058,48 @@
       </c>
       <c r="F30" s="12"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C31" s="24"/>
       <c r="F31" s="12"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="24"/>
       <c r="F32" s="12"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="28" t="s">
         <v>121</v>
       </c>
       <c r="B33" s="28"/>
-      <c r="C33" s="223">
+      <c r="C33" s="222">
         <v>610000</v>
       </c>
       <c r="F33" s="12"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="28" t="s">
         <v>120</v>
       </c>
       <c r="B34" s="28"/>
-      <c r="C34" s="226">
+      <c r="C34" s="225">
         <v>1034026.5</v>
       </c>
       <c r="F34" s="12"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="28"/>
       <c r="B35" s="28"/>
       <c r="C35" s="34"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C36" s="25"/>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="173" t="s">
         <v>110</v>
       </c>
@@ -2107,11 +2109,11 @@
       </c>
       <c r="F37" s="12"/>
     </row>
-    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C38" s="25"/>
       <c r="F38" s="12"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>15</v>
       </c>
@@ -2122,7 +2124,7 @@
       </c>
       <c r="E39" s="6"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="18" t="s">
         <v>7</v>
       </c>
@@ -2132,49 +2134,49 @@
         <v>2661552.997</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="231" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="230" t="s">
         <v>109</v>
       </c>
-      <c r="B43" s="232"/>
-      <c r="C43" s="232"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="232"/>
-      <c r="B44" s="232"/>
-      <c r="C44" s="232"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="232"/>
-      <c r="B45" s="232"/>
-      <c r="C45" s="232"/>
-    </row>
-    <row r="46" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="232"/>
-      <c r="B46" s="232"/>
-      <c r="C46" s="232"/>
+      <c r="B43" s="231"/>
+      <c r="C43" s="231"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="231"/>
+      <c r="B44" s="231"/>
+      <c r="C44" s="231"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="231"/>
+      <c r="B45" s="231"/>
+      <c r="C45" s="231"/>
+    </row>
+    <row r="46" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="231"/>
+      <c r="B46" s="231"/>
+      <c r="C46" s="231"/>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
     </row>
-    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
       <c r="C47" s="154"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="202" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="201" t="s">
         <v>100</v>
       </c>
       <c r="B48" s="28"/>
-      <c r="C48" s="203">
+      <c r="C48" s="202">
         <v>1081522.6958899994</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="202" t="s">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="201" t="s">
         <v>119</v>
       </c>
       <c r="B49" s="28"/>
@@ -2185,18 +2187,18 @@
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="202" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="201" t="s">
         <v>96</v>
       </c>
       <c r="B50" s="28"/>
-      <c r="C50" s="204">
+      <c r="C50" s="203">
         <f>'prorrateo '!F31</f>
         <v>2610074.1626310009</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="202" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="201" t="s">
         <v>116</v>
       </c>
       <c r="B51" s="28"/>
@@ -2204,50 +2206,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="202" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="201" t="s">
         <v>123</v>
       </c>
       <c r="B52" s="28"/>
-      <c r="C52" s="204">
+      <c r="C52" s="203">
         <v>107386.2</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="202" t="s">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="201" t="s">
         <v>8</v>
       </c>
       <c r="B53" s="28"/>
-      <c r="C53" s="203">
+      <c r="C53" s="202">
         <f>SUM(C48:C52)</f>
         <v>1137430.0615210002</v>
       </c>
       <c r="D53" s="5"/>
     </row>
-    <row r="54" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="9"/>
       <c r="B54" s="8"/>
       <c r="C54" s="10"/>
     </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="227"/>
-      <c r="B55" s="227"/>
-      <c r="C55" s="227"/>
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="226"/>
+      <c r="B55" s="226"/>
+      <c r="C55" s="226"/>
       <c r="F55" s="44"/>
     </row>
-    <row r="56" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="228"/>
-      <c r="B56" s="228"/>
-      <c r="C56" s="228"/>
-    </row>
-    <row r="57" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="227"/>
+      <c r="B56" s="227"/>
+      <c r="C56" s="227"/>
+    </row>
+    <row r="57" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="26" t="s">
         <v>20</v>
       </c>
       <c r="B57" s="27"/>
       <c r="C57" s="29"/>
     </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="28" t="s">
         <v>23</v>
       </c>
@@ -2257,17 +2259,17 @@
         <v>-1644026.5</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="28"/>
       <c r="B59" s="28"/>
       <c r="C59" s="31"/>
     </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="28"/>
       <c r="B60" s="28"/>
       <c r="C60" s="32"/>
     </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="155" t="s">
         <v>0</v>
       </c>
@@ -2277,24 +2279,24 @@
         <v>-1644026.5</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="229" t="s">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="228" t="s">
         <v>107</v>
       </c>
-      <c r="B62" s="230"/>
-      <c r="C62" s="230"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="230"/>
-      <c r="B63" s="230"/>
-      <c r="C63" s="230"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="230"/>
-      <c r="B64" s="230"/>
-      <c r="C64" s="230"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="229"/>
+      <c r="C62" s="229"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="229"/>
+      <c r="B63" s="229"/>
+      <c r="C63" s="229"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="229"/>
+      <c r="B64" s="229"/>
+      <c r="C64" s="229"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="8"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
@@ -2321,59 +2323,60 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="11"/>
-    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" customWidth="1"/>
+    <col min="9" max="10" width="10.6640625" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" customWidth="1"/>
+    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" style="11"/>
+    <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="233">
-        <f>D1-K1</f>
+      <c r="B1" s="232">
+        <f>D1-L1</f>
         <v>1057642.1270000001</v>
       </c>
-      <c r="C1" s="233"/>
+      <c r="C1" s="232"/>
       <c r="D1" s="138">
         <v>1667839.1270000001</v>
       </c>
       <c r="E1" t="s">
         <v>102</v>
       </c>
-      <c r="G1" s="235">
+      <c r="G1" s="234">
         <v>400000</v>
       </c>
-      <c r="H1" s="235"/>
-      <c r="I1" s="236" t="s">
+      <c r="H1" s="234"/>
+      <c r="I1" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="J1" s="236"/>
-      <c r="K1" s="233">
-        <f>M1</f>
+      <c r="J1" s="235"/>
+      <c r="K1" s="235"/>
+      <c r="L1" s="232">
+        <f>N1</f>
         <v>610197</v>
       </c>
-      <c r="L1" s="233"/>
-      <c r="M1">
+      <c r="M1" s="232"/>
+      <c r="N1">
         <v>610197</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="46" t="s">
         <v>26</v>
       </c>
@@ -2395,23 +2398,26 @@
       <c r="G2" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="201" t="s">
+      <c r="H2" s="200" t="s">
         <v>92</v>
       </c>
       <c r="I2" s="50" t="s">
         <v>104</v>
       </c>
       <c r="J2" s="50" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="K2" s="50" t="s">
+      <c r="L2" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="L2" s="51" t="s">
+      <c r="M2" s="51" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="52" t="s">
         <v>31</v>
       </c>
@@ -2427,7 +2433,7 @@
       <c r="E3" s="129">
         <v>105505.57938970001</v>
       </c>
-      <c r="F3" s="220">
+      <c r="F3" s="219">
         <f>E3</f>
         <v>105505.57938970001</v>
       </c>
@@ -2444,20 +2450,24 @@
         <v>54045.512689700008</v>
       </c>
       <c r="J3" s="56">
+        <f>Edesur!N10</f>
+        <v>31008.737138781005</v>
+      </c>
+      <c r="K3" s="56">
         <f>G$1*D3/100</f>
         <v>20440.000000000004</v>
       </c>
-      <c r="K3" s="56">
-        <f>K$1*D3/100</f>
+      <c r="L3" s="56">
+        <f>L$1*D3/100</f>
         <v>31181.066700000003</v>
       </c>
-      <c r="L3" s="57">
-        <f>I3+G3+K3+J3+H3</f>
-        <v>105666.57938970001</v>
-      </c>
-      <c r="M3" s="44"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M3" s="57">
+        <f>I3+G3+L3+K3+H3+J3</f>
+        <v>136675.31652848102</v>
+      </c>
+      <c r="N3" s="44"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="58" t="s">
         <v>33</v>
       </c>
@@ -2473,7 +2483,7 @@
       <c r="E4" s="129">
         <v>104519.0115643</v>
       </c>
-      <c r="F4" s="220">
+      <c r="F4" s="219">
         <f>E4</f>
         <v>104519.0115643</v>
       </c>
@@ -2490,20 +2500,24 @@
         <v>53833.984264300001</v>
       </c>
       <c r="J4" s="56">
-        <f t="shared" ref="J4:J29" si="3">G$1*D4/100</f>
+        <f>Edesur!N11</f>
+        <v>27414.769973639028</v>
+      </c>
+      <c r="K4" s="56">
+        <f t="shared" ref="K4:K29" si="3">G$1*D4/100</f>
         <v>20360</v>
       </c>
-      <c r="K4" s="56">
-        <f t="shared" ref="K4:K29" si="4">K$1*D4/100</f>
+      <c r="L4" s="56">
+        <f t="shared" ref="L4:L29" si="4">L$1*D4/100</f>
         <v>31059.027300000002</v>
       </c>
-      <c r="L4" s="57">
-        <f t="shared" ref="L4:L29" si="5">I4+G4+K4+J4+H4</f>
-        <v>105253.0115643</v>
-      </c>
-      <c r="M4" s="44"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M4" s="57">
+        <f t="shared" ref="M4:M29" si="5">I4+G4+L4+K4+H4+J4</f>
+        <v>132667.78153793904</v>
+      </c>
+      <c r="N4" s="44"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
         <v>35</v>
       </c>
@@ -2517,7 +2531,7 @@
       <c r="E5" s="129">
         <v>407656.00631120004</v>
       </c>
-      <c r="F5" s="220">
+      <c r="F5" s="219">
         <f>497170.55-64957-F23</f>
         <v>377751.01123959996</v>
       </c>
@@ -2534,20 +2548,24 @@
         <v>53305.163200800009</v>
       </c>
       <c r="J5" s="56">
+        <f>Edesur!N12</f>
+        <v>27942.198535784013</v>
+      </c>
+      <c r="K5" s="56">
         <f t="shared" si="3"/>
         <v>20160</v>
       </c>
-      <c r="K5" s="56">
+      <c r="L5" s="56">
         <f t="shared" si="4"/>
         <v>30753.928799999998</v>
       </c>
-      <c r="L5" s="57">
+      <c r="M5" s="57">
         <f t="shared" si="5"/>
-        <v>135320.28687526408</v>
-      </c>
-      <c r="M5" s="44"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>163262.48541104808</v>
+      </c>
+      <c r="N5" s="44"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="58" t="s">
         <v>37</v>
       </c>
@@ -2561,7 +2579,7 @@
       <c r="E6" s="129">
         <v>107734.41851670001</v>
       </c>
-      <c r="F6" s="220"/>
+      <c r="F6" s="219"/>
       <c r="G6" s="56">
         <f t="shared" si="0"/>
         <v>107734.41851670001</v>
@@ -2575,20 +2593,24 @@
         <v>55103.154816700007</v>
       </c>
       <c r="J6" s="56">
+        <f>Edesur!N13</f>
+        <v>25698.763824491016</v>
+      </c>
+      <c r="K6" s="56">
         <f t="shared" si="3"/>
         <v>20840</v>
       </c>
-      <c r="K6" s="56">
+      <c r="L6" s="56">
         <f t="shared" si="4"/>
         <v>31791.2637</v>
       </c>
-      <c r="L6" s="57">
+      <c r="M6" s="57">
         <f t="shared" si="5"/>
-        <v>219778.21377406802</v>
-      </c>
-      <c r="O6" s="175"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>245476.97759855902</v>
+      </c>
+      <c r="P6" s="175"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="58" t="s">
         <v>35</v>
       </c>
@@ -2604,7 +2626,7 @@
       <c r="E7" s="129">
         <v>105666.57938970001</v>
       </c>
-      <c r="F7" s="220">
+      <c r="F7" s="219">
         <f t="shared" ref="F7:F11" si="6">E7</f>
         <v>105666.57938970001</v>
       </c>
@@ -2621,20 +2643,24 @@
         <v>54045.512689700008</v>
       </c>
       <c r="J7" s="56">
+        <f>Edesur!N14</f>
+        <v>27391.372548781012</v>
+      </c>
+      <c r="K7" s="56">
         <f t="shared" si="3"/>
         <v>20440.000000000004</v>
       </c>
-      <c r="K7" s="56">
+      <c r="L7" s="56">
         <f t="shared" si="4"/>
         <v>31181.066700000003</v>
       </c>
-      <c r="L7" s="57">
+      <c r="M7" s="57">
         <f t="shared" si="5"/>
-        <v>105666.57938970001</v>
-      </c>
-      <c r="O7" s="175"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>133057.95193848101</v>
+      </c>
+      <c r="P7" s="175"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="58" t="s">
         <v>40</v>
       </c>
@@ -2648,7 +2674,7 @@
       <c r="E8" s="129">
         <v>105253.0115643</v>
       </c>
-      <c r="F8" s="220">
+      <c r="F8" s="219">
         <f t="shared" si="6"/>
         <v>105253.0115643</v>
       </c>
@@ -2665,19 +2691,23 @@
         <v>53833.984264300001</v>
       </c>
       <c r="J8" s="56">
+        <f>Edesur!N15</f>
+        <v>25501.515173639022</v>
+      </c>
+      <c r="K8" s="56">
         <f t="shared" si="3"/>
         <v>20360</v>
       </c>
-      <c r="K8" s="56">
+      <c r="L8" s="56">
         <f t="shared" si="4"/>
         <v>31059.027300000002</v>
       </c>
-      <c r="L8" s="57">
+      <c r="M8" s="57">
         <f t="shared" si="5"/>
-        <v>105253.0115643</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>130754.52673793903</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
         <v>42</v>
       </c>
@@ -2691,7 +2721,7 @@
       <c r="E9" s="129">
         <v>105666.57938970001</v>
       </c>
-      <c r="F9" s="220">
+      <c r="F9" s="219">
         <f t="shared" si="6"/>
         <v>105666.57938970001</v>
       </c>
@@ -2708,62 +2738,70 @@
         <v>54045.512689700008</v>
       </c>
       <c r="J9" s="56">
+        <f>Edesur!N16</f>
+        <v>26537.910848781001</v>
+      </c>
+      <c r="K9" s="56">
         <f t="shared" si="3"/>
         <v>20440.000000000004</v>
       </c>
-      <c r="K9" s="56">
+      <c r="L9" s="56">
         <f t="shared" si="4"/>
         <v>31181.066700000003</v>
       </c>
-      <c r="L9" s="57">
+      <c r="M9" s="57">
         <f t="shared" si="5"/>
-        <v>105666.57938970001</v>
-      </c>
-      <c r="O9" s="175"/>
-    </row>
-    <row r="10" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="178" t="s">
+        <v>132204.49023848103</v>
+      </c>
+      <c r="P9" s="175"/>
+    </row>
+    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="177" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="179" t="s">
+      <c r="B10" s="178" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="180" t="s">
+      <c r="C10" s="179" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="181">
+      <c r="D10" s="180">
         <v>5.09</v>
       </c>
-      <c r="E10" s="182">
+      <c r="E10" s="181">
         <v>105253.0115643</v>
       </c>
-      <c r="F10" s="221">
+      <c r="F10" s="220">
         <f t="shared" si="6"/>
         <v>105253.0115643</v>
       </c>
-      <c r="G10" s="183">
+      <c r="G10" s="182">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="183"/>
-      <c r="I10" s="183">
+      <c r="H10" s="182"/>
+      <c r="I10" s="182">
         <f t="shared" si="2"/>
         <v>53833.984264300001</v>
       </c>
-      <c r="J10" s="183">
+      <c r="J10" s="182">
+        <f>Edesur!N17</f>
+        <v>20193.170973638986</v>
+      </c>
+      <c r="K10" s="182">
         <f t="shared" si="3"/>
         <v>20360</v>
       </c>
-      <c r="K10" s="183">
+      <c r="L10" s="182">
         <f t="shared" si="4"/>
         <v>31059.027300000002</v>
       </c>
-      <c r="L10" s="184">
+      <c r="M10" s="183">
         <f t="shared" si="5"/>
-        <v>105253.0115643</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>125446.18253793899</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="58" t="s">
         <v>95</v>
       </c>
@@ -2777,7 +2815,7 @@
       <c r="E11" s="129">
         <v>104219.09200080001</v>
       </c>
-      <c r="F11" s="220">
+      <c r="F11" s="219">
         <f t="shared" si="6"/>
         <v>104219.09200080001</v>
       </c>
@@ -2794,19 +2832,23 @@
         <v>53305.163200800009</v>
       </c>
       <c r="J11" s="56">
+        <f>Edesur!N18</f>
+        <v>25635.038335784</v>
+      </c>
+      <c r="K11" s="56">
         <f t="shared" si="3"/>
         <v>20160</v>
       </c>
-      <c r="K11" s="56">
+      <c r="L11" s="56">
         <f t="shared" si="4"/>
         <v>30753.928799999998</v>
       </c>
-      <c r="L11" s="57">
+      <c r="M11" s="57">
         <f t="shared" si="5"/>
-        <v>104219.09200080001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+        <v>129854.13033658401</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="58" t="s">
         <v>47</v>
       </c>
@@ -2820,7 +2862,7 @@
       <c r="E12" s="129">
         <v>107734.41851670001</v>
       </c>
-      <c r="F12" s="220">
+      <c r="F12" s="219">
         <f t="shared" ref="F12" si="7">E12</f>
         <v>107734.41851670001</v>
       </c>
@@ -2837,19 +2879,23 @@
         <v>55103.154816700007</v>
       </c>
       <c r="J12" s="56">
+        <f>Edesur!N19</f>
+        <v>39279.12142449095</v>
+      </c>
+      <c r="K12" s="56">
         <f t="shared" si="3"/>
         <v>20840</v>
       </c>
-      <c r="K12" s="56">
+      <c r="L12" s="56">
         <f t="shared" si="4"/>
         <v>31791.2637</v>
       </c>
-      <c r="L12" s="57">
+      <c r="M12" s="57">
         <f t="shared" si="5"/>
-        <v>107734.41851670001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+        <v>147013.53994119097</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="58" t="s">
         <v>49</v>
       </c>
@@ -2865,7 +2911,7 @@
       <c r="E13" s="129">
         <v>105666.57938970001</v>
       </c>
-      <c r="F13" s="220">
+      <c r="F13" s="219">
         <f>E13</f>
         <v>105666.57938970001</v>
       </c>
@@ -2882,24 +2928,28 @@
         <v>54045.512689700008</v>
       </c>
       <c r="J13" s="56">
+        <f>Edesur!N20</f>
+        <v>71949.576248780984</v>
+      </c>
+      <c r="K13" s="56">
         <f t="shared" si="3"/>
         <v>20440.000000000004</v>
       </c>
-      <c r="K13" s="56">
+      <c r="L13" s="56">
         <f t="shared" si="4"/>
         <v>31181.066700000003</v>
       </c>
-      <c r="L13" s="57">
+      <c r="M13" s="57">
         <f t="shared" si="5"/>
-        <v>105666.57938970001</v>
-      </c>
-      <c r="M13" s="44"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+        <v>177616.155638481</v>
+      </c>
+      <c r="N13" s="44"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="200" t="s">
+      <c r="B14" s="199" t="s">
         <v>106</v>
       </c>
       <c r="C14" s="63" t="s">
@@ -2911,7 +2961,7 @@
       <c r="E14" s="129">
         <v>371509.96055870003</v>
       </c>
-      <c r="F14" s="220">
+      <c r="F14" s="219">
         <f>580000-F25-84879</f>
         <v>416293.74475960003</v>
       </c>
@@ -2927,20 +2977,24 @@
         <f t="shared" si="2"/>
         <v>53833.984264300001</v>
       </c>
-      <c r="J14" s="64">
+      <c r="J14" s="56">
+        <f>Edesur!N21</f>
+        <v>26064.23717363898</v>
+      </c>
+      <c r="K14" s="64">
         <f t="shared" si="3"/>
         <v>20360</v>
       </c>
-      <c r="K14" s="56">
+      <c r="L14" s="56">
         <f t="shared" si="4"/>
         <v>31059.027300000002</v>
       </c>
-      <c r="L14" s="177">
+      <c r="M14" s="57">
         <f t="shared" si="5"/>
-        <v>60469.227363400001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+        <v>86533.464537038977</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="58" t="s">
         <v>53</v>
       </c>
@@ -2956,7 +3010,7 @@
       <c r="E15" s="129">
         <v>104219.09188079997</v>
       </c>
-      <c r="F15" s="220">
+      <c r="F15" s="219">
         <f>104219-F29+22333.1-0.35</f>
         <v>104219.0874284</v>
       </c>
@@ -2973,19 +3027,23 @@
         <v>53305.163200800009</v>
       </c>
       <c r="J15" s="56">
+        <f>Edesur!N22</f>
+        <v>22952.730135784008</v>
+      </c>
+      <c r="K15" s="56">
         <f t="shared" si="3"/>
         <v>20160</v>
       </c>
-      <c r="K15" s="56">
+      <c r="L15" s="56">
         <f t="shared" si="4"/>
         <v>30753.928799999998</v>
       </c>
-      <c r="L15" s="57">
+      <c r="M15" s="57">
         <f t="shared" si="5"/>
-        <v>104219.09663129598</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>127171.82676707998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="58" t="s">
         <v>56</v>
       </c>
@@ -3001,7 +3059,7 @@
       <c r="E16" s="129">
         <v>107734.41851670001</v>
       </c>
-      <c r="F16" s="220">
+      <c r="F16" s="219">
         <f t="shared" ref="F16:F21" si="8">E16</f>
         <v>107734.41851670001</v>
       </c>
@@ -3018,20 +3076,24 @@
         <v>55103.154816700007</v>
       </c>
       <c r="J16" s="56">
+        <f>Edesur!N23</f>
+        <v>28971.93012449098</v>
+      </c>
+      <c r="K16" s="56">
         <f t="shared" si="3"/>
         <v>20840</v>
       </c>
-      <c r="K16" s="56">
+      <c r="L16" s="56">
         <f t="shared" si="4"/>
         <v>31791.2637</v>
       </c>
-      <c r="L16" s="57">
+      <c r="M16" s="57">
         <f t="shared" si="5"/>
-        <v>107734.41851670001</v>
-      </c>
-      <c r="M16" s="44"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+        <v>136706.348641191</v>
+      </c>
+      <c r="N16" s="44"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="58" t="s">
         <v>59</v>
       </c>
@@ -3045,7 +3107,7 @@
       <c r="E17" s="129">
         <v>104219.09200080001</v>
       </c>
-      <c r="F17" s="220">
+      <c r="F17" s="219">
         <f t="shared" si="8"/>
         <v>104219.09200080001</v>
       </c>
@@ -3062,23 +3124,27 @@
         <v>53305.163200800009</v>
       </c>
       <c r="J17" s="56">
+        <f>Edesur!N24</f>
+        <v>20176.634935784015</v>
+      </c>
+      <c r="K17" s="56">
         <f t="shared" si="3"/>
         <v>20160</v>
       </c>
-      <c r="K17" s="56">
+      <c r="L17" s="56">
         <f t="shared" si="4"/>
         <v>30753.928799999998</v>
       </c>
-      <c r="L17" s="57">
+      <c r="M17" s="57">
         <f t="shared" si="5"/>
-        <v>104219.09200080001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="207" t="s">
+        <v>124395.72693658402</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="206" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="208"/>
+      <c r="B18" s="207"/>
       <c r="C18" s="63" t="s">
         <v>62</v>
       </c>
@@ -3088,7 +3154,7 @@
       <c r="E18" s="129">
         <v>107734.41851670001</v>
       </c>
-      <c r="F18" s="220">
+      <c r="F18" s="219">
         <f t="shared" si="8"/>
         <v>107734.41851670001</v>
       </c>
@@ -3104,28 +3170,32 @@
         <f t="shared" si="2"/>
         <v>55103.154816700007</v>
       </c>
-      <c r="J18" s="64">
+      <c r="J18" s="56">
+        <f>Edesur!N25</f>
+        <v>25848.82302449103</v>
+      </c>
+      <c r="K18" s="64">
         <f t="shared" si="3"/>
         <v>20840</v>
       </c>
-      <c r="K18" s="64">
+      <c r="L18" s="64">
         <f t="shared" si="4"/>
         <v>31791.2637</v>
       </c>
-      <c r="L18" s="177">
+      <c r="M18" s="57">
         <f t="shared" si="5"/>
-        <v>107734.41851670001</v>
-      </c>
-      <c r="M18" s="211"/>
+        <v>133583.24154119103</v>
+      </c>
       <c r="N18" s="210"/>
       <c r="O18" s="209"/>
-      <c r="P18" s="206"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P18" s="208"/>
+      <c r="Q18" s="205"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="200"/>
+      <c r="B19" s="199"/>
       <c r="C19" s="63" t="s">
         <v>64</v>
       </c>
@@ -3135,7 +3205,7 @@
       <c r="E19" s="129">
         <v>153020.095398</v>
       </c>
-      <c r="F19" s="220">
+      <c r="F19" s="219">
         <f t="shared" si="8"/>
         <v>153020.095398</v>
       </c>
@@ -3151,60 +3221,68 @@
         <f t="shared" si="2"/>
         <v>78265.517398000011</v>
       </c>
-      <c r="J19" s="64">
+      <c r="J19" s="56">
+        <f>Edesur!N26</f>
+        <v>41293.909002540058</v>
+      </c>
+      <c r="K19" s="64">
         <f t="shared" si="3"/>
         <v>29600</v>
       </c>
-      <c r="K19" s="64">
+      <c r="L19" s="64">
         <f t="shared" si="4"/>
         <v>45154.578000000001</v>
       </c>
-      <c r="L19" s="177">
+      <c r="M19" s="57">
         <f t="shared" si="5"/>
-        <v>153020.095398</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="24" x14ac:dyDescent="0.25">
-      <c r="A20" s="185"/>
-      <c r="B20" s="179" t="s">
+        <v>194314.00440054006</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="24" x14ac:dyDescent="0.3">
+      <c r="A20" s="184"/>
+      <c r="B20" s="178" t="s">
         <v>99</v>
       </c>
-      <c r="C20" s="180" t="s">
+      <c r="C20" s="179" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="181">
+      <c r="D20" s="180">
         <v>1.08</v>
       </c>
-      <c r="E20" s="182">
+      <c r="E20" s="181">
         <v>22332.662571600002</v>
       </c>
-      <c r="F20" s="221">
+      <c r="F20" s="220">
         <f t="shared" si="8"/>
         <v>22332.662571600002</v>
       </c>
-      <c r="G20" s="183">
+      <c r="G20" s="182">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H20" s="183"/>
-      <c r="I20" s="183">
+      <c r="H20" s="182"/>
+      <c r="I20" s="182">
         <f t="shared" si="2"/>
         <v>11422.534971600002</v>
       </c>
-      <c r="J20" s="183">
+      <c r="J20" s="182">
+        <f>Edesur!N27</f>
+        <v>3801.0370576680034</v>
+      </c>
+      <c r="K20" s="182">
         <f t="shared" si="3"/>
         <v>4320</v>
       </c>
-      <c r="K20" s="183">
+      <c r="L20" s="182">
         <f t="shared" si="4"/>
         <v>6590.1275999999998</v>
       </c>
-      <c r="L20" s="184">
+      <c r="M20" s="183">
         <f t="shared" si="5"/>
-        <v>22332.662571600002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+        <v>26133.699629268005</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="62"/>
       <c r="B21" s="59" t="s">
         <v>57</v>
@@ -3218,7 +3296,7 @@
       <c r="E21" s="129">
         <v>22332.662571600002</v>
       </c>
-      <c r="F21" s="220">
+      <c r="F21" s="219">
         <f t="shared" si="8"/>
         <v>22332.662571600002</v>
       </c>
@@ -3235,19 +3313,23 @@
         <v>11422.534971600002</v>
       </c>
       <c r="J21" s="56">
+        <f>Edesur!N28</f>
+        <v>3801.0370576680034</v>
+      </c>
+      <c r="K21" s="56">
         <f t="shared" si="3"/>
         <v>4320</v>
       </c>
-      <c r="K21" s="56">
+      <c r="L21" s="56">
         <f t="shared" si="4"/>
         <v>6590.1275999999998</v>
       </c>
-      <c r="L21" s="57">
+      <c r="M21" s="57">
         <f t="shared" si="5"/>
-        <v>22332.662571600002</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+        <v>26133.699629268005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="139"/>
       <c r="B22" s="140"/>
       <c r="C22" s="141" t="s">
@@ -3259,7 +3341,7 @@
       <c r="E22" s="143">
         <v>262598.51501640002</v>
       </c>
-      <c r="F22" s="222">
+      <c r="F22" s="221">
         <v>0</v>
       </c>
       <c r="G22" s="144">
@@ -3275,19 +3357,23 @@
         <v>11422.534971600002</v>
       </c>
       <c r="J22" s="144">
+        <f>Edesur!N29</f>
+        <v>3801.0370576680034</v>
+      </c>
+      <c r="K22" s="144">
         <f t="shared" si="3"/>
         <v>4320</v>
       </c>
-      <c r="K22" s="144">
+      <c r="L22" s="144">
         <f t="shared" si="4"/>
         <v>6590.1275999999998</v>
       </c>
-      <c r="L22" s="145">
+      <c r="M22" s="145">
         <f t="shared" si="5"/>
-        <v>295435.11818865599</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+        <v>299236.15524632402</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
         <v>35</v>
       </c>
@@ -3301,7 +3387,7 @@
       <c r="E23" s="129">
         <v>54462.538760400006</v>
       </c>
-      <c r="F23" s="220">
+      <c r="F23" s="219">
         <f>E23</f>
         <v>54462.538760400006</v>
       </c>
@@ -3318,19 +3404,23 @@
         <v>11422.534971600002</v>
       </c>
       <c r="J23" s="56">
+        <f>Edesur!N30</f>
+        <v>3801.0370576680034</v>
+      </c>
+      <c r="K23" s="56">
         <f t="shared" si="3"/>
         <v>4320</v>
       </c>
-      <c r="K23" s="56">
+      <c r="L23" s="56">
         <f t="shared" si="4"/>
         <v>6590.1275999999998</v>
       </c>
-      <c r="L23" s="57">
+      <c r="M23" s="57">
         <f t="shared" si="5"/>
-        <v>22332.662571600002</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+        <v>26133.699629268005</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="58" t="s">
         <v>49</v>
       </c>
@@ -3346,7 +3436,7 @@
       <c r="E24" s="129">
         <v>22332.662571600002</v>
       </c>
-      <c r="F24" s="220">
+      <c r="F24" s="219">
         <f t="shared" ref="F24" si="9">E24</f>
         <v>22332.662571600002</v>
       </c>
@@ -3363,23 +3453,27 @@
         <v>11422.534971600002</v>
       </c>
       <c r="J24" s="56">
+        <f>Edesur!N31</f>
+        <v>3801.0370576680034</v>
+      </c>
+      <c r="K24" s="56">
         <f t="shared" si="3"/>
         <v>4320</v>
       </c>
-      <c r="K24" s="56">
+      <c r="L24" s="56">
         <f t="shared" si="4"/>
         <v>6590.1275999999998</v>
       </c>
-      <c r="L24" s="57">
+      <c r="M24" s="57">
         <f t="shared" si="5"/>
-        <v>22332.662571600002</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+        <v>26133.699629268005</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="200" t="s">
+      <c r="B25" s="199" t="s">
         <v>106</v>
       </c>
       <c r="C25" s="60" t="s">
@@ -3391,7 +3485,7 @@
       <c r="E25" s="129">
         <v>78827.255240400002</v>
       </c>
-      <c r="F25" s="220">
+      <c r="F25" s="219">
         <f>E25</f>
         <v>78827.255240400002</v>
       </c>
@@ -3408,19 +3502,23 @@
         <v>11422.534971600002</v>
       </c>
       <c r="J25" s="56">
+        <f>Edesur!N32</f>
+        <v>3801.0370576680034</v>
+      </c>
+      <c r="K25" s="56">
         <f t="shared" si="3"/>
         <v>4320</v>
       </c>
-      <c r="K25" s="56">
+      <c r="L25" s="56">
         <f t="shared" si="4"/>
         <v>6590.1275999999998</v>
       </c>
-      <c r="L25" s="57">
+      <c r="M25" s="57">
         <f t="shared" si="5"/>
-        <v>22332.662571600002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+        <v>26133.699629268005</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="58" t="s">
         <v>63</v>
       </c>
@@ -3434,7 +3532,7 @@
       <c r="E26" s="129">
         <v>22332.662571600002</v>
       </c>
-      <c r="F26" s="220">
+      <c r="F26" s="219">
         <f t="shared" ref="F26:F28" si="10">E26</f>
         <v>22332.662571600002</v>
       </c>
@@ -3451,19 +3549,23 @@
         <v>11422.534971600002</v>
       </c>
       <c r="J26" s="56">
+        <f>Edesur!N33</f>
+        <v>3801.0370576680034</v>
+      </c>
+      <c r="K26" s="56">
         <f t="shared" si="3"/>
         <v>4320</v>
       </c>
-      <c r="K26" s="56">
+      <c r="L26" s="56">
         <f t="shared" si="4"/>
         <v>6590.1275999999998</v>
       </c>
-      <c r="L26" s="57">
+      <c r="M26" s="57">
         <f t="shared" si="5"/>
-        <v>22332.662571600002</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+        <v>26133.699629268005</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="58" t="s">
         <v>63</v>
       </c>
@@ -3477,7 +3579,7 @@
       <c r="E27" s="129">
         <v>22332.662571600002</v>
       </c>
-      <c r="F27" s="220">
+      <c r="F27" s="219">
         <f t="shared" si="10"/>
         <v>22332.662571600002</v>
       </c>
@@ -3494,23 +3596,27 @@
         <v>11422.534971600002</v>
       </c>
       <c r="J27" s="56">
+        <f>Edesur!N34</f>
+        <v>3801.0370576680034</v>
+      </c>
+      <c r="K27" s="56">
         <f t="shared" si="3"/>
         <v>4320</v>
       </c>
-      <c r="K27" s="56">
+      <c r="L27" s="56">
         <f t="shared" si="4"/>
         <v>6590.1275999999998</v>
       </c>
-      <c r="L27" s="57">
+      <c r="M27" s="57">
         <f t="shared" si="5"/>
-        <v>22332.662571600002</v>
-      </c>
-      <c r="O27" s="44">
+        <v>26133.699629268005</v>
+      </c>
+      <c r="P27" s="44">
         <f>F27+F26+F19</f>
         <v>197685.4205412</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="66"/>
       <c r="B28" s="65" t="str">
         <f>B7</f>
@@ -3525,7 +3631,7 @@
       <c r="E28" s="129">
         <v>22332.662571600002</v>
       </c>
-      <c r="F28" s="220">
+      <c r="F28" s="219">
         <f t="shared" si="10"/>
         <v>22332.662571600002</v>
       </c>
@@ -3542,19 +3648,23 @@
         <v>11422.534971600002</v>
       </c>
       <c r="J28" s="56">
+        <f>Edesur!N35</f>
+        <v>3801.0370576680034</v>
+      </c>
+      <c r="K28" s="56">
         <f t="shared" si="3"/>
         <v>4320</v>
       </c>
-      <c r="K28" s="56">
+      <c r="L28" s="56">
         <f t="shared" si="4"/>
         <v>6590.1275999999998</v>
       </c>
-      <c r="L28" s="57">
+      <c r="M28" s="57">
         <f t="shared" si="5"/>
-        <v>22332.662571600002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+        <v>26133.699629268005</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="66" t="s">
         <v>53</v>
       </c>
@@ -3570,7 +3680,7 @@
       <c r="E29" s="129">
         <v>22332.662571600002</v>
       </c>
-      <c r="F29" s="220">
+      <c r="F29" s="219">
         <f>E29</f>
         <v>22332.662571600002</v>
       </c>
@@ -3587,19 +3697,23 @@
         <v>11422.534971600002</v>
       </c>
       <c r="J29" s="56">
+        <f>Edesur!N36</f>
+        <v>3801.0370576680034</v>
+      </c>
+      <c r="K29" s="56">
         <f t="shared" si="3"/>
         <v>4320</v>
       </c>
-      <c r="K29" s="56">
+      <c r="L29" s="56">
         <f t="shared" si="4"/>
         <v>6590.1275999999998</v>
       </c>
-      <c r="L29" s="57">
+      <c r="M29" s="57">
         <f t="shared" si="5"/>
-        <v>22332.662571600002</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+        <v>26133.699629268005</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="67"/>
       <c r="B30" s="67"/>
       <c r="C30" s="68"/>
@@ -3612,8 +3726,9 @@
       <c r="J30" s="71"/>
       <c r="K30" s="71"/>
       <c r="L30" s="71"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M30" s="71"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="72"/>
       <c r="B31" s="73"/>
       <c r="C31" s="74" t="s">
@@ -3634,87 +3749,92 @@
         <f>SUM(I3:I30)</f>
         <v>1057642.1270000003</v>
       </c>
-      <c r="J31" s="136">
-        <f>SUM(J3:J30)</f>
+      <c r="J31" s="136"/>
+      <c r="K31" s="136">
+        <f>SUM(K3:K30)</f>
         <v>400000</v>
       </c>
-      <c r="K31" s="135"/>
-      <c r="L31" s="135">
-        <f>SUM(L3:L29)</f>
-        <v>2439302.7931784848</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J32" s="22"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="234" t="s">
+      <c r="L31" s="135"/>
+      <c r="M31" s="135">
+        <f>SUM(M3:M29)</f>
+        <v>2991173.6031784853</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="K32" s="22"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" s="233" t="s">
         <v>111</v>
       </c>
-      <c r="B33" s="234"/>
-      <c r="C33" s="234"/>
-      <c r="D33" s="234"/>
-      <c r="E33" s="234"/>
-      <c r="F33" s="234"/>
-      <c r="G33" s="234"/>
-      <c r="H33" s="234"/>
-      <c r="I33" s="234"/>
-      <c r="J33" s="234"/>
-      <c r="K33" s="234"/>
-      <c r="L33" s="234"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="234"/>
-      <c r="B34" s="234"/>
-      <c r="C34" s="234"/>
-      <c r="D34" s="234"/>
-      <c r="E34" s="234"/>
-      <c r="F34" s="234"/>
-      <c r="G34" s="234"/>
-      <c r="H34" s="234"/>
-      <c r="I34" s="234"/>
-      <c r="J34" s="234"/>
-      <c r="K34" s="234"/>
-      <c r="L34" s="234"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="234"/>
-      <c r="B35" s="234"/>
-      <c r="C35" s="234"/>
-      <c r="D35" s="234"/>
-      <c r="E35" s="234"/>
-      <c r="F35" s="234"/>
-      <c r="G35" s="234"/>
-      <c r="H35" s="234"/>
-      <c r="I35" s="234"/>
-      <c r="J35" s="234"/>
-      <c r="K35" s="234"/>
-      <c r="L35" s="234"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="234"/>
-      <c r="B36" s="234"/>
-      <c r="C36" s="234"/>
-      <c r="D36" s="234"/>
-      <c r="E36" s="234"/>
-      <c r="F36" s="234"/>
-      <c r="G36" s="234"/>
-      <c r="H36" s="234"/>
-      <c r="I36" s="234"/>
-      <c r="J36" s="234"/>
-      <c r="K36" s="234"/>
-      <c r="L36" s="234"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B33" s="233"/>
+      <c r="C33" s="233"/>
+      <c r="D33" s="233"/>
+      <c r="E33" s="233"/>
+      <c r="F33" s="233"/>
+      <c r="G33" s="233"/>
+      <c r="H33" s="233"/>
+      <c r="I33" s="233"/>
+      <c r="J33" s="233"/>
+      <c r="K33" s="233"/>
+      <c r="L33" s="233"/>
+      <c r="M33" s="233"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" s="233"/>
+      <c r="B34" s="233"/>
+      <c r="C34" s="233"/>
+      <c r="D34" s="233"/>
+      <c r="E34" s="233"/>
+      <c r="F34" s="233"/>
+      <c r="G34" s="233"/>
+      <c r="H34" s="233"/>
+      <c r="I34" s="233"/>
+      <c r="J34" s="233"/>
+      <c r="K34" s="233"/>
+      <c r="L34" s="233"/>
+      <c r="M34" s="233"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" s="233"/>
+      <c r="B35" s="233"/>
+      <c r="C35" s="233"/>
+      <c r="D35" s="233"/>
+      <c r="E35" s="233"/>
+      <c r="F35" s="233"/>
+      <c r="G35" s="233"/>
+      <c r="H35" s="233"/>
+      <c r="I35" s="233"/>
+      <c r="J35" s="233"/>
+      <c r="K35" s="233"/>
+      <c r="L35" s="233"/>
+      <c r="M35" s="233"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" s="233"/>
+      <c r="B36" s="233"/>
+      <c r="C36" s="233"/>
+      <c r="D36" s="233"/>
+      <c r="E36" s="233"/>
+      <c r="F36" s="233"/>
+      <c r="G36" s="233"/>
+      <c r="H36" s="233"/>
+      <c r="I36" s="233"/>
+      <c r="J36" s="233"/>
+      <c r="K36" s="233"/>
+      <c r="L36" s="233"/>
+      <c r="M36" s="233"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E40" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A33:L36"/>
+    <mergeCell ref="A33:M36"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="L1:M1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -3725,45 +3845,45 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="237" t="s">
+    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="236" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="238"/>
-      <c r="C1" s="238"/>
-      <c r="D1" s="238"/>
-      <c r="E1" s="238"/>
-      <c r="F1" s="238"/>
-      <c r="G1" s="238"/>
-      <c r="H1" s="238"/>
-      <c r="I1" s="238"/>
-      <c r="J1" s="238"/>
-      <c r="K1" s="238"/>
-      <c r="L1" s="238"/>
-      <c r="M1" s="238"/>
-      <c r="N1" s="239"/>
+      <c r="B1" s="237"/>
+      <c r="C1" s="237"/>
+      <c r="D1" s="237"/>
+      <c r="E1" s="237"/>
+      <c r="F1" s="237"/>
+      <c r="G1" s="237"/>
+      <c r="H1" s="237"/>
+      <c r="I1" s="237"/>
+      <c r="J1" s="237"/>
+      <c r="K1" s="237"/>
+      <c r="L1" s="237"/>
+      <c r="M1" s="237"/>
+      <c r="N1" s="238"/>
       <c r="O1" s="76"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="77"/>
       <c r="B2" s="77"/>
       <c r="C2" s="161"/>
@@ -3781,7 +3901,7 @@
       <c r="O2" s="78"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="80"/>
       <c r="B3" s="80"/>
       <c r="C3" s="163"/>
@@ -3799,7 +3919,7 @@
       <c r="O3" s="78"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="80"/>
       <c r="B4" s="80"/>
       <c r="C4" s="163"/>
@@ -3819,7 +3939,7 @@
       <c r="O4" s="78"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="80"/>
       <c r="B5" s="80"/>
       <c r="C5" s="163"/>
@@ -3837,10 +3957,10 @@
       <c r="O5" s="78"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="80"/>
       <c r="B6" s="80"/>
-      <c r="C6" s="219" t="str">
+      <c r="C6" s="218" t="str">
         <f>'detalle y gastos'!C7</f>
         <v>Vto. 15/12</v>
       </c>
@@ -3858,12 +3978,12 @@
       <c r="O6" s="78"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="81"/>
       <c r="B7" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="205">
+      <c r="C7" s="204">
         <v>551870.81000000006</v>
       </c>
       <c r="D7" s="28"/>
@@ -3885,7 +4005,7 @@
       <c r="O7" s="78"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="81"/>
       <c r="B8" s="80" t="s">
         <v>77</v>
@@ -3901,16 +4021,16 @@
         <f>C8-J38</f>
         <v>-199922.9342899998</v>
       </c>
-      <c r="L8" s="241">
+      <c r="L8" s="240">
         <f>C7-J38</f>
         <v>351947.87571000028</v>
       </c>
-      <c r="M8" s="241"/>
+      <c r="M8" s="240"/>
       <c r="N8" s="84"/>
       <c r="O8" s="78"/>
       <c r="P8" s="11"/>
     </row>
-    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="87" t="s">
         <v>78</v>
       </c>
@@ -3955,7 +4075,7 @@
       </c>
       <c r="P9" s="11"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="98">
         <v>1</v>
       </c>
@@ -4006,12 +4126,12 @@
         <v>31008.737138781005</v>
       </c>
       <c r="O10" s="97">
-        <f>N10+'prorrateo '!L3</f>
-        <v>136675.31652848102</v>
+        <f>N10+'prorrateo '!M3</f>
+        <v>167684.05366726202</v>
       </c>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="99">
         <v>2</v>
       </c>
@@ -4062,12 +4182,12 @@
         <v>27414.769973639028</v>
       </c>
       <c r="O11" s="97">
-        <f>N11+'prorrateo '!L4</f>
-        <v>132667.78153793904</v>
+        <f>N11+'prorrateo '!M4</f>
+        <v>160082.55151157806</v>
       </c>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="98">
         <v>3</v>
       </c>
@@ -4118,15 +4238,15 @@
         <v>27942.198535784013</v>
       </c>
       <c r="O12" s="97">
-        <f>N12+'prorrateo '!L5</f>
-        <v>163262.48541104808</v>
+        <f>N12+'prorrateo '!M5</f>
+        <v>191204.68394683208</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="98">
         <v>4</v>
       </c>
@@ -4177,12 +4297,12 @@
         <v>25698.763824491016</v>
       </c>
       <c r="O13" s="97">
-        <f>N13+'prorrateo '!L6</f>
-        <v>245476.97759855902</v>
+        <f>N13+'prorrateo '!M6</f>
+        <v>271175.74142305006</v>
       </c>
       <c r="P13" s="11"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="98">
         <v>6</v>
       </c>
@@ -4233,12 +4353,12 @@
         <v>27391.372548781012</v>
       </c>
       <c r="O14" s="97">
-        <f>N14+'prorrateo '!L7</f>
-        <v>133057.95193848101</v>
+        <f>N14+'prorrateo '!M7</f>
+        <v>160449.32448726203</v>
       </c>
       <c r="P14" s="11"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="98">
         <v>7</v>
       </c>
@@ -4289,11 +4409,11 @@
         <v>25501.515173639022</v>
       </c>
       <c r="O15" s="97">
-        <f>N15+'prorrateo '!L8</f>
-        <v>130754.52673793903</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+        <f>N15+'prorrateo '!M8</f>
+        <v>156256.04191157804</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="98">
         <v>8</v>
       </c>
@@ -4344,66 +4464,66 @@
         <v>26537.910848781001</v>
       </c>
       <c r="O16" s="97">
-        <f>N16+'prorrateo '!L9</f>
-        <v>132204.49023848103</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+        <f>N16+'prorrateo '!M9</f>
+        <v>158742.40108726203</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="98">
         <v>9</v>
       </c>
       <c r="B17" s="89">
         <v>9</v>
       </c>
-      <c r="C17" s="186" t="s">
+      <c r="C17" s="185" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="187" t="s">
+      <c r="D17" s="186" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="188">
+      <c r="E17" s="187">
         <v>5.09</v>
       </c>
-      <c r="F17" s="190">
+      <c r="F17" s="189">
         <v>3375.8</v>
       </c>
-      <c r="G17" s="190">
+      <c r="G17" s="189">
         <v>3400.1</v>
       </c>
-      <c r="H17" s="191">
+      <c r="H17" s="190">
         <f t="shared" si="1"/>
         <v>24.299999999999727</v>
       </c>
-      <c r="I17" s="192">
+      <c r="I17" s="191">
         <f t="shared" si="0"/>
         <v>1.700999999999981</v>
       </c>
-      <c r="J17" s="193">
+      <c r="J17" s="192">
         <f t="shared" si="2"/>
         <v>2279.0240999999746</v>
       </c>
-      <c r="K17" s="194">
+      <c r="K17" s="193">
         <f>K8*E17%</f>
         <v>-10176.077355360991</v>
       </c>
-      <c r="L17" s="195">
+      <c r="L17" s="194">
         <f t="shared" si="3"/>
         <v>17914.146873639012</v>
       </c>
-      <c r="M17" s="196">
+      <c r="M17" s="195">
         <f t="shared" si="4"/>
         <v>24.299999999999727</v>
       </c>
-      <c r="N17" s="191">
+      <c r="N17" s="190">
         <f t="shared" si="5"/>
         <v>20193.170973638986</v>
       </c>
       <c r="O17" s="97">
-        <f>N17+'prorrateo '!L10</f>
-        <v>125446.18253793899</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+        <f>N17+'prorrateo '!M10</f>
+        <v>145639.35351157797</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="98">
         <v>10</v>
       </c>
@@ -4454,11 +4574,11 @@
         <v>25635.038335784</v>
       </c>
       <c r="O18" s="97">
-        <f>N18+'prorrateo '!L11</f>
-        <v>129854.13033658401</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <f>N18+'prorrateo '!M11</f>
+        <v>155489.16867236802</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="98">
         <v>11</v>
       </c>
@@ -4509,11 +4629,11 @@
         <v>39279.12142449095</v>
       </c>
       <c r="O19" s="97">
-        <f>N19+'prorrateo '!L12</f>
-        <v>147013.53994119097</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <f>N19+'prorrateo '!M12</f>
+        <v>186292.66136568191</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="98">
         <v>12</v>
       </c>
@@ -4564,41 +4684,41 @@
         <v>71949.576248780984</v>
       </c>
       <c r="O20" s="97">
-        <f>N20+'prorrateo '!L13</f>
-        <v>177616.155638481</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+        <f>N20+'prorrateo '!M13</f>
+        <v>249565.73188726197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="98">
         <v>13</v>
       </c>
       <c r="B21" s="89">
         <v>13</v>
       </c>
-      <c r="C21" s="212" t="s">
+      <c r="C21" s="211" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="213" t="s">
+      <c r="D21" s="212" t="s">
         <v>49</v>
       </c>
-      <c r="E21" s="214">
+      <c r="E21" s="213">
         <v>5.09</v>
       </c>
-      <c r="F21" s="215">
+      <c r="F21" s="214">
         <v>4112.1000000000004</v>
       </c>
-      <c r="G21" s="215">
+      <c r="G21" s="214">
         <v>4199</v>
       </c>
       <c r="H21" s="147">
         <f t="shared" si="1"/>
         <v>86.899999999999636</v>
       </c>
-      <c r="I21" s="216">
+      <c r="I21" s="215">
         <f t="shared" si="0"/>
         <v>6.0829999999999753</v>
       </c>
-      <c r="J21" s="217">
+      <c r="J21" s="216">
         <f t="shared" si="2"/>
         <v>8150.0902999999662</v>
       </c>
@@ -4619,11 +4739,11 @@
         <v>26064.23717363898</v>
       </c>
       <c r="O21" s="97">
-        <f>N21+'prorrateo '!L14</f>
-        <v>86533.464537038977</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+        <f>N21+'prorrateo '!M14</f>
+        <v>112597.70171067795</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="98">
         <v>14</v>
       </c>
@@ -4674,11 +4794,11 @@
         <v>22952.730135784008</v>
       </c>
       <c r="O22" s="97">
-        <f>N22+'prorrateo '!L15</f>
-        <v>127171.82676707998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+        <f>N22+'prorrateo '!M15</f>
+        <v>150124.55690286399</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="98">
         <v>15</v>
       </c>
@@ -4729,11 +4849,11 @@
         <v>28971.93012449098</v>
       </c>
       <c r="O23" s="97">
-        <f>N23+'prorrateo '!L16</f>
-        <v>136706.348641191</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+        <f>N23+'prorrateo '!M16</f>
+        <v>165678.27876568199</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="98">
         <v>16</v>
       </c>
@@ -4784,11 +4904,11 @@
         <v>20176.634935784015</v>
       </c>
       <c r="O24" s="97">
-        <f>N24+'prorrateo '!L17</f>
-        <v>124395.72693658402</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+        <f>N24+'prorrateo '!M17</f>
+        <v>144572.36187236803</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="98">
         <v>17</v>
       </c>
@@ -4839,11 +4959,11 @@
         <v>25848.82302449103</v>
       </c>
       <c r="O25" s="97">
-        <f>N25+'prorrateo '!L18</f>
-        <v>133583.24154119103</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+        <f>N25+'prorrateo '!M18</f>
+        <v>159432.06456568206</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="98">
         <v>18</v>
       </c>
@@ -4894,53 +5014,53 @@
         <v>41293.909002540058</v>
       </c>
       <c r="O26" s="97">
-        <f>N26+'prorrateo '!L19</f>
-        <v>194314.00440054006</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <f>N26+'prorrateo '!M19</f>
+        <v>235607.91340308011</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="98">
         <v>19</v>
       </c>
       <c r="B27" s="90">
         <v>19</v>
       </c>
-      <c r="C27" s="197" t="s">
+      <c r="C27" s="196" t="s">
         <v>65</v>
       </c>
-      <c r="D27" s="198"/>
-      <c r="E27" s="199">
+      <c r="D27" s="197"/>
+      <c r="E27" s="198">
         <v>1.08</v>
       </c>
-      <c r="F27" s="189"/>
-      <c r="G27" s="190"/>
-      <c r="H27" s="191">
+      <c r="F27" s="188"/>
+      <c r="G27" s="189"/>
+      <c r="H27" s="190">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="192">
+      <c r="I27" s="191">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="193"/>
-      <c r="K27" s="194"/>
-      <c r="L27" s="195">
+      <c r="J27" s="192"/>
+      <c r="K27" s="193"/>
+      <c r="L27" s="194">
         <f t="shared" si="3"/>
         <v>3801.0370576680034</v>
       </c>
-      <c r="M27" s="196">
-        <v>0</v>
-      </c>
-      <c r="N27" s="191">
+      <c r="M27" s="195">
+        <v>0</v>
+      </c>
+      <c r="N27" s="190">
         <f t="shared" ref="N27:N37" si="6">J27+L27</f>
         <v>3801.0370576680034</v>
       </c>
       <c r="O27" s="97">
-        <f>N27+'prorrateo '!L20</f>
-        <v>26133.699629268005</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+        <f>N27+'prorrateo '!M20</f>
+        <v>29934.736686936008</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="98">
         <v>20</v>
       </c>
@@ -4975,11 +5095,11 @@
         <v>3801.0370576680034</v>
       </c>
       <c r="O28" s="97">
-        <f>N28+'prorrateo '!L21</f>
-        <v>26133.699629268005</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+        <f>N28+'prorrateo '!M21</f>
+        <v>29934.736686936008</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="98"/>
       <c r="B29" s="90"/>
       <c r="C29" s="158" t="s">
@@ -5007,11 +5127,11 @@
         <v>3801.0370576680034</v>
       </c>
       <c r="O29" s="97">
-        <f>N29+'prorrateo '!L22</f>
-        <v>299236.15524632402</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+        <f>N29+'prorrateo '!M22</f>
+        <v>303037.19230399205</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="98"/>
       <c r="B30" s="90"/>
       <c r="C30" s="169" t="s">
@@ -5039,11 +5159,11 @@
         <v>3801.0370576680034</v>
       </c>
       <c r="O30" s="97">
-        <f>N30+'prorrateo '!L23</f>
-        <v>26133.699629268005</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+        <f>N30+'prorrateo '!M23</f>
+        <v>29934.736686936008</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="98"/>
       <c r="B31" s="90"/>
       <c r="C31" s="169" t="s">
@@ -5073,13 +5193,13 @@
         <v>3801.0370576680034</v>
       </c>
       <c r="O31" s="97">
-        <f>N31+'prorrateo '!L24</f>
-        <v>26133.699629268005</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+        <f>N31+'prorrateo '!M24</f>
+        <v>29934.736686936008</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="99"/>
-      <c r="B32" s="218"/>
+      <c r="B32" s="217"/>
       <c r="C32" s="158" t="s">
         <v>70</v>
       </c>
@@ -5107,11 +5227,11 @@
         <v>3801.0370576680034</v>
       </c>
       <c r="O32" s="97">
-        <f>N32+'prorrateo '!L25</f>
-        <v>26133.699629268005</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+        <f>N32+'prorrateo '!M25</f>
+        <v>29934.736686936008</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="98"/>
       <c r="B33" s="90"/>
       <c r="C33" s="130" t="s">
@@ -5141,11 +5261,11 @@
         <v>3801.0370576680034</v>
       </c>
       <c r="O33" s="97">
-        <f>N33+'prorrateo '!L26</f>
-        <v>26133.699629268005</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+        <f>N33+'prorrateo '!M26</f>
+        <v>29934.736686936008</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="98"/>
       <c r="B34" s="90"/>
       <c r="C34" s="130" t="s">
@@ -5175,11 +5295,11 @@
         <v>3801.0370576680034</v>
       </c>
       <c r="O34" s="97">
-        <f>N34+'prorrateo '!L27</f>
-        <v>26133.699629268005</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+        <f>N34+'prorrateo '!M27</f>
+        <v>29934.736686936008</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="98">
         <v>21</v>
       </c>
@@ -5214,11 +5334,11 @@
         <v>3801.0370576680034</v>
       </c>
       <c r="O35" s="97">
-        <f>N35+'prorrateo '!L28</f>
-        <v>26133.699629268005</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+        <f>N35+'prorrateo '!M28</f>
+        <v>29934.736686936008</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="98">
         <v>22</v>
       </c>
@@ -5255,11 +5375,11 @@
         <v>3801.0370576680034</v>
       </c>
       <c r="O36" s="97">
-        <f>N36+'prorrateo '!L29</f>
-        <v>26133.699629268005</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+        <f>N36+'prorrateo '!M29</f>
+        <v>29934.736686936008</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="98">
         <v>23</v>
       </c>
@@ -5289,7 +5409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="98">
         <v>24</v>
       </c>
@@ -5317,7 +5437,7 @@
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="78"/>
       <c r="C39" s="91"/>
       <c r="D39" s="92"/>
@@ -5342,41 +5462,41 @@
       <c r="N39" s="93"/>
       <c r="O39" s="79"/>
     </row>
-    <row r="40" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="95" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="240"/>
-      <c r="D40" s="238"/>
-      <c r="E40" s="238"/>
-      <c r="F40" s="238"/>
-      <c r="G40" s="238"/>
-      <c r="H40" s="238"/>
-      <c r="I40" s="238"/>
-      <c r="J40" s="238"/>
-      <c r="K40" s="238"/>
-      <c r="L40" s="238"/>
-      <c r="M40" s="238"/>
-      <c r="N40" s="238"/>
+      <c r="C40" s="239"/>
+      <c r="D40" s="237"/>
+      <c r="E40" s="237"/>
+      <c r="F40" s="237"/>
+      <c r="G40" s="237"/>
+      <c r="H40" s="237"/>
+      <c r="I40" s="237"/>
+      <c r="J40" s="237"/>
+      <c r="K40" s="237"/>
+      <c r="L40" s="237"/>
+      <c r="M40" s="237"/>
+      <c r="N40" s="237"/>
       <c r="O40" s="95"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="H41" s="79"/>
       <c r="J41" s="96"/>
       <c r="K41" s="96"/>
       <c r="L41" s="96"/>
       <c r="N41" s="97"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="L44" s="151"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="L45" s="96"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E46" s="152"/>
       <c r="F46" s="152"/>
       <c r="G46" s="152"/>

--- a/ROSALES/Noviembre/expensas rosales Noviembre.xlsx
+++ b/ROSALES/Noviembre/expensas rosales Noviembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\ROSALES\Noviembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC4D5A4-710B-4D06-9F65-F645C3AFACD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56C7D27-D4F4-429E-AB81-99173AF6C8A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="126">
   <si>
     <t>TOTAL</t>
   </si>
@@ -404,6 +404,9 @@
   </si>
   <si>
     <t>EDESUR</t>
+  </si>
+  <si>
+    <t>SIN EDESUR</t>
   </si>
 </sst>
 </file>
@@ -1027,7 +1030,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1351,7 +1354,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1833,16 +1835,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:F65"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -1850,22 +1852,22 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="15"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
@@ -1876,89 +1878,89 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="36"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
       <c r="B17" s="37"/>
       <c r="C17" s="33"/>
       <c r="D17" s="4"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
         <v>105</v>
       </c>
       <c r="B18" s="38"/>
-      <c r="C18" s="222">
+      <c r="C18" s="221">
         <v>76654</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="223">
+      <c r="C19" s="222">
         <v>316973.44</v>
       </c>
       <c r="D19" s="20"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
         <v>25</v>
       </c>
       <c r="B20" s="39"/>
-      <c r="C20" s="222">
+      <c r="C20" s="221">
         <v>80000</v>
       </c>
       <c r="D20" s="20"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
         <v>122</v>
       </c>
       <c r="B21" s="39"/>
-      <c r="C21" s="222">
+      <c r="C21" s="221">
         <v>15748</v>
       </c>
       <c r="D21" s="4"/>
@@ -1967,26 +1969,26 @@
         <v>115</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="222">
+      <c r="C22" s="221">
         <v>83400</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="40"/>
       <c r="B23" s="41"/>
-      <c r="C23" s="224">
+      <c r="C23" s="223">
         <f>SUM(C17:C22)</f>
         <v>572775.43999999994</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="35" t="s">
         <v>12</v>
       </c>
@@ -1995,40 +1997,40 @@
       <c r="D24" s="45"/>
       <c r="F24" s="12"/>
     </row>
-    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="28" t="s">
         <v>97</v>
       </c>
       <c r="B25" s="42"/>
-      <c r="C25" s="222">
+      <c r="C25" s="221">
         <f>349151.87+ (349151.87*10%)</f>
         <v>384067.05699999997</v>
       </c>
       <c r="D25" s="45"/>
       <c r="F25" s="12"/>
     </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
         <v>98</v>
       </c>
       <c r="B26" s="42"/>
-      <c r="C26" s="222">
+      <c r="C26" s="221">
         <v>5684</v>
       </c>
       <c r="D26" s="45"/>
       <c r="F26" s="12"/>
     </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="28" t="s">
         <v>112</v>
       </c>
       <c r="B27" s="42"/>
-      <c r="C27" s="222">
+      <c r="C27" s="221">
         <v>55000</v>
       </c>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
         <v>91</v>
       </c>
@@ -2038,7 +2040,7 @@
       <c r="E28" s="6"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="40"/>
       <c r="B29" s="41"/>
       <c r="C29" s="23">
@@ -2047,7 +2049,7 @@
       </c>
       <c r="F29" s="12"/>
     </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="30" t="s">
         <v>6</v>
       </c>
@@ -2058,48 +2060,48 @@
       </c>
       <c r="F30" s="12"/>
     </row>
-    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C31" s="24"/>
       <c r="F31" s="12"/>
     </row>
-    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="24"/>
       <c r="F32" s="12"/>
     </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="28" t="s">
         <v>121</v>
       </c>
       <c r="B33" s="28"/>
-      <c r="C33" s="222">
+      <c r="C33" s="221">
         <v>610000</v>
       </c>
       <c r="F33" s="12"/>
     </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
         <v>120</v>
       </c>
       <c r="B34" s="28"/>
-      <c r="C34" s="225">
+      <c r="C34" s="224">
         <v>1034026.5</v>
       </c>
       <c r="F34" s="12"/>
     </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="28"/>
       <c r="B35" s="28"/>
       <c r="C35" s="34"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C36" s="25"/>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="173" t="s">
         <v>110</v>
       </c>
@@ -2109,11 +2111,11 @@
       </c>
       <c r="F37" s="12"/>
     </row>
-    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C38" s="25"/>
       <c r="F38" s="12"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>15</v>
       </c>
@@ -2124,7 +2126,7 @@
       </c>
       <c r="E39" s="6"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="18" t="s">
         <v>7</v>
       </c>
@@ -2134,37 +2136,37 @@
         <v>2661552.997</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="230" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="229" t="s">
         <v>109</v>
       </c>
-      <c r="B43" s="231"/>
-      <c r="C43" s="231"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="231"/>
-      <c r="B44" s="231"/>
-      <c r="C44" s="231"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="231"/>
-      <c r="B45" s="231"/>
-      <c r="C45" s="231"/>
-    </row>
-    <row r="46" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="231"/>
-      <c r="B46" s="231"/>
-      <c r="C46" s="231"/>
+      <c r="B43" s="230"/>
+      <c r="C43" s="230"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="230"/>
+      <c r="B44" s="230"/>
+      <c r="C44" s="230"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="230"/>
+      <c r="B45" s="230"/>
+      <c r="C45" s="230"/>
+    </row>
+    <row r="46" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="230"/>
+      <c r="B46" s="230"/>
+      <c r="C46" s="230"/>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
     </row>
-    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="C47" s="154"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="201" t="s">
         <v>100</v>
       </c>
@@ -2175,7 +2177,7 @@
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="201" t="s">
         <v>119</v>
       </c>
@@ -2187,7 +2189,7 @@
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="201" t="s">
         <v>96</v>
       </c>
@@ -2197,7 +2199,7 @@
         <v>2610074.1626310009</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="201" t="s">
         <v>116</v>
       </c>
@@ -2206,7 +2208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="201" t="s">
         <v>123</v>
       </c>
@@ -2215,7 +2217,7 @@
         <v>107386.2</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="201" t="s">
         <v>8</v>
       </c>
@@ -2226,30 +2228,30 @@
       </c>
       <c r="D53" s="5"/>
     </row>
-    <row r="54" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="9"/>
       <c r="B54" s="8"/>
       <c r="C54" s="10"/>
     </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="226"/>
-      <c r="B55" s="226"/>
-      <c r="C55" s="226"/>
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="225"/>
+      <c r="B55" s="225"/>
+      <c r="C55" s="225"/>
       <c r="F55" s="44"/>
     </row>
-    <row r="56" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="227"/>
-      <c r="B56" s="227"/>
-      <c r="C56" s="227"/>
-    </row>
-    <row r="57" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="226"/>
+      <c r="B56" s="226"/>
+      <c r="C56" s="226"/>
+    </row>
+    <row r="57" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
         <v>20</v>
       </c>
       <c r="B57" s="27"/>
       <c r="C57" s="29"/>
     </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="28" t="s">
         <v>23</v>
       </c>
@@ -2259,17 +2261,17 @@
         <v>-1644026.5</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="28"/>
       <c r="B59" s="28"/>
       <c r="C59" s="31"/>
     </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="28"/>
       <c r="B60" s="28"/>
       <c r="C60" s="32"/>
     </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="155" t="s">
         <v>0</v>
       </c>
@@ -2279,24 +2281,24 @@
         <v>-1644026.5</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="228" t="s">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="227" t="s">
         <v>107</v>
       </c>
-      <c r="B62" s="229"/>
-      <c r="C62" s="229"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="229"/>
-      <c r="B63" s="229"/>
-      <c r="C63" s="229"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="229"/>
-      <c r="B64" s="229"/>
-      <c r="C64" s="229"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B62" s="228"/>
+      <c r="C62" s="228"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="228"/>
+      <c r="B63" s="228"/>
+      <c r="C63" s="228"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="228"/>
+      <c r="B64" s="228"/>
+      <c r="C64" s="228"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="8"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
@@ -2324,59 +2326,56 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" customWidth="1"/>
-    <col min="9" max="10" width="10.6640625" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="11"/>
+    <col min="1" max="1" width="19.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="10" width="10.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.42578125" style="11" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="232">
-        <f>D1-L1</f>
-        <v>1057642.1270000001</v>
-      </c>
-      <c r="C1" s="232"/>
+      <c r="B1" s="231">
+        <f>N1</f>
+        <v>1017526.497</v>
+      </c>
+      <c r="C1" s="231"/>
       <c r="D1" s="138">
         <v>1667839.1270000001</v>
       </c>
       <c r="E1" t="s">
         <v>102</v>
       </c>
-      <c r="G1" s="234">
-        <v>400000</v>
-      </c>
-      <c r="H1" s="234"/>
-      <c r="I1" s="235" t="s">
+      <c r="G1" s="233"/>
+      <c r="H1" s="233"/>
+      <c r="I1" s="234" t="s">
         <v>114</v>
       </c>
-      <c r="J1" s="235"/>
-      <c r="K1" s="235"/>
-      <c r="L1" s="232">
-        <f>N1</f>
-        <v>610197</v>
-      </c>
-      <c r="M1" s="232"/>
+      <c r="J1" s="234"/>
+      <c r="K1" s="234"/>
+      <c r="L1" s="231">
+        <v>1000000</v>
+      </c>
+      <c r="M1" s="231"/>
       <c r="N1">
-        <v>610197</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1017526.497</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
         <v>26</v>
       </c>
@@ -2416,8 +2415,11 @@
       <c r="M2" s="51" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O2" s="11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
         <v>31</v>
       </c>
@@ -2433,7 +2435,7 @@
       <c r="E3" s="129">
         <v>105505.57938970001</v>
       </c>
-      <c r="F3" s="219">
+      <c r="F3" s="218">
         <f>E3</f>
         <v>105505.57938970001</v>
       </c>
@@ -2447,7 +2449,7 @@
       </c>
       <c r="I3" s="56">
         <f>B$1*D3/100</f>
-        <v>54045.512689700008</v>
+        <v>51995.603996700003</v>
       </c>
       <c r="J3" s="56">
         <f>Edesur!N10</f>
@@ -2455,19 +2457,23 @@
       </c>
       <c r="K3" s="56">
         <f>G$1*D3/100</f>
-        <v>20440.000000000004</v>
+        <v>0</v>
       </c>
       <c r="L3" s="56">
         <f>L$1*D3/100</f>
-        <v>31181.066700000003</v>
+        <v>51100</v>
       </c>
       <c r="M3" s="57">
         <f>I3+G3+L3+K3+H3+J3</f>
-        <v>136675.31652848102</v>
+        <v>134104.34113548099</v>
       </c>
       <c r="N3" s="44"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O3" s="151">
+        <f>M3-J3</f>
+        <v>103095.6039967</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="58" t="s">
         <v>33</v>
       </c>
@@ -2483,7 +2489,7 @@
       <c r="E4" s="129">
         <v>104519.0115643</v>
       </c>
-      <c r="F4" s="219">
+      <c r="F4" s="218">
         <f>E4</f>
         <v>104519.0115643</v>
       </c>
@@ -2497,7 +2503,7 @@
       </c>
       <c r="I4" s="56">
         <f t="shared" ref="I4:I29" si="2">B$1*D4/100</f>
-        <v>53833.984264300001</v>
+        <v>51792.098697299996</v>
       </c>
       <c r="J4" s="56">
         <f>Edesur!N11</f>
@@ -2505,19 +2511,23 @@
       </c>
       <c r="K4" s="56">
         <f t="shared" ref="K4:K29" si="3">G$1*D4/100</f>
-        <v>20360</v>
+        <v>0</v>
       </c>
       <c r="L4" s="56">
         <f t="shared" ref="L4:L29" si="4">L$1*D4/100</f>
-        <v>31059.027300000002</v>
+        <v>50900</v>
       </c>
       <c r="M4" s="57">
         <f t="shared" ref="M4:M29" si="5">I4+G4+L4+K4+H4+J4</f>
-        <v>132667.78153793904</v>
+        <v>130106.86867093903</v>
       </c>
       <c r="N4" s="44"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O4" s="151">
+        <f t="shared" ref="O4:O29" si="6">M4-J4</f>
+        <v>102692.09869730001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>35</v>
       </c>
@@ -2531,7 +2541,7 @@
       <c r="E5" s="129">
         <v>407656.00631120004</v>
       </c>
-      <c r="F5" s="219">
+      <c r="F5" s="218">
         <f>497170.55-64957-F23</f>
         <v>377751.01123959996</v>
       </c>
@@ -2545,7 +2555,7 @@
       </c>
       <c r="I5" s="56">
         <f t="shared" si="2"/>
-        <v>53305.163200800009</v>
+        <v>51283.335448799997</v>
       </c>
       <c r="J5" s="56">
         <f>Edesur!N12</f>
@@ -2553,64 +2563,72 @@
       </c>
       <c r="K5" s="56">
         <f t="shared" si="3"/>
-        <v>20160</v>
+        <v>0</v>
       </c>
       <c r="L5" s="56">
         <f t="shared" si="4"/>
-        <v>30753.928799999998</v>
+        <v>50400</v>
       </c>
       <c r="M5" s="57">
         <f t="shared" si="5"/>
-        <v>163262.48541104808</v>
+        <v>160726.72885904807</v>
       </c>
       <c r="N5" s="44"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="58" t="s">
+      <c r="O5" s="151">
+        <f t="shared" si="6"/>
+        <v>132784.53032326407</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="139" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="60" t="s">
+      <c r="B6" s="140"/>
+      <c r="C6" s="141" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="61">
+      <c r="D6" s="142">
         <v>5.21</v>
       </c>
-      <c r="E6" s="129">
+      <c r="E6" s="143">
         <v>107734.41851670001</v>
       </c>
-      <c r="F6" s="219"/>
-      <c r="G6" s="56">
+      <c r="F6" s="220"/>
+      <c r="G6" s="144">
         <f t="shared" si="0"/>
         <v>107734.41851670001</v>
       </c>
-      <c r="H6" s="56">
+      <c r="H6" s="144">
         <f t="shared" si="1"/>
         <v>4309.3767406680008</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="144">
         <f t="shared" si="2"/>
-        <v>55103.154816700007</v>
-      </c>
-      <c r="J6" s="56">
+        <v>53013.130493700002</v>
+      </c>
+      <c r="J6" s="144">
         <f>Edesur!N13</f>
         <v>25698.763824491016</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="144">
         <f t="shared" si="3"/>
-        <v>20840</v>
-      </c>
-      <c r="L6" s="56">
+        <v>0</v>
+      </c>
+      <c r="L6" s="144">
         <f t="shared" si="4"/>
-        <v>31791.2637</v>
-      </c>
-      <c r="M6" s="57">
+        <v>52100</v>
+      </c>
+      <c r="M6" s="145">
         <f t="shared" si="5"/>
-        <v>245476.97759855902</v>
+        <v>242855.68957555902</v>
+      </c>
+      <c r="O6" s="151">
+        <f t="shared" si="6"/>
+        <v>217156.92575106802</v>
       </c>
       <c r="P6" s="175"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>35</v>
       </c>
@@ -2626,8 +2644,8 @@
       <c r="E7" s="129">
         <v>105666.57938970001</v>
       </c>
-      <c r="F7" s="219">
-        <f t="shared" ref="F7:F11" si="6">E7</f>
+      <c r="F7" s="218">
+        <f t="shared" ref="F7:F11" si="7">E7</f>
         <v>105666.57938970001</v>
       </c>
       <c r="G7" s="56">
@@ -2640,7 +2658,7 @@
       </c>
       <c r="I7" s="56">
         <f t="shared" si="2"/>
-        <v>54045.512689700008</v>
+        <v>51995.603996700003</v>
       </c>
       <c r="J7" s="56">
         <f>Edesur!N14</f>
@@ -2648,19 +2666,23 @@
       </c>
       <c r="K7" s="56">
         <f t="shared" si="3"/>
-        <v>20440.000000000004</v>
+        <v>0</v>
       </c>
       <c r="L7" s="56">
         <f t="shared" si="4"/>
-        <v>31181.066700000003</v>
+        <v>51100</v>
       </c>
       <c r="M7" s="57">
         <f t="shared" si="5"/>
-        <v>133057.95193848101</v>
+        <v>130486.97654548101</v>
+      </c>
+      <c r="O7" s="151">
+        <f t="shared" si="6"/>
+        <v>103095.6039967</v>
       </c>
       <c r="P7" s="175"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
         <v>40</v>
       </c>
@@ -2674,8 +2696,8 @@
       <c r="E8" s="129">
         <v>105253.0115643</v>
       </c>
-      <c r="F8" s="219">
-        <f t="shared" si="6"/>
+      <c r="F8" s="218">
+        <f t="shared" si="7"/>
         <v>105253.0115643</v>
       </c>
       <c r="G8" s="56">
@@ -2688,7 +2710,7 @@
       </c>
       <c r="I8" s="56">
         <f t="shared" si="2"/>
-        <v>53833.984264300001</v>
+        <v>51792.098697299996</v>
       </c>
       <c r="J8" s="56">
         <f>Edesur!N15</f>
@@ -2696,18 +2718,22 @@
       </c>
       <c r="K8" s="56">
         <f t="shared" si="3"/>
-        <v>20360</v>
+        <v>0</v>
       </c>
       <c r="L8" s="56">
         <f t="shared" si="4"/>
-        <v>31059.027300000002</v>
+        <v>50900</v>
       </c>
       <c r="M8" s="57">
         <f t="shared" si="5"/>
-        <v>130754.52673793903</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+        <v>128193.61387093902</v>
+      </c>
+      <c r="O8" s="151">
+        <f t="shared" si="6"/>
+        <v>102692.0986973</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>42</v>
       </c>
@@ -2721,8 +2747,8 @@
       <c r="E9" s="129">
         <v>105666.57938970001</v>
       </c>
-      <c r="F9" s="219">
-        <f t="shared" si="6"/>
+      <c r="F9" s="218">
+        <f t="shared" si="7"/>
         <v>105666.57938970001</v>
       </c>
       <c r="G9" s="56">
@@ -2735,7 +2761,7 @@
       </c>
       <c r="I9" s="56">
         <f t="shared" si="2"/>
-        <v>54045.512689700008</v>
+        <v>51995.603996700003</v>
       </c>
       <c r="J9" s="56">
         <f>Edesur!N16</f>
@@ -2743,19 +2769,23 @@
       </c>
       <c r="K9" s="56">
         <f t="shared" si="3"/>
-        <v>20440.000000000004</v>
+        <v>0</v>
       </c>
       <c r="L9" s="56">
         <f t="shared" si="4"/>
-        <v>31181.066700000003</v>
+        <v>51100</v>
       </c>
       <c r="M9" s="57">
         <f t="shared" si="5"/>
-        <v>132204.49023848103</v>
+        <v>129633.514845481</v>
+      </c>
+      <c r="O9" s="151">
+        <f t="shared" si="6"/>
+        <v>103095.6039967</v>
       </c>
       <c r="P9" s="175"/>
     </row>
-    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="177" t="s">
         <v>44</v>
       </c>
@@ -2771,8 +2801,8 @@
       <c r="E10" s="181">
         <v>105253.0115643</v>
       </c>
-      <c r="F10" s="220">
-        <f t="shared" si="6"/>
+      <c r="F10" s="219">
+        <f t="shared" si="7"/>
         <v>105253.0115643</v>
       </c>
       <c r="G10" s="182">
@@ -2782,7 +2812,7 @@
       <c r="H10" s="182"/>
       <c r="I10" s="182">
         <f t="shared" si="2"/>
-        <v>53833.984264300001</v>
+        <v>51792.098697299996</v>
       </c>
       <c r="J10" s="182">
         <f>Edesur!N17</f>
@@ -2790,18 +2820,22 @@
       </c>
       <c r="K10" s="182">
         <f t="shared" si="3"/>
-        <v>20360</v>
+        <v>0</v>
       </c>
       <c r="L10" s="182">
         <f t="shared" si="4"/>
-        <v>31059.027300000002</v>
+        <v>50900</v>
       </c>
       <c r="M10" s="183">
         <f t="shared" si="5"/>
-        <v>125446.18253793899</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+        <v>122885.26967093899</v>
+      </c>
+      <c r="O10" s="151">
+        <f t="shared" si="6"/>
+        <v>102692.0986973</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
         <v>95</v>
       </c>
@@ -2815,8 +2849,8 @@
       <c r="E11" s="129">
         <v>104219.09200080001</v>
       </c>
-      <c r="F11" s="219">
-        <f t="shared" si="6"/>
+      <c r="F11" s="218">
+        <f t="shared" si="7"/>
         <v>104219.09200080001</v>
       </c>
       <c r="G11" s="56">
@@ -2829,7 +2863,7 @@
       </c>
       <c r="I11" s="56">
         <f t="shared" si="2"/>
-        <v>53305.163200800009</v>
+        <v>51283.335448799997</v>
       </c>
       <c r="J11" s="56">
         <f>Edesur!N18</f>
@@ -2837,18 +2871,22 @@
       </c>
       <c r="K11" s="56">
         <f t="shared" si="3"/>
-        <v>20160</v>
+        <v>0</v>
       </c>
       <c r="L11" s="56">
         <f t="shared" si="4"/>
-        <v>30753.928799999998</v>
+        <v>50400</v>
       </c>
       <c r="M11" s="57">
         <f t="shared" si="5"/>
-        <v>129854.13033658401</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+        <v>127318.37378458401</v>
+      </c>
+      <c r="O11" s="151">
+        <f t="shared" si="6"/>
+        <v>101683.3354488</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="58" t="s">
         <v>47</v>
       </c>
@@ -2862,8 +2900,8 @@
       <c r="E12" s="129">
         <v>107734.41851670001</v>
       </c>
-      <c r="F12" s="219">
-        <f t="shared" ref="F12" si="7">E12</f>
+      <c r="F12" s="218">
+        <f t="shared" ref="F12" si="8">E12</f>
         <v>107734.41851670001</v>
       </c>
       <c r="G12" s="56">
@@ -2876,7 +2914,7 @@
       </c>
       <c r="I12" s="56">
         <f t="shared" si="2"/>
-        <v>55103.154816700007</v>
+        <v>53013.130493700002</v>
       </c>
       <c r="J12" s="56">
         <f>Edesur!N19</f>
@@ -2884,18 +2922,22 @@
       </c>
       <c r="K12" s="56">
         <f t="shared" si="3"/>
-        <v>20840</v>
+        <v>0</v>
       </c>
       <c r="L12" s="56">
         <f t="shared" si="4"/>
-        <v>31791.2637</v>
+        <v>52100</v>
       </c>
       <c r="M12" s="57">
         <f t="shared" si="5"/>
-        <v>147013.53994119097</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+        <v>144392.25191819097</v>
+      </c>
+      <c r="O12" s="151">
+        <f t="shared" si="6"/>
+        <v>105113.13049370002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>49</v>
       </c>
@@ -2911,7 +2953,7 @@
       <c r="E13" s="129">
         <v>105666.57938970001</v>
       </c>
-      <c r="F13" s="219">
+      <c r="F13" s="218">
         <f>E13</f>
         <v>105666.57938970001</v>
       </c>
@@ -2925,7 +2967,7 @@
       </c>
       <c r="I13" s="56">
         <f t="shared" si="2"/>
-        <v>54045.512689700008</v>
+        <v>51995.603996700003</v>
       </c>
       <c r="J13" s="56">
         <f>Edesur!N20</f>
@@ -2933,19 +2975,23 @@
       </c>
       <c r="K13" s="56">
         <f t="shared" si="3"/>
-        <v>20440.000000000004</v>
+        <v>0</v>
       </c>
       <c r="L13" s="56">
         <f t="shared" si="4"/>
-        <v>31181.066700000003</v>
+        <v>51100</v>
       </c>
       <c r="M13" s="57">
         <f t="shared" si="5"/>
-        <v>177616.155638481</v>
+        <v>175045.18024548097</v>
       </c>
       <c r="N13" s="44"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O13" s="151">
+        <f t="shared" si="6"/>
+        <v>103095.60399669998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="62" t="s">
         <v>49</v>
       </c>
@@ -2961,7 +3007,7 @@
       <c r="E14" s="129">
         <v>371509.96055870003</v>
       </c>
-      <c r="F14" s="219">
+      <c r="F14" s="218">
         <f>580000-F25-84879</f>
         <v>416293.74475960003</v>
       </c>
@@ -2975,7 +3021,7 @@
       </c>
       <c r="I14" s="64">
         <f t="shared" si="2"/>
-        <v>53833.984264300001</v>
+        <v>51792.098697299996</v>
       </c>
       <c r="J14" s="56">
         <f>Edesur!N21</f>
@@ -2983,18 +3029,22 @@
       </c>
       <c r="K14" s="64">
         <f t="shared" si="3"/>
-        <v>20360</v>
+        <v>0</v>
       </c>
       <c r="L14" s="56">
         <f t="shared" si="4"/>
-        <v>31059.027300000002</v>
+        <v>50900</v>
       </c>
       <c r="M14" s="57">
         <f t="shared" si="5"/>
-        <v>86533.464537038977</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+        <v>83972.551670038971</v>
+      </c>
+      <c r="O14" s="151">
+        <f t="shared" si="6"/>
+        <v>57908.314496399995</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>53</v>
       </c>
@@ -3010,7 +3060,7 @@
       <c r="E15" s="129">
         <v>104219.09188079997</v>
       </c>
-      <c r="F15" s="219">
+      <c r="F15" s="218">
         <f>104219-F29+22333.1-0.35</f>
         <v>104219.0874284</v>
       </c>
@@ -3024,7 +3074,7 @@
       </c>
       <c r="I15" s="56">
         <f t="shared" si="2"/>
-        <v>53305.163200800009</v>
+        <v>51283.335448799997</v>
       </c>
       <c r="J15" s="56">
         <f>Edesur!N22</f>
@@ -3032,18 +3082,22 @@
       </c>
       <c r="K15" s="56">
         <f t="shared" si="3"/>
-        <v>20160</v>
+        <v>0</v>
       </c>
       <c r="L15" s="56">
         <f t="shared" si="4"/>
-        <v>30753.928799999998</v>
+        <v>50400</v>
       </c>
       <c r="M15" s="57">
         <f t="shared" si="5"/>
-        <v>127171.82676707998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+        <v>124636.07021507998</v>
+      </c>
+      <c r="O15" s="151">
+        <f t="shared" si="6"/>
+        <v>101683.34007929597</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="58" t="s">
         <v>56</v>
       </c>
@@ -3059,8 +3113,8 @@
       <c r="E16" s="129">
         <v>107734.41851670001</v>
       </c>
-      <c r="F16" s="219">
-        <f t="shared" ref="F16:F21" si="8">E16</f>
+      <c r="F16" s="218">
+        <f t="shared" ref="F16:F21" si="9">E16</f>
         <v>107734.41851670001</v>
       </c>
       <c r="G16" s="56">
@@ -3073,7 +3127,7 @@
       </c>
       <c r="I16" s="56">
         <f t="shared" si="2"/>
-        <v>55103.154816700007</v>
+        <v>53013.130493700002</v>
       </c>
       <c r="J16" s="56">
         <f>Edesur!N23</f>
@@ -3081,19 +3135,23 @@
       </c>
       <c r="K16" s="56">
         <f t="shared" si="3"/>
-        <v>20840</v>
+        <v>0</v>
       </c>
       <c r="L16" s="56">
         <f t="shared" si="4"/>
-        <v>31791.2637</v>
+        <v>52100</v>
       </c>
       <c r="M16" s="57">
         <f t="shared" si="5"/>
-        <v>136706.348641191</v>
+        <v>134085.060618191</v>
       </c>
       <c r="N16" s="44"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O16" s="151">
+        <f t="shared" si="6"/>
+        <v>105113.13049370001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>59</v>
       </c>
@@ -3107,8 +3165,8 @@
       <c r="E17" s="129">
         <v>104219.09200080001</v>
       </c>
-      <c r="F17" s="219">
-        <f t="shared" si="8"/>
+      <c r="F17" s="218">
+        <f t="shared" si="9"/>
         <v>104219.09200080001</v>
       </c>
       <c r="G17" s="56">
@@ -3121,7 +3179,7 @@
       </c>
       <c r="I17" s="56">
         <f t="shared" si="2"/>
-        <v>53305.163200800009</v>
+        <v>51283.335448799997</v>
       </c>
       <c r="J17" s="56">
         <f>Edesur!N24</f>
@@ -3129,18 +3187,22 @@
       </c>
       <c r="K17" s="56">
         <f t="shared" si="3"/>
-        <v>20160</v>
+        <v>0</v>
       </c>
       <c r="L17" s="56">
         <f t="shared" si="4"/>
-        <v>30753.928799999998</v>
+        <v>50400</v>
       </c>
       <c r="M17" s="57">
         <f t="shared" si="5"/>
-        <v>124395.72693658402</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>121859.97038458401</v>
+      </c>
+      <c r="O17" s="151">
+        <f t="shared" si="6"/>
+        <v>101683.3354488</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="206" t="s">
         <v>61</v>
       </c>
@@ -3154,8 +3216,8 @@
       <c r="E18" s="129">
         <v>107734.41851670001</v>
       </c>
-      <c r="F18" s="219">
-        <f t="shared" si="8"/>
+      <c r="F18" s="218">
+        <f t="shared" si="9"/>
         <v>107734.41851670001</v>
       </c>
       <c r="G18" s="64">
@@ -3168,7 +3230,7 @@
       </c>
       <c r="I18" s="64">
         <f t="shared" si="2"/>
-        <v>55103.154816700007</v>
+        <v>53013.130493700002</v>
       </c>
       <c r="J18" s="56">
         <f>Edesur!N25</f>
@@ -3176,22 +3238,25 @@
       </c>
       <c r="K18" s="64">
         <f t="shared" si="3"/>
-        <v>20840</v>
+        <v>0</v>
       </c>
       <c r="L18" s="64">
         <f t="shared" si="4"/>
-        <v>31791.2637</v>
+        <v>52100</v>
       </c>
       <c r="M18" s="57">
         <f t="shared" si="5"/>
-        <v>133583.24154119103</v>
-      </c>
-      <c r="N18" s="210"/>
-      <c r="O18" s="209"/>
+        <v>130961.95351819103</v>
+      </c>
+      <c r="N18" s="209"/>
+      <c r="O18" s="151">
+        <f t="shared" si="6"/>
+        <v>105113.13049370001</v>
+      </c>
       <c r="P18" s="208"/>
       <c r="Q18" s="205"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="62" t="s">
         <v>63</v>
       </c>
@@ -3205,8 +3270,8 @@
       <c r="E19" s="129">
         <v>153020.095398</v>
       </c>
-      <c r="F19" s="219">
-        <f t="shared" si="8"/>
+      <c r="F19" s="218">
+        <f t="shared" si="9"/>
         <v>153020.095398</v>
       </c>
       <c r="G19" s="64">
@@ -3219,7 +3284,7 @@
       </c>
       <c r="I19" s="64">
         <f t="shared" si="2"/>
-        <v>78265.517398000011</v>
+        <v>75296.960778000008</v>
       </c>
       <c r="J19" s="56">
         <f>Edesur!N26</f>
@@ -3227,18 +3292,22 @@
       </c>
       <c r="K19" s="64">
         <f t="shared" si="3"/>
-        <v>29600</v>
+        <v>0</v>
       </c>
       <c r="L19" s="64">
         <f t="shared" si="4"/>
-        <v>45154.578000000001</v>
+        <v>74000</v>
       </c>
       <c r="M19" s="57">
         <f t="shared" si="5"/>
-        <v>194314.00440054006</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" ht="24" x14ac:dyDescent="0.3">
+        <v>190590.86978054006</v>
+      </c>
+      <c r="O19" s="151">
+        <f t="shared" si="6"/>
+        <v>149296.96077800001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="184"/>
       <c r="B20" s="178" t="s">
         <v>99</v>
@@ -3252,8 +3321,8 @@
       <c r="E20" s="181">
         <v>22332.662571600002</v>
       </c>
-      <c r="F20" s="220">
-        <f t="shared" si="8"/>
+      <c r="F20" s="219">
+        <f t="shared" si="9"/>
         <v>22332.662571600002</v>
       </c>
       <c r="G20" s="182">
@@ -3263,7 +3332,7 @@
       <c r="H20" s="182"/>
       <c r="I20" s="182">
         <f t="shared" si="2"/>
-        <v>11422.534971600002</v>
+        <v>10989.286167600001</v>
       </c>
       <c r="J20" s="182">
         <f>Edesur!N27</f>
@@ -3271,18 +3340,22 @@
       </c>
       <c r="K20" s="182">
         <f t="shared" si="3"/>
-        <v>4320</v>
+        <v>0</v>
       </c>
       <c r="L20" s="182">
         <f t="shared" si="4"/>
-        <v>6590.1275999999998</v>
+        <v>10800</v>
       </c>
       <c r="M20" s="183">
         <f t="shared" si="5"/>
-        <v>26133.699629268005</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+        <v>25590.323225268006</v>
+      </c>
+      <c r="O20" s="151">
+        <f t="shared" si="6"/>
+        <v>21789.286167600003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="62"/>
       <c r="B21" s="59" t="s">
         <v>57</v>
@@ -3296,8 +3369,8 @@
       <c r="E21" s="129">
         <v>22332.662571600002</v>
       </c>
-      <c r="F21" s="219">
-        <f t="shared" si="8"/>
+      <c r="F21" s="218">
+        <f t="shared" si="9"/>
         <v>22332.662571600002</v>
       </c>
       <c r="G21" s="56">
@@ -3310,7 +3383,7 @@
       </c>
       <c r="I21" s="56">
         <f t="shared" si="2"/>
-        <v>11422.534971600002</v>
+        <v>10989.286167600001</v>
       </c>
       <c r="J21" s="56">
         <f>Edesur!N28</f>
@@ -3318,18 +3391,22 @@
       </c>
       <c r="K21" s="56">
         <f t="shared" si="3"/>
-        <v>4320</v>
+        <v>0</v>
       </c>
       <c r="L21" s="56">
         <f t="shared" si="4"/>
-        <v>6590.1275999999998</v>
+        <v>10800</v>
       </c>
       <c r="M21" s="57">
         <f t="shared" si="5"/>
-        <v>26133.699629268005</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+        <v>25590.323225268006</v>
+      </c>
+      <c r="O21" s="151">
+        <f t="shared" si="6"/>
+        <v>21789.286167600003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="139"/>
       <c r="B22" s="140"/>
       <c r="C22" s="141" t="s">
@@ -3341,7 +3418,7 @@
       <c r="E22" s="143">
         <v>262598.51501640002</v>
       </c>
-      <c r="F22" s="221">
+      <c r="F22" s="220">
         <v>0</v>
       </c>
       <c r="G22" s="144">
@@ -3354,7 +3431,7 @@
       </c>
       <c r="I22" s="144">
         <f t="shared" si="2"/>
-        <v>11422.534971600002</v>
+        <v>10989.286167600001</v>
       </c>
       <c r="J22" s="144">
         <f>Edesur!N29</f>
@@ -3362,18 +3439,22 @@
       </c>
       <c r="K22" s="144">
         <f t="shared" si="3"/>
-        <v>4320</v>
+        <v>0</v>
       </c>
       <c r="L22" s="144">
         <f t="shared" si="4"/>
-        <v>6590.1275999999998</v>
+        <v>10800</v>
       </c>
       <c r="M22" s="145">
         <f t="shared" si="5"/>
-        <v>299236.15524632402</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+        <v>298692.77884232404</v>
+      </c>
+      <c r="O22" s="151">
+        <f t="shared" si="6"/>
+        <v>294891.74178465601</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>35</v>
       </c>
@@ -3387,7 +3468,7 @@
       <c r="E23" s="129">
         <v>54462.538760400006</v>
       </c>
-      <c r="F23" s="219">
+      <c r="F23" s="218">
         <f>E23</f>
         <v>54462.538760400006</v>
       </c>
@@ -3401,7 +3482,7 @@
       </c>
       <c r="I23" s="56">
         <f t="shared" si="2"/>
-        <v>11422.534971600002</v>
+        <v>10989.286167600001</v>
       </c>
       <c r="J23" s="56">
         <f>Edesur!N30</f>
@@ -3409,18 +3490,22 @@
       </c>
       <c r="K23" s="56">
         <f t="shared" si="3"/>
-        <v>4320</v>
+        <v>0</v>
       </c>
       <c r="L23" s="56">
         <f t="shared" si="4"/>
-        <v>6590.1275999999998</v>
+        <v>10800</v>
       </c>
       <c r="M23" s="57">
         <f t="shared" si="5"/>
-        <v>26133.699629268005</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+        <v>25590.323225268006</v>
+      </c>
+      <c r="O23" s="151">
+        <f t="shared" si="6"/>
+        <v>21789.286167600003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
         <v>49</v>
       </c>
@@ -3436,8 +3521,8 @@
       <c r="E24" s="129">
         <v>22332.662571600002</v>
       </c>
-      <c r="F24" s="219">
-        <f t="shared" ref="F24" si="9">E24</f>
+      <c r="F24" s="218">
+        <f t="shared" ref="F24" si="10">E24</f>
         <v>22332.662571600002</v>
       </c>
       <c r="G24" s="56">
@@ -3450,7 +3535,7 @@
       </c>
       <c r="I24" s="56">
         <f t="shared" si="2"/>
-        <v>11422.534971600002</v>
+        <v>10989.286167600001</v>
       </c>
       <c r="J24" s="56">
         <f>Edesur!N31</f>
@@ -3458,18 +3543,22 @@
       </c>
       <c r="K24" s="56">
         <f t="shared" si="3"/>
-        <v>4320</v>
+        <v>0</v>
       </c>
       <c r="L24" s="56">
         <f t="shared" si="4"/>
-        <v>6590.1275999999998</v>
+        <v>10800</v>
       </c>
       <c r="M24" s="57">
         <f t="shared" si="5"/>
-        <v>26133.699629268005</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+        <v>25590.323225268006</v>
+      </c>
+      <c r="O24" s="151">
+        <f t="shared" si="6"/>
+        <v>21789.286167600003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
@@ -3485,7 +3574,7 @@
       <c r="E25" s="129">
         <v>78827.255240400002</v>
       </c>
-      <c r="F25" s="219">
+      <c r="F25" s="218">
         <f>E25</f>
         <v>78827.255240400002</v>
       </c>
@@ -3499,7 +3588,7 @@
       </c>
       <c r="I25" s="56">
         <f t="shared" si="2"/>
-        <v>11422.534971600002</v>
+        <v>10989.286167600001</v>
       </c>
       <c r="J25" s="56">
         <f>Edesur!N32</f>
@@ -3507,18 +3596,22 @@
       </c>
       <c r="K25" s="56">
         <f t="shared" si="3"/>
-        <v>4320</v>
+        <v>0</v>
       </c>
       <c r="L25" s="56">
         <f t="shared" si="4"/>
-        <v>6590.1275999999998</v>
+        <v>10800</v>
       </c>
       <c r="M25" s="57">
         <f t="shared" si="5"/>
-        <v>26133.699629268005</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+        <v>25590.323225268006</v>
+      </c>
+      <c r="O25" s="151">
+        <f t="shared" si="6"/>
+        <v>21789.286167600003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
         <v>63</v>
       </c>
@@ -3532,8 +3625,8 @@
       <c r="E26" s="129">
         <v>22332.662571600002</v>
       </c>
-      <c r="F26" s="219">
-        <f t="shared" ref="F26:F28" si="10">E26</f>
+      <c r="F26" s="218">
+        <f t="shared" ref="F26:F28" si="11">E26</f>
         <v>22332.662571600002</v>
       </c>
       <c r="G26" s="56">
@@ -3546,7 +3639,7 @@
       </c>
       <c r="I26" s="56">
         <f t="shared" si="2"/>
-        <v>11422.534971600002</v>
+        <v>10989.286167600001</v>
       </c>
       <c r="J26" s="56">
         <f>Edesur!N33</f>
@@ -3554,18 +3647,22 @@
       </c>
       <c r="K26" s="56">
         <f t="shared" si="3"/>
-        <v>4320</v>
+        <v>0</v>
       </c>
       <c r="L26" s="56">
         <f t="shared" si="4"/>
-        <v>6590.1275999999998</v>
+        <v>10800</v>
       </c>
       <c r="M26" s="57">
         <f t="shared" si="5"/>
-        <v>26133.699629268005</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+        <v>25590.323225268006</v>
+      </c>
+      <c r="O26" s="151">
+        <f t="shared" si="6"/>
+        <v>21789.286167600003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
         <v>63</v>
       </c>
@@ -3579,8 +3676,8 @@
       <c r="E27" s="129">
         <v>22332.662571600002</v>
       </c>
-      <c r="F27" s="219">
-        <f t="shared" si="10"/>
+      <c r="F27" s="218">
+        <f t="shared" si="11"/>
         <v>22332.662571600002</v>
       </c>
       <c r="G27" s="56">
@@ -3593,7 +3690,7 @@
       </c>
       <c r="I27" s="56">
         <f t="shared" si="2"/>
-        <v>11422.534971600002</v>
+        <v>10989.286167600001</v>
       </c>
       <c r="J27" s="56">
         <f>Edesur!N34</f>
@@ -3601,22 +3698,26 @@
       </c>
       <c r="K27" s="56">
         <f t="shared" si="3"/>
-        <v>4320</v>
+        <v>0</v>
       </c>
       <c r="L27" s="56">
         <f t="shared" si="4"/>
-        <v>6590.1275999999998</v>
+        <v>10800</v>
       </c>
       <c r="M27" s="57">
         <f t="shared" si="5"/>
-        <v>26133.699629268005</v>
+        <v>25590.323225268006</v>
+      </c>
+      <c r="O27" s="151">
+        <f t="shared" si="6"/>
+        <v>21789.286167600003</v>
       </c>
       <c r="P27" s="44">
         <f>F27+F26+F19</f>
         <v>197685.4205412</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="66"/>
       <c r="B28" s="65" t="str">
         <f>B7</f>
@@ -3631,8 +3732,8 @@
       <c r="E28" s="129">
         <v>22332.662571600002</v>
       </c>
-      <c r="F28" s="219">
-        <f t="shared" si="10"/>
+      <c r="F28" s="218">
+        <f t="shared" si="11"/>
         <v>22332.662571600002</v>
       </c>
       <c r="G28" s="56">
@@ -3645,7 +3746,7 @@
       </c>
       <c r="I28" s="56">
         <f t="shared" si="2"/>
-        <v>11422.534971600002</v>
+        <v>10989.286167600001</v>
       </c>
       <c r="J28" s="56">
         <f>Edesur!N35</f>
@@ -3653,18 +3754,22 @@
       </c>
       <c r="K28" s="56">
         <f t="shared" si="3"/>
-        <v>4320</v>
+        <v>0</v>
       </c>
       <c r="L28" s="56">
         <f t="shared" si="4"/>
-        <v>6590.1275999999998</v>
+        <v>10800</v>
       </c>
       <c r="M28" s="57">
         <f t="shared" si="5"/>
-        <v>26133.699629268005</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+        <v>25590.323225268006</v>
+      </c>
+      <c r="O28" s="151">
+        <f t="shared" si="6"/>
+        <v>21789.286167600003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="66" t="s">
         <v>53</v>
       </c>
@@ -3680,7 +3785,7 @@
       <c r="E29" s="129">
         <v>22332.662571600002</v>
       </c>
-      <c r="F29" s="219">
+      <c r="F29" s="218">
         <f>E29</f>
         <v>22332.662571600002</v>
       </c>
@@ -3694,7 +3799,7 @@
       </c>
       <c r="I29" s="56">
         <f t="shared" si="2"/>
-        <v>11422.534971600002</v>
+        <v>10989.286167600001</v>
       </c>
       <c r="J29" s="56">
         <f>Edesur!N36</f>
@@ -3702,18 +3807,22 @@
       </c>
       <c r="K29" s="56">
         <f t="shared" si="3"/>
-        <v>4320</v>
+        <v>0</v>
       </c>
       <c r="L29" s="56">
         <f t="shared" si="4"/>
-        <v>6590.1275999999998</v>
+        <v>10800</v>
       </c>
       <c r="M29" s="57">
         <f t="shared" si="5"/>
-        <v>26133.699629268005</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+        <v>25590.323225268006</v>
+      </c>
+      <c r="O29" s="151">
+        <f t="shared" si="6"/>
+        <v>21789.286167600003</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="67"/>
       <c r="B30" s="67"/>
       <c r="C30" s="68"/>
@@ -3728,7 +3837,7 @@
       <c r="L30" s="71"/>
       <c r="M30" s="71"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="72"/>
       <c r="B31" s="73"/>
       <c r="C31" s="74" t="s">
@@ -3747,85 +3856,85 @@
       <c r="H31" s="75"/>
       <c r="I31" s="136">
         <f>SUM(I3:I30)</f>
-        <v>1057642.1270000003</v>
+        <v>1017526.4969999997</v>
       </c>
       <c r="J31" s="136"/>
       <c r="K31" s="136">
         <f>SUM(K3:K30)</f>
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="L31" s="135"/>
       <c r="M31" s="135">
         <f>SUM(M3:M29)</f>
-        <v>2991173.6031784853</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+        <v>2940860.9731784859</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K32" s="22"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" s="233" t="s">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="232" t="s">
         <v>111</v>
       </c>
-      <c r="B33" s="233"/>
-      <c r="C33" s="233"/>
-      <c r="D33" s="233"/>
-      <c r="E33" s="233"/>
-      <c r="F33" s="233"/>
-      <c r="G33" s="233"/>
-      <c r="H33" s="233"/>
-      <c r="I33" s="233"/>
-      <c r="J33" s="233"/>
-      <c r="K33" s="233"/>
-      <c r="L33" s="233"/>
-      <c r="M33" s="233"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" s="233"/>
-      <c r="B34" s="233"/>
-      <c r="C34" s="233"/>
-      <c r="D34" s="233"/>
-      <c r="E34" s="233"/>
-      <c r="F34" s="233"/>
-      <c r="G34" s="233"/>
-      <c r="H34" s="233"/>
-      <c r="I34" s="233"/>
-      <c r="J34" s="233"/>
-      <c r="K34" s="233"/>
-      <c r="L34" s="233"/>
-      <c r="M34" s="233"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" s="233"/>
-      <c r="B35" s="233"/>
-      <c r="C35" s="233"/>
-      <c r="D35" s="233"/>
-      <c r="E35" s="233"/>
-      <c r="F35" s="233"/>
-      <c r="G35" s="233"/>
-      <c r="H35" s="233"/>
-      <c r="I35" s="233"/>
-      <c r="J35" s="233"/>
-      <c r="K35" s="233"/>
-      <c r="L35" s="233"/>
-      <c r="M35" s="233"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="233"/>
-      <c r="B36" s="233"/>
-      <c r="C36" s="233"/>
-      <c r="D36" s="233"/>
-      <c r="E36" s="233"/>
-      <c r="F36" s="233"/>
-      <c r="G36" s="233"/>
-      <c r="H36" s="233"/>
-      <c r="I36" s="233"/>
-      <c r="J36" s="233"/>
-      <c r="K36" s="233"/>
-      <c r="L36" s="233"/>
-      <c r="M36" s="233"/>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B33" s="232"/>
+      <c r="C33" s="232"/>
+      <c r="D33" s="232"/>
+      <c r="E33" s="232"/>
+      <c r="F33" s="232"/>
+      <c r="G33" s="232"/>
+      <c r="H33" s="232"/>
+      <c r="I33" s="232"/>
+      <c r="J33" s="232"/>
+      <c r="K33" s="232"/>
+      <c r="L33" s="232"/>
+      <c r="M33" s="232"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="232"/>
+      <c r="B34" s="232"/>
+      <c r="C34" s="232"/>
+      <c r="D34" s="232"/>
+      <c r="E34" s="232"/>
+      <c r="F34" s="232"/>
+      <c r="G34" s="232"/>
+      <c r="H34" s="232"/>
+      <c r="I34" s="232"/>
+      <c r="J34" s="232"/>
+      <c r="K34" s="232"/>
+      <c r="L34" s="232"/>
+      <c r="M34" s="232"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="232"/>
+      <c r="B35" s="232"/>
+      <c r="C35" s="232"/>
+      <c r="D35" s="232"/>
+      <c r="E35" s="232"/>
+      <c r="F35" s="232"/>
+      <c r="G35" s="232"/>
+      <c r="H35" s="232"/>
+      <c r="I35" s="232"/>
+      <c r="J35" s="232"/>
+      <c r="K35" s="232"/>
+      <c r="L35" s="232"/>
+      <c r="M35" s="232"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="232"/>
+      <c r="B36" s="232"/>
+      <c r="C36" s="232"/>
+      <c r="D36" s="232"/>
+      <c r="E36" s="232"/>
+      <c r="F36" s="232"/>
+      <c r="G36" s="232"/>
+      <c r="H36" s="232"/>
+      <c r="I36" s="232"/>
+      <c r="J36" s="232"/>
+      <c r="K36" s="232"/>
+      <c r="L36" s="232"/>
+      <c r="M36" s="232"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E40" s="21"/>
     </row>
   </sheetData>
@@ -3838,52 +3947,52 @@
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="96" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="236" t="s">
+    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="235" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="237"/>
-      <c r="C1" s="237"/>
-      <c r="D1" s="237"/>
-      <c r="E1" s="237"/>
-      <c r="F1" s="237"/>
-      <c r="G1" s="237"/>
-      <c r="H1" s="237"/>
-      <c r="I1" s="237"/>
-      <c r="J1" s="237"/>
-      <c r="K1" s="237"/>
-      <c r="L1" s="237"/>
-      <c r="M1" s="237"/>
-      <c r="N1" s="238"/>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="236"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="236"/>
+      <c r="I1" s="236"/>
+      <c r="J1" s="236"/>
+      <c r="K1" s="236"/>
+      <c r="L1" s="236"/>
+      <c r="M1" s="236"/>
+      <c r="N1" s="237"/>
       <c r="O1" s="76"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="77"/>
       <c r="B2" s="77"/>
       <c r="C2" s="161"/>
@@ -3901,7 +4010,7 @@
       <c r="O2" s="78"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="80"/>
       <c r="C3" s="163"/>
@@ -3919,7 +4028,7 @@
       <c r="O3" s="78"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="80"/>
       <c r="B4" s="80"/>
       <c r="C4" s="163"/>
@@ -3939,7 +4048,7 @@
       <c r="O4" s="78"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="80"/>
       <c r="B5" s="80"/>
       <c r="C5" s="163"/>
@@ -3957,10 +4066,10 @@
       <c r="O5" s="78"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="80"/>
       <c r="B6" s="80"/>
-      <c r="C6" s="218" t="str">
+      <c r="C6" s="217" t="str">
         <f>'detalle y gastos'!C7</f>
         <v>Vto. 15/12</v>
       </c>
@@ -3978,7 +4087,7 @@
       <c r="O6" s="78"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="81"/>
       <c r="B7" s="81" t="s">
         <v>77</v>
@@ -4005,7 +4114,7 @@
       <c r="O7" s="78"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="81"/>
       <c r="B8" s="80" t="s">
         <v>77</v>
@@ -4021,16 +4130,16 @@
         <f>C8-J38</f>
         <v>-199922.9342899998</v>
       </c>
-      <c r="L8" s="240">
+      <c r="L8" s="239">
         <f>C7-J38</f>
         <v>351947.87571000028</v>
       </c>
-      <c r="M8" s="240"/>
+      <c r="M8" s="239"/>
       <c r="N8" s="84"/>
       <c r="O8" s="78"/>
       <c r="P8" s="11"/>
     </row>
-    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="87" t="s">
         <v>78</v>
       </c>
@@ -4075,7 +4184,7 @@
       </c>
       <c r="P9" s="11"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="98">
         <v>1</v>
       </c>
@@ -4127,11 +4236,11 @@
       </c>
       <c r="O10" s="97">
         <f>N10+'prorrateo '!M3</f>
-        <v>167684.05366726202</v>
+        <v>165113.07827426199</v>
       </c>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="99">
         <v>2</v>
       </c>
@@ -4183,11 +4292,11 @@
       </c>
       <c r="O11" s="97">
         <f>N11+'prorrateo '!M4</f>
-        <v>160082.55151157806</v>
+        <v>157521.63864457805</v>
       </c>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="98">
         <v>3</v>
       </c>
@@ -4239,14 +4348,14 @@
       </c>
       <c r="O12" s="97">
         <f>N12+'prorrateo '!M5</f>
-        <v>191204.68394683208</v>
+        <v>188668.92739483208</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="98">
         <v>4</v>
       </c>
@@ -4298,11 +4407,11 @@
       </c>
       <c r="O13" s="97">
         <f>N13+'prorrateo '!M6</f>
-        <v>271175.74142305006</v>
+        <v>268554.45340005006</v>
       </c>
       <c r="P13" s="11"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="98">
         <v>6</v>
       </c>
@@ -4354,11 +4463,11 @@
       </c>
       <c r="O14" s="97">
         <f>N14+'prorrateo '!M7</f>
-        <v>160449.32448726203</v>
+        <v>157878.34909426203</v>
       </c>
       <c r="P14" s="11"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="98">
         <v>7</v>
       </c>
@@ -4410,10 +4519,10 @@
       </c>
       <c r="O15" s="97">
         <f>N15+'prorrateo '!M8</f>
-        <v>156256.04191157804</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+        <v>153695.12904457803</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="98">
         <v>8</v>
       </c>
@@ -4465,10 +4574,10 @@
       </c>
       <c r="O16" s="97">
         <f>N16+'prorrateo '!M9</f>
-        <v>158742.40108726203</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+        <v>156171.425694262</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="98">
         <v>9</v>
       </c>
@@ -4520,10 +4629,10 @@
       </c>
       <c r="O17" s="97">
         <f>N17+'prorrateo '!M10</f>
-        <v>145639.35351157797</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+        <v>143078.44064457796</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="98">
         <v>10</v>
       </c>
@@ -4575,10 +4684,10 @@
       </c>
       <c r="O18" s="97">
         <f>N18+'prorrateo '!M11</f>
-        <v>155489.16867236802</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>152953.41212036801</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="98">
         <v>11</v>
       </c>
@@ -4630,10 +4739,10 @@
       </c>
       <c r="O19" s="97">
         <f>N19+'prorrateo '!M12</f>
-        <v>186292.66136568191</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>183671.37334268191</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="98">
         <v>12</v>
       </c>
@@ -4685,40 +4794,40 @@
       </c>
       <c r="O20" s="97">
         <f>N20+'prorrateo '!M13</f>
-        <v>249565.73188726197</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+        <v>246994.75649426196</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="98">
         <v>13</v>
       </c>
       <c r="B21" s="89">
         <v>13</v>
       </c>
-      <c r="C21" s="211" t="s">
+      <c r="C21" s="210" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="212" t="s">
+      <c r="D21" s="211" t="s">
         <v>49</v>
       </c>
-      <c r="E21" s="213">
+      <c r="E21" s="212">
         <v>5.09</v>
       </c>
-      <c r="F21" s="214">
+      <c r="F21" s="213">
         <v>4112.1000000000004</v>
       </c>
-      <c r="G21" s="214">
+      <c r="G21" s="213">
         <v>4199</v>
       </c>
       <c r="H21" s="147">
         <f t="shared" si="1"/>
         <v>86.899999999999636</v>
       </c>
-      <c r="I21" s="215">
+      <c r="I21" s="214">
         <f t="shared" si="0"/>
         <v>6.0829999999999753</v>
       </c>
-      <c r="J21" s="216">
+      <c r="J21" s="215">
         <f t="shared" si="2"/>
         <v>8150.0902999999662</v>
       </c>
@@ -4740,10 +4849,10 @@
       </c>
       <c r="O21" s="97">
         <f>N21+'prorrateo '!M14</f>
-        <v>112597.70171067795</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+        <v>110036.78884367795</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="98">
         <v>14</v>
       </c>
@@ -4795,10 +4904,10 @@
       </c>
       <c r="O22" s="97">
         <f>N22+'prorrateo '!M15</f>
-        <v>150124.55690286399</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+        <v>147588.80035086398</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="98">
         <v>15</v>
       </c>
@@ -4850,10 +4959,10 @@
       </c>
       <c r="O23" s="97">
         <f>N23+'prorrateo '!M16</f>
-        <v>165678.27876568199</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+        <v>163056.99074268198</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="98">
         <v>16</v>
       </c>
@@ -4905,10 +5014,10 @@
       </c>
       <c r="O24" s="97">
         <f>N24+'prorrateo '!M17</f>
-        <v>144572.36187236803</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+        <v>142036.60532036802</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="98">
         <v>17</v>
       </c>
@@ -4960,10 +5069,10 @@
       </c>
       <c r="O25" s="97">
         <f>N25+'prorrateo '!M18</f>
-        <v>159432.06456568206</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+        <v>156810.77654268206</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="98">
         <v>18</v>
       </c>
@@ -5015,10 +5124,10 @@
       </c>
       <c r="O26" s="97">
         <f>N26+'prorrateo '!M19</f>
-        <v>235607.91340308011</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>231884.77878308011</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="98">
         <v>19</v>
       </c>
@@ -5057,10 +5166,10 @@
       </c>
       <c r="O27" s="97">
         <f>N27+'prorrateo '!M20</f>
-        <v>29934.736686936008</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+        <v>29391.36028293601</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="98">
         <v>20</v>
       </c>
@@ -5096,10 +5205,10 @@
       </c>
       <c r="O28" s="97">
         <f>N28+'prorrateo '!M21</f>
-        <v>29934.736686936008</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+        <v>29391.36028293601</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="98"/>
       <c r="B29" s="90"/>
       <c r="C29" s="158" t="s">
@@ -5128,10 +5237,10 @@
       </c>
       <c r="O29" s="97">
         <f>N29+'prorrateo '!M22</f>
-        <v>303037.19230399205</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+        <v>302493.81589999207</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="98"/>
       <c r="B30" s="90"/>
       <c r="C30" s="169" t="s">
@@ -5160,10 +5269,10 @@
       </c>
       <c r="O30" s="97">
         <f>N30+'prorrateo '!M23</f>
-        <v>29934.736686936008</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+        <v>29391.36028293601</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="98"/>
       <c r="B31" s="90"/>
       <c r="C31" s="169" t="s">
@@ -5194,12 +5303,12 @@
       </c>
       <c r="O31" s="97">
         <f>N31+'prorrateo '!M24</f>
-        <v>29934.736686936008</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+        <v>29391.36028293601</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="99"/>
-      <c r="B32" s="217"/>
+      <c r="B32" s="216"/>
       <c r="C32" s="158" t="s">
         <v>70</v>
       </c>
@@ -5228,10 +5337,10 @@
       </c>
       <c r="O32" s="97">
         <f>N32+'prorrateo '!M25</f>
-        <v>29934.736686936008</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+        <v>29391.36028293601</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="98"/>
       <c r="B33" s="90"/>
       <c r="C33" s="130" t="s">
@@ -5262,10 +5371,10 @@
       </c>
       <c r="O33" s="97">
         <f>N33+'prorrateo '!M26</f>
-        <v>29934.736686936008</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+        <v>29391.36028293601</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="98"/>
       <c r="B34" s="90"/>
       <c r="C34" s="130" t="s">
@@ -5296,10 +5405,10 @@
       </c>
       <c r="O34" s="97">
         <f>N34+'prorrateo '!M27</f>
-        <v>29934.736686936008</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+        <v>29391.36028293601</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="98">
         <v>21</v>
       </c>
@@ -5335,10 +5444,10 @@
       </c>
       <c r="O35" s="97">
         <f>N35+'prorrateo '!M28</f>
-        <v>29934.736686936008</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+        <v>29391.36028293601</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="98">
         <v>22</v>
       </c>
@@ -5376,10 +5485,10 @@
       </c>
       <c r="O36" s="97">
         <f>N36+'prorrateo '!M29</f>
-        <v>29934.736686936008</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+        <v>29391.36028293601</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="98">
         <v>23</v>
       </c>
@@ -5409,7 +5518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="98">
         <v>24</v>
       </c>
@@ -5437,7 +5546,7 @@
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="78"/>
       <c r="C39" s="91"/>
       <c r="D39" s="92"/>
@@ -5462,41 +5571,41 @@
       <c r="N39" s="93"/>
       <c r="O39" s="79"/>
     </row>
-    <row r="40" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="95" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="239"/>
-      <c r="D40" s="237"/>
-      <c r="E40" s="237"/>
-      <c r="F40" s="237"/>
-      <c r="G40" s="237"/>
-      <c r="H40" s="237"/>
-      <c r="I40" s="237"/>
-      <c r="J40" s="237"/>
-      <c r="K40" s="237"/>
-      <c r="L40" s="237"/>
-      <c r="M40" s="237"/>
-      <c r="N40" s="237"/>
+      <c r="C40" s="238"/>
+      <c r="D40" s="236"/>
+      <c r="E40" s="236"/>
+      <c r="F40" s="236"/>
+      <c r="G40" s="236"/>
+      <c r="H40" s="236"/>
+      <c r="I40" s="236"/>
+      <c r="J40" s="236"/>
+      <c r="K40" s="236"/>
+      <c r="L40" s="236"/>
+      <c r="M40" s="236"/>
+      <c r="N40" s="236"/>
       <c r="O40" s="95"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H41" s="79"/>
       <c r="J41" s="96"/>
       <c r="K41" s="96"/>
       <c r="L41" s="96"/>
       <c r="N41" s="97"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L44" s="151"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L45" s="96"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E46" s="152"/>
       <c r="F46" s="152"/>
       <c r="G46" s="152"/>
